--- a/VT_Model_DMD.xlsx
+++ b/VT_Model_DMD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showObjects="placeholders" codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\2026\2. AGR_model_wyizolowany\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\1. 2026\2. AGR_model_wyizolowany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB09588-B985-41FB-859C-E5D3B994A296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D46D7F7-A5FF-4C40-9055-9331D947E2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I73" authorId="1" shapeId="0" xr:uid="{75EE449B-1191-42E9-9288-D8EEF162166B}">
+    <comment ref="I75" authorId="1" shapeId="0" xr:uid="{75EE449B-1191-42E9-9288-D8EEF162166B}">
       <text>
         <t>[Komentarz podzielony na wątki]
 Używana wersja programu Excel umożliwia odczytanie tego komentarza podzielonego na wątki, jednak wszelkie wprowadzone w nim zmiany zostaną usunięte po otwarciu pliku w nowszej wersji programu Excel. Dowiedz się więcej: https://go.microsoft.com/fwlink/?linkid=870924
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="189">
   <si>
     <t>Typ dokumentu</t>
   </si>
@@ -1163,6 +1163,12 @@
   </si>
   <si>
     <t>crop in kt</t>
+  </si>
+  <si>
+    <t>PRI_BIOG_AGR</t>
+  </si>
+  <si>
+    <t>PRI_BIO_CH4_AGR</t>
   </si>
 </sst>
 </file>
@@ -5638,7 +5644,7 @@
       <alignment horizontal="right"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5830,7 +5836,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="19" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="19" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="30" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5879,35 +5884,35 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="53" xfId="14" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="3" borderId="25" xfId="14" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="3" borderId="54" xfId="14" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="4" borderId="0" xfId="19" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="5" borderId="0" xfId="19" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="14" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="19" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="14" fillId="3" borderId="0" xfId="14" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2193">
     <cellStyle name="20 % - Akzent1 2" xfId="67" xr:uid="{0BDC621E-8D3A-42DB-9E36-DCD3236A3B37}"/>
@@ -9268,7 +9273,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I73" dT="2025-10-21T08:46:14.13" personId="{7AFA507A-0B28-4B68-9CA2-DAF5F4D8282E}" id="{75EE449B-1191-42E9-9288-D8EEF162166B}">
+  <threadedComment ref="I75" dT="2025-10-21T08:46:14.13" personId="{7AFA507A-0B28-4B68-9CA2-DAF5F4D8282E}" id="{75EE449B-1191-42E9-9288-D8EEF162166B}">
     <text>Brak danych dla 2020r. - pobrano dane z odpowiadającego dokumentu dla roku 2022.</text>
   </threadedComment>
 </ThreadedComments>
@@ -9412,15 +9417,15 @@
       <c r="A14" s="52"/>
       <c r="B14" s="47"/>
       <c r="C14" s="42"/>
-      <c r="D14" s="159" t="s">
+      <c r="D14" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="159"/>
-      <c r="F14" s="160" t="s">
+      <c r="E14" s="164"/>
+      <c r="F14" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="160"/>
-      <c r="H14" s="160"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="165"/>
       <c r="J14" s="41"/>
       <c r="K14" s="43"/>
       <c r="L14" s="52"/>
@@ -9431,9 +9436,9 @@
       <c r="C15" s="42"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="160"/>
-      <c r="H15" s="160"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="165"/>
+      <c r="H15" s="165"/>
       <c r="J15" s="41"/>
       <c r="K15" s="43"/>
       <c r="L15" s="52"/>
@@ -9458,16 +9463,16 @@
       <c r="A18" s="52"/>
       <c r="B18" s="47"/>
       <c r="C18" s="42"/>
-      <c r="D18" s="159" t="s">
+      <c r="D18" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="159"/>
-      <c r="F18" s="160" t="s">
+      <c r="E18" s="164"/>
+      <c r="F18" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="160"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="160"/>
+      <c r="G18" s="165"/>
+      <c r="H18" s="165"/>
+      <c r="I18" s="165"/>
       <c r="J18" s="41"/>
       <c r="K18" s="43"/>
       <c r="L18" s="52"/>
@@ -9478,10 +9483,10 @@
       <c r="C19" s="42"/>
       <c r="D19" s="39"/>
       <c r="E19" s="39"/>
-      <c r="F19" s="160"/>
-      <c r="G19" s="160"/>
-      <c r="H19" s="160"/>
-      <c r="I19" s="160"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
+      <c r="H19" s="165"/>
+      <c r="I19" s="165"/>
       <c r="J19" s="41"/>
       <c r="K19" s="43"/>
       <c r="L19" s="52"/>
@@ -9492,10 +9497,10 @@
       <c r="C20" s="42"/>
       <c r="D20" s="39"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="160"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="165"/>
+      <c r="I20" s="165"/>
       <c r="J20" s="41"/>
       <c r="K20" s="43"/>
       <c r="L20" s="52"/>
@@ -9515,10 +9520,10 @@
       <c r="A22" s="52"/>
       <c r="B22" s="47"/>
       <c r="C22" s="42"/>
-      <c r="D22" s="159" t="s">
+      <c r="D22" s="164" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="159"/>
+      <c r="E22" s="164"/>
       <c r="F22" s="37">
         <v>45173</v>
       </c>
@@ -9596,10 +9601,10 @@
       <c r="A28" s="52"/>
       <c r="B28" s="47"/>
       <c r="C28" s="42"/>
-      <c r="D28" s="159" t="s">
+      <c r="D28" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="159"/>
+      <c r="E28" s="164"/>
       <c r="F28" s="51" t="s">
         <v>7</v>
       </c>
@@ -9638,10 +9643,10 @@
       <c r="A32" s="52"/>
       <c r="B32" s="47"/>
       <c r="C32" s="42"/>
-      <c r="D32" s="159" t="s">
+      <c r="D32" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="159"/>
+      <c r="E32" s="164"/>
       <c r="F32" s="51" t="s">
         <v>7</v>
       </c>
@@ -9805,11 +9810,11 @@
       <c r="A4" s="52"/>
       <c r="B4" s="47"/>
       <c r="C4" s="42"/>
-      <c r="D4" s="161" t="s">
+      <c r="D4" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
+      <c r="E4" s="166"/>
+      <c r="F4" s="166"/>
       <c r="G4" s="41"/>
       <c r="H4" s="43"/>
       <c r="I4" s="52"/>
@@ -9829,11 +9834,11 @@
       <c r="A6" s="52"/>
       <c r="B6" s="47"/>
       <c r="C6" s="42"/>
-      <c r="D6" s="141" t="s">
+      <c r="D6" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="E6" s="140"/>
-      <c r="F6" s="140"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
       <c r="G6" s="41"/>
       <c r="H6" s="43"/>
       <c r="I6" s="52"/>
@@ -9842,9 +9847,9 @@
       <c r="A7" s="52"/>
       <c r="B7" s="47"/>
       <c r="C7" s="42"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
       <c r="G7" s="41"/>
       <c r="H7" s="43"/>
       <c r="I7" s="52"/>
@@ -9853,13 +9858,13 @@
       <c r="A8" s="52"/>
       <c r="B8" s="47"/>
       <c r="C8" s="42"/>
-      <c r="D8" s="142" t="s">
+      <c r="D8" s="141" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="142" t="s">
+      <c r="E8" s="141" t="s">
         <v>147</v>
       </c>
-      <c r="F8" s="142" t="s">
+      <c r="F8" s="141" t="s">
         <v>148</v>
       </c>
       <c r="G8" s="41"/>
@@ -9870,13 +9875,13 @@
       <c r="A9" s="52"/>
       <c r="B9" s="47"/>
       <c r="C9" s="42"/>
-      <c r="D9" s="137" t="s">
+      <c r="D9" s="136" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="143" t="s">
+      <c r="E9" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="137" t="s">
+      <c r="F9" s="136" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="41"/>
@@ -9887,13 +9892,13 @@
       <c r="A10" s="52"/>
       <c r="B10" s="47"/>
       <c r="C10" s="42"/>
-      <c r="D10" s="137" t="s">
+      <c r="D10" s="136" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="143" t="s">
+      <c r="E10" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="137" t="s">
+      <c r="F10" s="136" t="s">
         <v>151</v>
       </c>
       <c r="G10" s="41"/>
@@ -9904,13 +9909,13 @@
       <c r="A11" s="52"/>
       <c r="B11" s="47"/>
       <c r="C11" s="42"/>
-      <c r="D11" s="137" t="s">
+      <c r="D11" s="136" t="s">
         <v>154</v>
       </c>
-      <c r="E11" s="143" t="s">
+      <c r="E11" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="F11" s="137" t="s">
+      <c r="F11" s="136" t="s">
         <v>162</v>
       </c>
       <c r="G11" s="41"/>
@@ -9921,13 +9926,13 @@
       <c r="A12" s="52"/>
       <c r="B12" s="47"/>
       <c r="C12" s="42"/>
-      <c r="D12" s="137" t="s">
+      <c r="D12" s="136" t="s">
         <v>155</v>
       </c>
-      <c r="E12" s="143" t="s">
+      <c r="E12" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="137" t="s">
+      <c r="F12" s="136" t="s">
         <v>162</v>
       </c>
       <c r="G12" s="41"/>
@@ -9938,13 +9943,13 @@
       <c r="A13" s="52"/>
       <c r="B13" s="47"/>
       <c r="C13" s="42"/>
-      <c r="D13" s="137" t="s">
+      <c r="D13" s="136" t="s">
         <v>156</v>
       </c>
-      <c r="E13" s="143" t="s">
+      <c r="E13" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="F13" s="137" t="s">
+      <c r="F13" s="136" t="s">
         <v>162</v>
       </c>
       <c r="G13" s="41"/>
@@ -9955,13 +9960,13 @@
       <c r="A14" s="52"/>
       <c r="B14" s="47"/>
       <c r="C14" s="42"/>
-      <c r="D14" s="137" t="s">
+      <c r="D14" s="136" t="s">
         <v>157</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="F14" s="137" t="s">
+      <c r="F14" s="136" t="s">
         <v>162</v>
       </c>
       <c r="G14" s="41"/>
@@ -9972,7 +9977,7 @@
       <c r="A15" s="52"/>
       <c r="B15" s="47"/>
       <c r="C15" s="42"/>
-      <c r="D15" s="137" t="s">
+      <c r="D15" s="136" t="s">
         <v>158</v>
       </c>
       <c r="E15" s="27" t="s">
@@ -9987,7 +9992,7 @@
       <c r="A16" s="52"/>
       <c r="B16" s="47"/>
       <c r="C16" s="42"/>
-      <c r="D16" s="137" t="s">
+      <c r="D16" s="136" t="s">
         <v>159</v>
       </c>
       <c r="E16" s="27" t="s">
@@ -10002,7 +10007,7 @@
       <c r="A17" s="52"/>
       <c r="B17" s="47"/>
       <c r="C17" s="42"/>
-      <c r="D17" s="137" t="s">
+      <c r="D17" s="136" t="s">
         <v>160</v>
       </c>
       <c r="E17" s="27" t="s">
@@ -10017,7 +10022,7 @@
       <c r="A18" s="52"/>
       <c r="B18" s="47"/>
       <c r="C18" s="42"/>
-      <c r="D18" s="137" t="s">
+      <c r="D18" s="136" t="s">
         <v>161</v>
       </c>
       <c r="E18" s="27" t="s">
@@ -10445,7 +10450,7 @@
       <c r="C9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="152" t="s">
+      <c r="D9" s="151" t="s">
         <v>175</v>
       </c>
       <c r="E9" s="18" t="s">
@@ -10466,7 +10471,7 @@
       <c r="C10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="152" t="s">
+      <c r="D10" s="151" t="s">
         <v>176</v>
       </c>
       <c r="E10" s="16" t="s">
@@ -10481,25 +10486,25 @@
       <c r="J10" s="19"/>
     </row>
     <row r="11" spans="2:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B11" s="145" t="s">
+      <c r="B11" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="145" t="s">
+      <c r="C11" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="153" t="s">
+      <c r="D11" s="152" t="s">
         <v>177</v>
       </c>
-      <c r="E11" s="145" t="s">
+      <c r="E11" s="144" t="s">
         <v>179</v>
       </c>
-      <c r="F11" s="145" t="s">
+      <c r="F11" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
     </row>
     <row r="24" ht="13.7" customHeight="1"/>
   </sheetData>
@@ -10770,7 +10775,7 @@
       <c r="F6" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="154"/>
+      <c r="G6" s="153"/>
       <c r="H6" s="13" t="s">
         <v>68</v>
       </c>
@@ -10853,24 +10858,24 @@
       <c r="I10" s="9"/>
     </row>
     <row r="11" spans="2:12" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B11" s="148" t="str">
+      <c r="B11" s="147" t="str">
         <f>DMD_Processes!D8</f>
         <v>DMD_HT_DH_FIN_ADD</v>
       </c>
-      <c r="C11" s="148"/>
-      <c r="D11" s="149" t="s">
+      <c r="C11" s="147"/>
+      <c r="D11" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="148" t="str">
+      <c r="E11" s="147" t="str">
         <f>DMD_Comm!D8</f>
         <v>PL_DEM_HT_DH_FIN_ADD</v>
       </c>
-      <c r="F11" s="148"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="150">
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="149">
         <v>1</v>
       </c>
-      <c r="I11" s="150">
+      <c r="I11" s="149">
         <v>1</v>
       </c>
     </row>
@@ -10885,7 +10890,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41D2646-6146-4D14-B889-3C0C97BBED9D}">
-  <dimension ref="A2:S82"/>
+  <dimension ref="A2:S84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="72" bestFit="1" customWidth="1"/>
@@ -10915,58 +10920,58 @@
       <c r="D3" s="63"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="132" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="133">
-        <v>2020</v>
-      </c>
-      <c r="E4" s="133">
+      <c r="D4" s="132">
+        <v>2024</v>
+      </c>
+      <c r="E4" s="132">
         <v>2025</v>
       </c>
-      <c r="F4" s="133">
+      <c r="F4" s="132">
         <v>2030</v>
       </c>
-      <c r="G4" s="133">
+      <c r="G4" s="132">
         <v>2035</v>
       </c>
-      <c r="H4" s="133">
+      <c r="H4" s="132">
         <v>2040</v>
       </c>
-      <c r="I4" s="133">
+      <c r="I4" s="132">
         <v>2045</v>
       </c>
-      <c r="J4" s="133">
+      <c r="J4" s="132">
         <v>2050</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.5" thickBot="1">
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="133" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134" t="s">
+      <c r="C5" s="133"/>
+      <c r="D5" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="135" t="s">
+      <c r="E5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="135" t="s">
+      <c r="F5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="135" t="s">
+      <c r="G5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="135" t="s">
+      <c r="H5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="135" t="s">
+      <c r="I5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="135" t="s">
+      <c r="J5" s="134" t="s">
         <v>77</v>
       </c>
     </row>
@@ -10980,22 +10985,22 @@
       <c r="D6" s="68">
         <v>100</v>
       </c>
-      <c r="E6" s="136">
+      <c r="E6" s="135">
         <v>100</v>
       </c>
-      <c r="F6" s="136">
+      <c r="F6" s="135">
         <v>100</v>
       </c>
-      <c r="G6" s="136">
+      <c r="G6" s="135">
         <v>100</v>
       </c>
-      <c r="H6" s="136">
+      <c r="H6" s="135">
         <v>100</v>
       </c>
-      <c r="I6" s="136">
+      <c r="I6" s="135">
         <v>100</v>
       </c>
-      <c r="J6" s="136">
+      <c r="J6" s="135">
         <v>100</v>
       </c>
     </row>
@@ -11015,17 +11020,17 @@
       <c r="J7" s="69"/>
     </row>
     <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="131" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="71" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="129">
-        <f>D76/1000</f>
+        <f>D78/1000</f>
         <v>2101.1590000000001</v>
       </c>
-      <c r="E8" s="132">
+      <c r="E8" s="131">
         <f>D8</f>
         <v>2101.1590000000001</v>
       </c>
@@ -11037,7 +11042,7 @@
         <f t="shared" si="0"/>
         <v>2101.1590000000001</v>
       </c>
-      <c r="H8" s="132">
+      <c r="H8" s="131">
         <f t="shared" si="0"/>
         <v>2101.1590000000001</v>
       </c>
@@ -11051,17 +11056,17 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B9" s="131" t="s">
+      <c r="B9" s="130" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="70" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="70">
-        <f>(C76-D76)/1000</f>
+        <f>(C78-D78)/1000</f>
         <v>4089.768</v>
       </c>
-      <c r="E9" s="131">
+      <c r="E9" s="130">
         <f t="shared" ref="E9:J28" si="1">D9</f>
         <v>4089.768</v>
       </c>
@@ -11073,7 +11078,7 @@
         <f t="shared" si="1"/>
         <v>4089.768</v>
       </c>
-      <c r="H9" s="131">
+      <c r="H9" s="130">
         <f t="shared" si="1"/>
         <v>4089.768</v>
       </c>
@@ -11087,53 +11092,53 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B10" s="130" t="s">
+      <c r="B10" s="167" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="53">
-        <f>G76/1000</f>
+      <c r="D10" s="168">
+        <f>G78/1000</f>
         <v>269.53800000000001</v>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="79">
         <f t="shared" si="1"/>
         <v>269.53800000000001</v>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="79">
         <f t="shared" si="1"/>
         <v>269.53800000000001</v>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="79">
         <f t="shared" si="1"/>
         <v>269.53800000000001</v>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="79">
         <f t="shared" si="1"/>
         <v>269.53800000000001</v>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="79">
         <f t="shared" si="1"/>
         <v>269.53800000000001</v>
       </c>
-      <c r="J10" s="72">
+      <c r="J10" s="79">
         <f t="shared" si="1"/>
         <v>269.53800000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="130" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="70" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="70">
-        <f>E76/1000</f>
+        <f>E78/1000</f>
         <v>9078.25</v>
       </c>
-      <c r="E11" s="131">
+      <c r="E11" s="130">
         <f t="shared" si="1"/>
         <v>9078.25</v>
       </c>
@@ -11145,7 +11150,7 @@
         <f t="shared" si="1"/>
         <v>9078.25</v>
       </c>
-      <c r="H11" s="131">
+      <c r="H11" s="130">
         <f t="shared" si="1"/>
         <v>9078.25</v>
       </c>
@@ -11159,53 +11164,53 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="167" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="53">
-        <f>I76/1000</f>
+      <c r="D12" s="168">
+        <f>I78/1000</f>
         <v>64.180000000000007</v>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="79">
         <f t="shared" si="1"/>
         <v>64.180000000000007</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="79">
         <f t="shared" si="1"/>
         <v>64.180000000000007</v>
       </c>
-      <c r="G12" s="72">
+      <c r="G12" s="79">
         <f t="shared" si="1"/>
         <v>64.180000000000007</v>
       </c>
-      <c r="H12" s="72">
+      <c r="H12" s="79">
         <f t="shared" si="1"/>
         <v>64.180000000000007</v>
       </c>
-      <c r="I12" s="72">
+      <c r="I12" s="79">
         <f t="shared" si="1"/>
         <v>64.180000000000007</v>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="79">
         <f t="shared" si="1"/>
         <v>64.180000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B13" s="131" t="s">
+      <c r="B13" s="130" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="70" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="70">
-        <f>D82/1000</f>
+        <f>D84/1000</f>
         <v>268862.57400000002</v>
       </c>
-      <c r="E13" s="131">
+      <c r="E13" s="130">
         <f t="shared" si="1"/>
         <v>268862.57400000002</v>
       </c>
@@ -11217,7 +11222,7 @@
         <f t="shared" si="1"/>
         <v>268862.57400000002</v>
       </c>
-      <c r="H13" s="131">
+      <c r="H13" s="130">
         <f t="shared" si="1"/>
         <v>268862.57400000002</v>
       </c>
@@ -11246,17 +11251,17 @@
       <c r="J14" s="69"/>
     </row>
     <row r="15" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B15" s="132" t="s">
+      <c r="B15" s="131" t="s">
         <v>86</v>
       </c>
       <c r="C15" s="71" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="129">
-        <f>H40</f>
+        <f>H42</f>
         <v>12405.603600000002</v>
       </c>
-      <c r="E15" s="167">
+      <c r="E15" s="157">
         <f t="shared" si="1"/>
         <v>12405.603600000002</v>
       </c>
@@ -11268,7 +11273,7 @@
         <f t="shared" si="1"/>
         <v>12405.603600000002</v>
       </c>
-      <c r="H15" s="167">
+      <c r="H15" s="157">
         <f t="shared" si="1"/>
         <v>12405.603600000002</v>
       </c>
@@ -11282,472 +11287,472 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="B16" s="131" t="s">
+      <c r="B16" s="130" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="168">
-        <f>H44</f>
+      <c r="D16" s="158">
+        <f>H46</f>
         <v>3017.6627599999997</v>
       </c>
-      <c r="E16" s="169">
+      <c r="E16" s="159">
         <f t="shared" si="1"/>
         <v>3017.6627599999997</v>
       </c>
-      <c r="F16" s="168">
+      <c r="F16" s="158">
         <f t="shared" si="1"/>
         <v>3017.6627599999997</v>
       </c>
-      <c r="G16" s="168">
+      <c r="G16" s="158">
         <f t="shared" si="1"/>
         <v>3017.6627599999997</v>
       </c>
-      <c r="H16" s="169">
+      <c r="H16" s="159">
         <f t="shared" si="1"/>
         <v>3017.6627599999997</v>
       </c>
-      <c r="I16" s="168">
+      <c r="I16" s="158">
         <f t="shared" si="1"/>
         <v>3017.6627599999997</v>
       </c>
-      <c r="J16" s="168">
+      <c r="J16" s="158">
         <f t="shared" si="1"/>
         <v>3017.6627599999997</v>
       </c>
     </row>
     <row r="17" spans="2:19">
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="167" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="170">
-        <f>H52</f>
+      <c r="D17" s="169">
+        <f>H54</f>
         <v>9396.7107199999991</v>
       </c>
-      <c r="E17" s="171">
+      <c r="E17" s="170">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="F17" s="171">
+      <c r="F17" s="170">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="G17" s="171">
+      <c r="G17" s="170">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="H17" s="171">
+      <c r="H17" s="170">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="I17" s="171">
+      <c r="I17" s="170">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="J17" s="171">
+      <c r="J17" s="170">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
     </row>
     <row r="18" spans="2:19">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="130" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="168">
-        <f>H50</f>
+      <c r="D18" s="158">
+        <f>H52</f>
         <v>832.92</v>
       </c>
-      <c r="E18" s="169">
+      <c r="E18" s="159">
         <f t="shared" si="1"/>
         <v>832.92</v>
       </c>
-      <c r="F18" s="168">
+      <c r="F18" s="158">
         <f t="shared" si="1"/>
         <v>832.92</v>
       </c>
-      <c r="G18" s="168">
+      <c r="G18" s="158">
         <f t="shared" si="1"/>
         <v>832.92</v>
       </c>
-      <c r="H18" s="169">
+      <c r="H18" s="159">
         <f t="shared" si="1"/>
         <v>832.92</v>
       </c>
-      <c r="I18" s="168">
+      <c r="I18" s="158">
         <f t="shared" si="1"/>
         <v>832.92</v>
       </c>
-      <c r="J18" s="168">
+      <c r="J18" s="158">
         <f t="shared" si="1"/>
         <v>832.92</v>
       </c>
     </row>
     <row r="19" spans="2:19">
-      <c r="B19" s="130" t="s">
+      <c r="B19" s="167" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="170">
-        <f>H48</f>
+      <c r="D19" s="169">
+        <f>H50</f>
         <v>5046.9496000000008</v>
       </c>
-      <c r="E19" s="171">
+      <c r="E19" s="170">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="F19" s="171">
+      <c r="F19" s="170">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="G19" s="171">
+      <c r="G19" s="170">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="H19" s="171">
+      <c r="H19" s="170">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="I19" s="171">
+      <c r="I19" s="170">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="J19" s="171">
+      <c r="J19" s="170">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
       <c r="S19" s="63"/>
     </row>
     <row r="20" spans="2:19">
-      <c r="B20" s="131" t="s">
+      <c r="B20" s="130" t="s">
         <v>91</v>
       </c>
       <c r="C20" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="168">
-        <f>H46</f>
+      <c r="D20" s="158">
+        <f>H48</f>
         <v>1645.2395100000001</v>
       </c>
-      <c r="E20" s="169">
+      <c r="E20" s="159">
         <f t="shared" si="1"/>
         <v>1645.2395100000001</v>
       </c>
-      <c r="F20" s="168">
+      <c r="F20" s="158">
         <f t="shared" si="1"/>
         <v>1645.2395100000001</v>
       </c>
-      <c r="G20" s="168">
+      <c r="G20" s="158">
         <f t="shared" si="1"/>
         <v>1645.2395100000001</v>
       </c>
-      <c r="H20" s="169">
+      <c r="H20" s="159">
         <f t="shared" si="1"/>
         <v>1645.2395100000001</v>
       </c>
-      <c r="I20" s="168">
+      <c r="I20" s="158">
         <f t="shared" si="1"/>
         <v>1645.2395100000001</v>
       </c>
-      <c r="J20" s="168">
+      <c r="J20" s="158">
         <f t="shared" si="1"/>
         <v>1645.2395100000001</v>
       </c>
       <c r="S20" s="63"/>
     </row>
     <row r="21" spans="2:19">
-      <c r="B21" s="130" t="s">
+      <c r="B21" s="167" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="170">
-        <f>H42</f>
+      <c r="D21" s="169">
+        <f>H44</f>
         <v>2435.3861700000002</v>
       </c>
-      <c r="E21" s="171">
+      <c r="E21" s="170">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="F21" s="171">
+      <c r="F21" s="170">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="G21" s="171">
+      <c r="G21" s="170">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="H21" s="171">
+      <c r="H21" s="170">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="I21" s="171">
+      <c r="I21" s="170">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="J21" s="171">
+      <c r="J21" s="170">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
       <c r="S21" s="63"/>
     </row>
     <row r="22" spans="2:19">
-      <c r="B22" s="131" t="s">
+      <c r="B22" s="130" t="s">
         <v>93</v>
       </c>
       <c r="C22" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="168">
-        <f>H54+H56</f>
+      <c r="D22" s="158">
+        <f>H56+H58</f>
         <v>185.32583</v>
       </c>
-      <c r="E22" s="169">
+      <c r="E22" s="159">
         <f t="shared" si="1"/>
         <v>185.32583</v>
       </c>
-      <c r="F22" s="168">
+      <c r="F22" s="158">
         <f t="shared" si="1"/>
         <v>185.32583</v>
       </c>
-      <c r="G22" s="168">
+      <c r="G22" s="158">
         <f t="shared" si="1"/>
         <v>185.32583</v>
       </c>
-      <c r="H22" s="169">
+      <c r="H22" s="159">
         <f t="shared" si="1"/>
         <v>185.32583</v>
       </c>
-      <c r="I22" s="168">
+      <c r="I22" s="158">
         <f t="shared" si="1"/>
         <v>185.32583</v>
       </c>
-      <c r="J22" s="168">
+      <c r="J22" s="158">
         <f t="shared" si="1"/>
         <v>185.32583</v>
       </c>
       <c r="S22" s="63"/>
     </row>
     <row r="23" spans="2:19">
-      <c r="B23" s="130" t="s">
+      <c r="B23" s="167" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="170">
-        <f>H64</f>
+      <c r="D23" s="169">
+        <f>H66</f>
         <v>779.12891000000002</v>
       </c>
-      <c r="E23" s="171">
+      <c r="E23" s="170">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="F23" s="171">
+      <c r="F23" s="170">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="G23" s="171">
+      <c r="G23" s="170">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="H23" s="171">
+      <c r="H23" s="170">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="I23" s="171">
+      <c r="I23" s="170">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="J23" s="171">
+      <c r="J23" s="170">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
       <c r="S23" s="63"/>
     </row>
     <row r="24" spans="2:19">
-      <c r="B24" s="131" t="s">
+      <c r="B24" s="130" t="s">
         <v>95</v>
       </c>
       <c r="C24" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="168">
-        <f>H62</f>
+      <c r="D24" s="158">
+        <f>H64</f>
         <v>513.29357999999991</v>
       </c>
-      <c r="E24" s="169">
+      <c r="E24" s="159">
         <f t="shared" si="1"/>
         <v>513.29357999999991</v>
       </c>
-      <c r="F24" s="168">
+      <c r="F24" s="158">
         <f t="shared" si="1"/>
         <v>513.29357999999991</v>
       </c>
-      <c r="G24" s="168">
+      <c r="G24" s="158">
         <f t="shared" si="1"/>
         <v>513.29357999999991</v>
       </c>
-      <c r="H24" s="169">
+      <c r="H24" s="159">
         <f t="shared" si="1"/>
         <v>513.29357999999991</v>
       </c>
-      <c r="I24" s="168">
+      <c r="I24" s="158">
         <f t="shared" si="1"/>
         <v>513.29357999999991</v>
       </c>
-      <c r="J24" s="168">
+      <c r="J24" s="158">
         <f t="shared" si="1"/>
         <v>513.29357999999991</v>
       </c>
     </row>
     <row r="25" spans="2:19">
-      <c r="B25" s="130" t="s">
+      <c r="B25" s="167" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="170">
-        <f>H58</f>
+      <c r="D25" s="169">
+        <f>H60</f>
         <v>5923.7602000000006</v>
       </c>
-      <c r="E25" s="171">
+      <c r="E25" s="170">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="F25" s="171">
+      <c r="F25" s="170">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="G25" s="171">
+      <c r="G25" s="170">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="H25" s="171">
+      <c r="H25" s="170">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="I25" s="171">
+      <c r="I25" s="170">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="J25" s="171">
+      <c r="J25" s="170">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
     </row>
     <row r="26" spans="2:19">
-      <c r="B26" s="131" t="s">
+      <c r="B26" s="130" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="168">
-        <f>H60</f>
+      <c r="D26" s="158">
+        <f>H62</f>
         <v>3468.2807199999997</v>
       </c>
-      <c r="E26" s="169">
+      <c r="E26" s="159">
         <f t="shared" si="1"/>
         <v>3468.2807199999997</v>
       </c>
-      <c r="F26" s="168">
+      <c r="F26" s="158">
         <f t="shared" si="1"/>
         <v>3468.2807199999997</v>
       </c>
-      <c r="G26" s="168">
+      <c r="G26" s="158">
         <f t="shared" si="1"/>
         <v>3468.2807199999997</v>
       </c>
-      <c r="H26" s="169">
+      <c r="H26" s="159">
         <f t="shared" si="1"/>
         <v>3468.2807199999997</v>
       </c>
-      <c r="I26" s="168">
+      <c r="I26" s="158">
         <f t="shared" si="1"/>
         <v>3468.2807199999997</v>
       </c>
-      <c r="J26" s="168">
+      <c r="J26" s="158">
         <f t="shared" si="1"/>
         <v>3468.2807199999997</v>
       </c>
     </row>
     <row r="27" spans="2:19">
-      <c r="B27" s="130" t="s">
+      <c r="B27" s="167" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="170">
+      <c r="D27" s="169">
         <v>0</v>
       </c>
-      <c r="E27" s="171">
+      <c r="E27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F27" s="171">
+      <c r="F27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G27" s="171">
+      <c r="G27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H27" s="171">
+      <c r="H27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="171">
+      <c r="I27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="171">
+      <c r="J27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:19">
-      <c r="B28" s="131" t="s">
+      <c r="B28" s="130" t="s">
         <v>99</v>
       </c>
       <c r="C28" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="168">
+      <c r="D28" s="158">
         <v>0</v>
       </c>
-      <c r="E28" s="169">
+      <c r="E28" s="159">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="168">
+      <c r="F28" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="168">
+      <c r="G28" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H28" s="169">
+      <c r="H28" s="159">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="168">
+      <c r="I28" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="168">
+      <c r="J28" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11768,768 +11773,840 @@
       <c r="J29" s="69"/>
     </row>
     <row r="30" spans="2:19" ht="16.149999999999999" customHeight="1">
-      <c r="B30" s="151" t="s">
+      <c r="B30" s="150" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="144">
+      <c r="D30" s="143">
         <v>3</v>
       </c>
-      <c r="E30" s="144">
+      <c r="E30" s="143">
         <v>3</v>
       </c>
-      <c r="F30" s="144">
+      <c r="F30" s="143">
         <v>3</v>
       </c>
-      <c r="G30" s="144">
+      <c r="G30" s="143">
         <v>3</v>
       </c>
-      <c r="H30" s="144">
+      <c r="H30" s="143">
         <v>3</v>
       </c>
-      <c r="I30" s="144">
+      <c r="I30" s="143">
         <v>3</v>
       </c>
-      <c r="J30" s="144">
+      <c r="J30" s="143">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="16.149999999999999" customHeight="1"/>
-    <row r="32" spans="2:19" ht="16.149999999999999" customHeight="1"/>
-    <row r="33" spans="2:8" ht="16.149999999999999" customHeight="1" thickBot="1">
-      <c r="B33" s="72" t="s">
+    <row r="31" spans="2:19" ht="16.149999999999999" customHeight="1">
+      <c r="B31" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="69"/>
+      <c r="D31" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+    </row>
+    <row r="32" spans="2:19" ht="16.149999999999999" customHeight="1">
+      <c r="B32" s="167" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="168" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="167">
+        <v>10</v>
+      </c>
+      <c r="E32" s="167">
+        <v>10</v>
+      </c>
+      <c r="F32" s="167">
+        <v>10</v>
+      </c>
+      <c r="G32" s="167">
+        <v>10</v>
+      </c>
+      <c r="H32" s="167">
+        <v>10</v>
+      </c>
+      <c r="I32" s="167">
+        <v>10</v>
+      </c>
+      <c r="J32" s="167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="16.149999999999999" customHeight="1">
+      <c r="B33" s="130" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="130">
+        <v>5</v>
+      </c>
+      <c r="E33" s="70">
+        <v>5</v>
+      </c>
+      <c r="F33" s="130">
+        <v>5</v>
+      </c>
+      <c r="G33" s="70">
+        <v>5</v>
+      </c>
+      <c r="H33" s="130">
+        <v>5</v>
+      </c>
+      <c r="I33" s="70">
+        <v>5</v>
+      </c>
+      <c r="J33" s="130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="16.149999999999999" customHeight="1"/>
+    <row r="35" spans="2:10" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B35" s="72" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="105"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="107"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75">
-      <c r="B35" s="155" t="s">
+    <row r="36" spans="2:10">
+      <c r="B36" s="105"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="107"/>
+    </row>
+    <row r="37" spans="2:10" ht="15.75">
+      <c r="B37" s="160" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
-      <c r="F35" s="156"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="109" t="s">
+      <c r="C37" s="161"/>
+      <c r="D37" s="161"/>
+      <c r="E37" s="161"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="109" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="110"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="111"/>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="157" t="s">
+    <row r="38" spans="2:10">
+      <c r="B38" s="110"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="111"/>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="162" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="158" t="s">
+      <c r="C39" s="163" t="s">
         <v>103</v>
       </c>
-      <c r="D37" s="158" t="s">
+      <c r="D39" s="163" t="s">
         <v>104</v>
       </c>
-      <c r="E37" s="158" t="s">
+      <c r="E39" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108" t="s">
+      <c r="F39" s="108"/>
+      <c r="G39" s="108" t="s">
         <v>106</v>
       </c>
-      <c r="H37" s="111" t="s">
+      <c r="H39" s="111" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="13.7" customHeight="1">
-      <c r="B38" s="157"/>
-      <c r="C38" s="158"/>
-      <c r="D38" s="158"/>
-      <c r="E38" s="158"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162" t="s">
+    <row r="40" spans="2:10" ht="13.7" customHeight="1">
+      <c r="B40" s="162"/>
+      <c r="C40" s="163"/>
+      <c r="D40" s="163"/>
+      <c r="E40" s="163"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="H38" s="163" t="s">
+      <c r="H40" s="111" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="112" t="s">
+    <row r="41" spans="2:10">
+      <c r="B41" s="112" t="s">
         <v>107</v>
-      </c>
-      <c r="C39" s="108"/>
-      <c r="D39" s="108"/>
-      <c r="E39" s="108"/>
-      <c r="F39" s="108"/>
-      <c r="G39" s="108"/>
-      <c r="H39" s="111"/>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="110" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="113">
-        <v>2385.6930000000002</v>
-      </c>
-      <c r="D40" s="108">
-        <v>52</v>
-      </c>
-      <c r="E40" s="114">
-        <v>124145899</v>
-      </c>
-      <c r="F40" s="108"/>
-      <c r="G40" s="108">
-        <f>D40/10</f>
-        <v>5.2</v>
-      </c>
-      <c r="H40" s="165">
-        <f>G40*C40</f>
-        <v>12405.603600000002</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="112" t="s">
-        <v>109</v>
       </c>
       <c r="C41" s="108"/>
       <c r="D41" s="108"/>
       <c r="E41" s="108"/>
       <c r="F41" s="108"/>
       <c r="G41" s="108"/>
-      <c r="H41" s="165"/>
-    </row>
-    <row r="42" spans="2:8">
+      <c r="H41" s="111"/>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" s="110" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="108">
-        <v>682.18100000000004</v>
+        <v>108</v>
+      </c>
+      <c r="C42" s="113">
+        <v>2385.6930000000002</v>
       </c>
       <c r="D42" s="108">
-        <v>35.700000000000003</v>
+        <v>52</v>
       </c>
       <c r="E42" s="114">
-        <v>24385526</v>
+        <v>124145899</v>
       </c>
       <c r="F42" s="108"/>
       <c r="G42" s="108">
-        <f t="shared" ref="G41:G64" si="2">D42/10</f>
-        <v>3.5700000000000003</v>
-      </c>
-      <c r="H42" s="165">
-        <f t="shared" ref="H41:H64" si="3">G42*C42</f>
-        <v>2435.3861700000002</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
+        <f>D42/10</f>
+        <v>5.2</v>
+      </c>
+      <c r="H42" s="155">
+        <f>G42*C42</f>
+        <v>12405.603600000002</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43" s="112" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C43" s="108"/>
       <c r="D43" s="108"/>
       <c r="E43" s="108"/>
       <c r="F43" s="108"/>
       <c r="G43" s="108"/>
-      <c r="H43" s="165"/>
-    </row>
-    <row r="44" spans="2:8">
+      <c r="H43" s="155"/>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" s="110" t="s">
         <v>110</v>
       </c>
       <c r="C44" s="108">
-        <v>695.31399999999996</v>
+        <v>682.18100000000004</v>
       </c>
       <c r="D44" s="108">
-        <v>43.4</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="E44" s="114">
-        <v>30161612</v>
+        <v>24385526</v>
       </c>
       <c r="F44" s="108"/>
       <c r="G44" s="108">
-        <f t="shared" si="2"/>
-        <v>4.34</v>
-      </c>
-      <c r="H44" s="165">
-        <f t="shared" si="3"/>
-        <v>3017.6627599999997</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
+        <f t="shared" ref="G44:G66" si="2">D44/10</f>
+        <v>3.5700000000000003</v>
+      </c>
+      <c r="H44" s="155">
+        <f t="shared" ref="H44:H66" si="3">G44*C44</f>
+        <v>2435.3861700000002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45" s="112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C45" s="108"/>
       <c r="D45" s="108"/>
       <c r="E45" s="108"/>
       <c r="F45" s="108"/>
       <c r="G45" s="108"/>
-      <c r="H45" s="165"/>
-    </row>
-    <row r="46" spans="2:8">
+      <c r="H45" s="155"/>
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46" s="110" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C46" s="108">
-        <v>519.00300000000004</v>
+        <v>695.31399999999996</v>
       </c>
       <c r="D46" s="108">
-        <v>31.7</v>
+        <v>43.4</v>
       </c>
       <c r="E46" s="114">
-        <v>16475645</v>
+        <v>30161612</v>
       </c>
       <c r="F46" s="108"/>
       <c r="G46" s="108">
         <f t="shared" si="2"/>
-        <v>3.17</v>
-      </c>
-      <c r="H46" s="165">
+        <v>4.34</v>
+      </c>
+      <c r="H46" s="155">
         <f t="shared" si="3"/>
-        <v>1645.2395100000001</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
+        <v>3017.6627599999997</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47" s="112" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C47" s="108"/>
       <c r="D47" s="108"/>
       <c r="E47" s="108"/>
       <c r="F47" s="108"/>
       <c r="G47" s="108"/>
-      <c r="H47" s="165"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="H47" s="155"/>
+    </row>
+    <row r="48" spans="2:10">
       <c r="B48" s="110" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="113">
-        <v>1147.0340000000001</v>
+        <v>108</v>
+      </c>
+      <c r="C48" s="108">
+        <v>519.00300000000004</v>
       </c>
       <c r="D48" s="108">
-        <v>44</v>
+        <v>31.7</v>
       </c>
       <c r="E48" s="114">
-        <v>50521954</v>
+        <v>16475645</v>
       </c>
       <c r="F48" s="108"/>
       <c r="G48" s="108">
         <f t="shared" si="2"/>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H48" s="165">
+        <v>3.17</v>
+      </c>
+      <c r="H48" s="155">
         <f t="shared" si="3"/>
-        <v>5046.9496000000008</v>
+        <v>1645.2395100000001</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="112" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C49" s="108"/>
       <c r="D49" s="108"/>
       <c r="E49" s="108"/>
       <c r="F49" s="108"/>
       <c r="G49" s="108"/>
-      <c r="H49" s="165"/>
+      <c r="H49" s="155"/>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="108">
-        <v>252.4</v>
+      <c r="C50" s="113">
+        <v>1147.0340000000001</v>
       </c>
       <c r="D50" s="108">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E50" s="114">
-        <v>8334447</v>
+        <v>50521954</v>
       </c>
       <c r="F50" s="108"/>
       <c r="G50" s="108">
         <f t="shared" si="2"/>
-        <v>3.3</v>
-      </c>
-      <c r="H50" s="165">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H50" s="155">
         <f t="shared" si="3"/>
-        <v>832.92</v>
+        <v>5046.9496000000008</v>
       </c>
     </row>
     <row r="51" spans="2:8">
       <c r="B51" s="112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" s="108"/>
       <c r="D51" s="108"/>
       <c r="E51" s="108"/>
       <c r="F51" s="108"/>
       <c r="G51" s="108"/>
-      <c r="H51" s="165"/>
-    </row>
-    <row r="52" spans="2:8" ht="15">
+      <c r="H51" s="155"/>
+    </row>
+    <row r="52" spans="2:8">
       <c r="B52" s="110" t="s">
         <v>110</v>
       </c>
       <c r="C52" s="108">
-        <v>1276.7270000000001</v>
+        <v>252.4</v>
       </c>
       <c r="D52" s="108">
-        <v>73.599999999999994</v>
+        <v>33</v>
       </c>
       <c r="E52" s="114">
-        <v>93980760</v>
-      </c>
-      <c r="F52" s="115"/>
+        <v>8334447</v>
+      </c>
+      <c r="F52" s="108"/>
       <c r="G52" s="108">
         <f t="shared" si="2"/>
-        <v>7.3599999999999994</v>
-      </c>
-      <c r="H52" s="165">
+        <v>3.3</v>
+      </c>
+      <c r="H52" s="155">
         <f t="shared" si="3"/>
-        <v>9396.7107199999991</v>
+        <v>832.92</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" s="112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C53" s="108"/>
       <c r="D53" s="108"/>
       <c r="E53" s="108"/>
       <c r="F53" s="108"/>
       <c r="G53" s="108"/>
-      <c r="H53" s="165"/>
-    </row>
-    <row r="54" spans="2:8">
+      <c r="H53" s="155"/>
+    </row>
+    <row r="54" spans="2:8" ht="15">
       <c r="B54" s="110" t="s">
         <v>110</v>
       </c>
       <c r="C54" s="108">
-        <v>93.600999999999999</v>
+        <v>1276.7270000000001</v>
       </c>
       <c r="D54" s="108">
-        <v>15.2</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="E54" s="114">
-        <v>1422008</v>
-      </c>
-      <c r="F54" s="108"/>
+        <v>93980760</v>
+      </c>
+      <c r="F54" s="115"/>
       <c r="G54" s="108">
         <f t="shared" si="2"/>
-        <v>1.52</v>
-      </c>
-      <c r="H54" s="165">
+        <v>7.3599999999999994</v>
+      </c>
+      <c r="H54" s="155">
         <f t="shared" si="3"/>
-        <v>142.27351999999999</v>
+        <v>9396.7107199999991</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" s="112" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C55" s="108"/>
       <c r="D55" s="108"/>
       <c r="E55" s="108"/>
       <c r="F55" s="108"/>
       <c r="G55" s="108"/>
-      <c r="H55" s="165"/>
+      <c r="H55" s="155"/>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" s="110" t="s">
         <v>110</v>
       </c>
       <c r="C56" s="108">
-        <v>22.779</v>
+        <v>93.600999999999999</v>
       </c>
       <c r="D56" s="108">
-        <v>18.899999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="E56" s="114">
-        <v>431612</v>
+        <v>1422008</v>
       </c>
       <c r="F56" s="108"/>
       <c r="G56" s="108">
         <f t="shared" si="2"/>
-        <v>1.89</v>
-      </c>
-      <c r="H56" s="165">
+        <v>1.52</v>
+      </c>
+      <c r="H56" s="155">
         <f t="shared" si="3"/>
-        <v>43.052309999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" ht="14.25">
+        <v>142.27351999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
       <c r="B57" s="112" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C57" s="108"/>
       <c r="D57" s="108"/>
       <c r="E57" s="108"/>
       <c r="F57" s="108"/>
       <c r="G57" s="108"/>
-      <c r="H57" s="165"/>
+      <c r="H57" s="155"/>
     </row>
     <row r="58" spans="2:8">
-      <c r="B58" s="116" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" s="117">
-        <v>196.15100000000001</v>
-      </c>
-      <c r="D58" s="118">
-        <v>302</v>
-      </c>
-      <c r="E58" s="119">
-        <v>59201683</v>
-      </c>
-      <c r="F58" s="118"/>
+      <c r="B58" s="110" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="108">
+        <v>22.779</v>
+      </c>
+      <c r="D58" s="108">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E58" s="114">
+        <v>431612</v>
+      </c>
+      <c r="F58" s="108"/>
       <c r="G58" s="108">
         <f t="shared" si="2"/>
-        <v>30.2</v>
-      </c>
-      <c r="H58" s="165">
+        <v>1.89</v>
+      </c>
+      <c r="H58" s="155">
         <f t="shared" si="3"/>
-        <v>5923.7602000000006</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
+        <v>43.052309999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="14.25">
       <c r="B59" s="112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C59" s="108"/>
       <c r="D59" s="108"/>
       <c r="E59" s="108"/>
       <c r="F59" s="108"/>
       <c r="G59" s="108"/>
-      <c r="H59" s="165"/>
+      <c r="H59" s="155"/>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="110" t="s">
-        <v>110</v>
-      </c>
-      <c r="C60" s="113">
-        <v>1104.548</v>
-      </c>
-      <c r="D60" s="108">
-        <v>31.4</v>
-      </c>
-      <c r="E60" s="114">
-        <v>34713263</v>
-      </c>
-      <c r="F60" s="108"/>
+      <c r="B60" s="116" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="117">
+        <v>196.15100000000001</v>
+      </c>
+      <c r="D60" s="118">
+        <v>302</v>
+      </c>
+      <c r="E60" s="119">
+        <v>59201683</v>
+      </c>
+      <c r="F60" s="118"/>
       <c r="G60" s="108">
         <f t="shared" si="2"/>
+        <v>30.2</v>
+      </c>
+      <c r="H60" s="155">
+        <f t="shared" si="3"/>
+        <v>5923.7602000000006</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="B61" s="112" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="108"/>
+      <c r="D61" s="108"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="108"/>
+      <c r="G61" s="108"/>
+      <c r="H61" s="155"/>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" s="110" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="113">
+        <v>1104.548</v>
+      </c>
+      <c r="D62" s="108">
+        <v>31.4</v>
+      </c>
+      <c r="E62" s="114">
+        <v>34713263</v>
+      </c>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108">
+        <f t="shared" si="2"/>
         <v>3.1399999999999997</v>
       </c>
-      <c r="H60" s="165">
+      <c r="H62" s="155">
         <f t="shared" si="3"/>
         <v>3468.2807199999997</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="120" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="121"/>
-      <c r="D61" s="121"/>
-      <c r="E61" s="121"/>
-      <c r="F61" s="121"/>
-      <c r="G61" s="108"/>
-      <c r="H61" s="165"/>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="122" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" s="121">
-        <v>206.142</v>
-      </c>
-      <c r="D62" s="121">
-        <v>24.9</v>
-      </c>
-      <c r="E62" s="123">
-        <v>5138244</v>
-      </c>
-      <c r="F62" s="121"/>
-      <c r="G62" s="108">
-        <f t="shared" si="2"/>
-        <v>2.4899999999999998</v>
-      </c>
-      <c r="H62" s="165">
-        <f t="shared" si="3"/>
-        <v>513.29357999999991</v>
-      </c>
-    </row>
     <row r="63" spans="2:8">
       <c r="B63" s="120" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63" s="121"/>
       <c r="D63" s="121"/>
       <c r="E63" s="121"/>
       <c r="F63" s="121"/>
       <c r="G63" s="108"/>
-      <c r="H63" s="165"/>
-    </row>
-    <row r="64" spans="2:8" ht="13.5" thickBot="1">
-      <c r="B64" s="124" t="s">
+      <c r="H63" s="155"/>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" s="122" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="121">
+        <v>206.142</v>
+      </c>
+      <c r="D64" s="121">
+        <v>24.9</v>
+      </c>
+      <c r="E64" s="123">
+        <v>5138244</v>
+      </c>
+      <c r="F64" s="121"/>
+      <c r="G64" s="108">
+        <f t="shared" si="2"/>
+        <v>2.4899999999999998</v>
+      </c>
+      <c r="H64" s="155">
+        <f t="shared" si="3"/>
+        <v>513.29357999999991</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="120" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="121"/>
+      <c r="D65" s="121"/>
+      <c r="E65" s="121"/>
+      <c r="F65" s="121"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="155"/>
+    </row>
+    <row r="66" spans="2:9" ht="13.5" thickBot="1">
+      <c r="B66" s="124" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="125">
+      <c r="C66" s="125">
         <v>43.308999999999997</v>
       </c>
-      <c r="D64" s="125">
+      <c r="D66" s="125">
         <v>179.9</v>
       </c>
-      <c r="E64" s="126">
+      <c r="E66" s="126">
         <v>7791301</v>
       </c>
-      <c r="F64" s="127"/>
-      <c r="G64" s="164">
+      <c r="F66" s="127"/>
+      <c r="G66" s="154">
         <f t="shared" si="2"/>
         <v>17.990000000000002</v>
       </c>
-      <c r="H64" s="166">
+      <c r="H66" s="156">
         <f t="shared" si="3"/>
         <v>779.12891000000002</v>
       </c>
     </row>
-    <row r="68" spans="2:9" ht="13.5" thickBot="1">
-      <c r="B68" s="72" t="s">
+    <row r="70" spans="2:9" ht="13.5" thickBot="1">
+      <c r="B70" s="72" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="15.75">
-      <c r="B69" s="73" t="s">
+    <row r="71" spans="2:9" ht="15.75">
+      <c r="B71" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="C69" s="74"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="74"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="75" t="s">
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="H69" s="76"/>
-      <c r="I69" s="77"/>
-    </row>
-    <row r="70" spans="2:9">
-      <c r="B70" s="78"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="79"/>
-      <c r="I70" s="80"/>
-    </row>
-    <row r="71" spans="2:9">
-      <c r="B71" s="81" t="s">
+      <c r="H71" s="76"/>
+      <c r="I71" s="77"/>
+    </row>
+    <row r="72" spans="2:9">
+      <c r="B72" s="78"/>
+      <c r="C72" s="79"/>
+      <c r="D72" s="79"/>
+      <c r="E72" s="79"/>
+      <c r="F72" s="79"/>
+      <c r="G72" s="79"/>
+      <c r="H72" s="79"/>
+      <c r="I72" s="80"/>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="B73" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="C71" s="82"/>
-      <c r="D71" s="82"/>
-      <c r="E71" s="82"/>
-      <c r="F71" s="82"/>
-      <c r="G71" s="82"/>
-      <c r="H71" s="82"/>
-      <c r="I71" s="83"/>
-    </row>
-    <row r="72" spans="2:9">
-      <c r="B72" s="84"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="85"/>
-      <c r="E72" s="85"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="85"/>
-      <c r="H72" s="85"/>
-      <c r="I72" s="86"/>
-    </row>
-    <row r="73" spans="2:9">
-      <c r="B73" s="87" t="s">
+      <c r="C73" s="82"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="82"/>
+      <c r="F73" s="82"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
+      <c r="I73" s="83"/>
+    </row>
+    <row r="74" spans="2:9">
+      <c r="B74" s="84"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="85"/>
+      <c r="E74" s="85"/>
+      <c r="F74" s="85"/>
+      <c r="G74" s="85"/>
+      <c r="H74" s="85"/>
+      <c r="I74" s="86"/>
+    </row>
+    <row r="75" spans="2:9">
+      <c r="B75" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="C73" s="88" t="s">
+      <c r="C75" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="D73" s="88"/>
-      <c r="E73" s="88" t="s">
+      <c r="D75" s="88"/>
+      <c r="E75" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="F73" s="88"/>
-      <c r="G73" s="88" t="s">
+      <c r="F75" s="88"/>
+      <c r="G75" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="H73" s="89" t="s">
+      <c r="H75" s="89" t="s">
         <v>129</v>
       </c>
-      <c r="I73" s="90" t="s">
+      <c r="I75" s="90" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="74" spans="2:9">
-      <c r="B74" s="87"/>
-      <c r="C74" s="88" t="s">
+    <row r="76" spans="2:9">
+      <c r="B76" s="87"/>
+      <c r="C76" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="D74" s="89" t="s">
+      <c r="D76" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="E74" s="88" t="s">
+      <c r="E76" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="F74" s="89" t="s">
+      <c r="F76" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="G74" s="88"/>
-      <c r="H74" s="89"/>
-      <c r="I74" s="90"/>
-    </row>
-    <row r="75" spans="2:9">
-      <c r="B75" s="87"/>
-      <c r="C75" s="88" t="s">
+      <c r="G76" s="88"/>
+      <c r="H76" s="89"/>
+      <c r="I76" s="90"/>
+    </row>
+    <row r="77" spans="2:9">
+      <c r="B77" s="87"/>
+      <c r="C77" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="D75" s="88"/>
-      <c r="E75" s="88"/>
-      <c r="F75" s="88"/>
-      <c r="G75" s="88"/>
-      <c r="H75" s="88"/>
-      <c r="I75" s="91" t="s">
+      <c r="D77" s="88"/>
+      <c r="E77" s="88"/>
+      <c r="F77" s="88"/>
+      <c r="G77" s="88"/>
+      <c r="H77" s="88"/>
+      <c r="I77" s="91" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="76" spans="2:9" ht="13.5" thickBot="1">
-      <c r="B76" s="92" t="s">
+    <row r="78" spans="2:9" ht="13.5" thickBot="1">
+      <c r="B78" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="C76" s="93">
+      <c r="C78" s="93">
         <v>6190927</v>
       </c>
-      <c r="D76" s="93">
+      <c r="D78" s="93">
         <v>2101159</v>
       </c>
-      <c r="E76" s="93">
+      <c r="E78" s="93">
         <v>9078250</v>
       </c>
-      <c r="F76" s="93">
+      <c r="F78" s="93">
         <v>599707</v>
       </c>
-      <c r="G76" s="93">
+      <c r="G78" s="93">
         <v>269538</v>
       </c>
-      <c r="H76" s="93">
+      <c r="H78" s="93">
         <v>244679548</v>
       </c>
-      <c r="I76" s="94">
+      <c r="I78" s="94">
         <v>64180</v>
       </c>
     </row>
-    <row r="77" spans="2:9">
-      <c r="B77" s="95" t="s">
+    <row r="79" spans="2:9">
+      <c r="B79" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="C77" s="96"/>
-      <c r="D77" s="96"/>
-      <c r="E77" s="96"/>
-      <c r="F77" s="96"/>
-      <c r="G77" s="97"/>
-      <c r="H77" s="98"/>
-      <c r="I77" s="99"/>
-    </row>
-    <row r="78" spans="2:9">
-      <c r="B78" s="87" t="s">
+      <c r="C79" s="96"/>
+      <c r="D79" s="96"/>
+      <c r="E79" s="96"/>
+      <c r="F79" s="96"/>
+      <c r="G79" s="97"/>
+      <c r="H79" s="98"/>
+      <c r="I79" s="99"/>
+    </row>
+    <row r="80" spans="2:9">
+      <c r="B80" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="C78" s="88" t="s">
+      <c r="C80" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="D78" s="88"/>
-      <c r="E78" s="88" t="s">
+      <c r="D80" s="88"/>
+      <c r="E80" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="F78" s="88"/>
-      <c r="I78" s="100"/>
-    </row>
-    <row r="79" spans="2:9">
-      <c r="B79" s="87"/>
-      <c r="C79" s="88" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="88"/>
-      <c r="E79" s="88"/>
-      <c r="F79" s="88"/>
-      <c r="I79" s="100"/>
-    </row>
-    <row r="80" spans="2:9">
-      <c r="B80" s="87"/>
-      <c r="C80" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="D80" s="88" t="s">
-        <v>143</v>
-      </c>
-      <c r="E80" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="F80" s="88" t="s">
-        <v>143</v>
-      </c>
+      <c r="F80" s="88"/>
       <c r="I80" s="100"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="87"/>
       <c r="C81" s="88" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D81" s="88"/>
       <c r="E81" s="88"/>
       <c r="F81" s="88"/>
       <c r="I81" s="100"/>
     </row>
-    <row r="82" spans="2:9" ht="13.5" thickBot="1">
-      <c r="B82" s="101" t="s">
+    <row r="82" spans="2:9">
+      <c r="B82" s="87"/>
+      <c r="C82" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="D82" s="88" t="s">
+        <v>143</v>
+      </c>
+      <c r="E82" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="F82" s="88" t="s">
+        <v>143</v>
+      </c>
+      <c r="I82" s="100"/>
+    </row>
+    <row r="83" spans="2:9">
+      <c r="B83" s="87"/>
+      <c r="C83" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="D83" s="88"/>
+      <c r="E83" s="88"/>
+      <c r="F83" s="88"/>
+      <c r="I83" s="100"/>
+    </row>
+    <row r="84" spans="2:9" ht="13.5" thickBot="1">
+      <c r="B84" s="101" t="s">
         <v>144</v>
       </c>
-      <c r="C82" s="102">
+      <c r="C84" s="102">
         <v>214987216</v>
       </c>
-      <c r="D82" s="102">
+      <c r="D84" s="102">
         <v>268862574</v>
       </c>
-      <c r="E82" s="102">
+      <c r="E84" s="102">
         <v>185713737</v>
       </c>
-      <c r="F82" s="102">
+      <c r="F84" s="102">
         <v>244679548</v>
       </c>
-      <c r="G82" s="103"/>
-      <c r="H82" s="103"/>
-      <c r="I82" s="104"/>
+      <c r="G84" s="103"/>
+      <c r="H84" s="103"/>
+      <c r="I84" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12538,12 +12615,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12790,20 +12869,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12828,18 +12914,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/VT_Model_DMD.xlsx
+++ b/VT_Model_DMD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\1. 2026\2. AGR_model_wyizolowany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D46D7F7-A5FF-4C40-9055-9331D947E2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5890,29 +5890,29 @@
     <xf numFmtId="4" fontId="14" fillId="4" borderId="0" xfId="19" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="5" borderId="0" xfId="19" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="19" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="3" borderId="0" xfId="14" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2193">
     <cellStyle name="20 % - Akzent1 2" xfId="67" xr:uid="{0BDC621E-8D3A-42DB-9E36-DCD3236A3B37}"/>
@@ -9417,15 +9417,15 @@
       <c r="A14" s="52"/>
       <c r="B14" s="47"/>
       <c r="C14" s="42"/>
-      <c r="D14" s="164" t="s">
+      <c r="D14" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="164"/>
-      <c r="F14" s="165" t="s">
+      <c r="E14" s="168"/>
+      <c r="F14" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="165"/>
+      <c r="G14" s="169"/>
+      <c r="H14" s="169"/>
       <c r="J14" s="41"/>
       <c r="K14" s="43"/>
       <c r="L14" s="52"/>
@@ -9436,9 +9436,9 @@
       <c r="C15" s="42"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
-      <c r="F15" s="165"/>
-      <c r="G15" s="165"/>
-      <c r="H15" s="165"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="169"/>
+      <c r="H15" s="169"/>
       <c r="J15" s="41"/>
       <c r="K15" s="43"/>
       <c r="L15" s="52"/>
@@ -9463,16 +9463,16 @@
       <c r="A18" s="52"/>
       <c r="B18" s="47"/>
       <c r="C18" s="42"/>
-      <c r="D18" s="164" t="s">
+      <c r="D18" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="164"/>
-      <c r="F18" s="165" t="s">
+      <c r="E18" s="168"/>
+      <c r="F18" s="169" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="165"/>
-      <c r="H18" s="165"/>
-      <c r="I18" s="165"/>
+      <c r="G18" s="169"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="169"/>
       <c r="J18" s="41"/>
       <c r="K18" s="43"/>
       <c r="L18" s="52"/>
@@ -9483,10 +9483,10 @@
       <c r="C19" s="42"/>
       <c r="D19" s="39"/>
       <c r="E19" s="39"/>
-      <c r="F19" s="165"/>
-      <c r="G19" s="165"/>
-      <c r="H19" s="165"/>
-      <c r="I19" s="165"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="169"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="169"/>
       <c r="J19" s="41"/>
       <c r="K19" s="43"/>
       <c r="L19" s="52"/>
@@ -9497,10 +9497,10 @@
       <c r="C20" s="42"/>
       <c r="D20" s="39"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
-      <c r="H20" s="165"/>
-      <c r="I20" s="165"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="169"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="169"/>
       <c r="J20" s="41"/>
       <c r="K20" s="43"/>
       <c r="L20" s="52"/>
@@ -9520,10 +9520,10 @@
       <c r="A22" s="52"/>
       <c r="B22" s="47"/>
       <c r="C22" s="42"/>
-      <c r="D22" s="164" t="s">
+      <c r="D22" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="164"/>
+      <c r="E22" s="168"/>
       <c r="F22" s="37">
         <v>45173</v>
       </c>
@@ -9601,10 +9601,10 @@
       <c r="A28" s="52"/>
       <c r="B28" s="47"/>
       <c r="C28" s="42"/>
-      <c r="D28" s="164" t="s">
+      <c r="D28" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="164"/>
+      <c r="E28" s="168"/>
       <c r="F28" s="51" t="s">
         <v>7</v>
       </c>
@@ -9643,10 +9643,10 @@
       <c r="A32" s="52"/>
       <c r="B32" s="47"/>
       <c r="C32" s="42"/>
-      <c r="D32" s="164" t="s">
+      <c r="D32" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="164"/>
+      <c r="E32" s="168"/>
       <c r="F32" s="51" t="s">
         <v>7</v>
       </c>
@@ -9810,11 +9810,11 @@
       <c r="A4" s="52"/>
       <c r="B4" s="47"/>
       <c r="C4" s="42"/>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
+      <c r="E4" s="170"/>
+      <c r="F4" s="170"/>
       <c r="G4" s="41"/>
       <c r="H4" s="43"/>
       <c r="I4" s="52"/>
@@ -11092,13 +11092,13 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B10" s="167" t="s">
+      <c r="B10" s="160" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="168" t="s">
+      <c r="C10" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="168">
+      <c r="D10" s="161">
         <f>G78/1000</f>
         <v>269.53800000000001</v>
       </c>
@@ -11164,13 +11164,13 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="B12" s="167" t="s">
+      <c r="B12" s="160" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="168" t="s">
+      <c r="C12" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="168">
+      <c r="D12" s="161">
         <f>I78/1000</f>
         <v>64.180000000000007</v>
       </c>
@@ -11323,37 +11323,37 @@
       </c>
     </row>
     <row r="17" spans="2:19">
-      <c r="B17" s="167" t="s">
+      <c r="B17" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="168" t="s">
+      <c r="C17" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="169">
+      <c r="D17" s="162">
         <f>H54</f>
         <v>9396.7107199999991</v>
       </c>
-      <c r="E17" s="170">
+      <c r="E17" s="163">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="F17" s="170">
+      <c r="F17" s="163">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="G17" s="170">
+      <c r="G17" s="163">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="H17" s="170">
+      <c r="H17" s="163">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="I17" s="170">
+      <c r="I17" s="163">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
-      <c r="J17" s="170">
+      <c r="J17" s="163">
         <f t="shared" si="1"/>
         <v>9396.7107199999991</v>
       </c>
@@ -11395,37 +11395,37 @@
       </c>
     </row>
     <row r="19" spans="2:19">
-      <c r="B19" s="167" t="s">
+      <c r="B19" s="160" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="168" t="s">
+      <c r="C19" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="169">
+      <c r="D19" s="162">
         <f>H50</f>
         <v>5046.9496000000008</v>
       </c>
-      <c r="E19" s="170">
+      <c r="E19" s="163">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="F19" s="170">
+      <c r="F19" s="163">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="G19" s="170">
+      <c r="G19" s="163">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="H19" s="170">
+      <c r="H19" s="163">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="I19" s="170">
+      <c r="I19" s="163">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
-      <c r="J19" s="170">
+      <c r="J19" s="163">
         <f t="shared" si="1"/>
         <v>5046.9496000000008</v>
       </c>
@@ -11469,37 +11469,37 @@
       <c r="S20" s="63"/>
     </row>
     <row r="21" spans="2:19">
-      <c r="B21" s="167" t="s">
+      <c r="B21" s="160" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="168" t="s">
+      <c r="C21" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="169">
+      <c r="D21" s="162">
         <f>H44</f>
         <v>2435.3861700000002</v>
       </c>
-      <c r="E21" s="170">
+      <c r="E21" s="163">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="F21" s="170">
+      <c r="F21" s="163">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="G21" s="170">
+      <c r="G21" s="163">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="H21" s="170">
+      <c r="H21" s="163">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="I21" s="170">
+      <c r="I21" s="163">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
-      <c r="J21" s="170">
+      <c r="J21" s="163">
         <f t="shared" si="1"/>
         <v>2435.3861700000002</v>
       </c>
@@ -11543,37 +11543,37 @@
       <c r="S22" s="63"/>
     </row>
     <row r="23" spans="2:19">
-      <c r="B23" s="167" t="s">
+      <c r="B23" s="160" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="168" t="s">
+      <c r="C23" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="169">
+      <c r="D23" s="162">
         <f>H66</f>
         <v>779.12891000000002</v>
       </c>
-      <c r="E23" s="170">
+      <c r="E23" s="163">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="F23" s="170">
+      <c r="F23" s="163">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="G23" s="170">
+      <c r="G23" s="163">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="H23" s="170">
+      <c r="H23" s="163">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="I23" s="170">
+      <c r="I23" s="163">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
-      <c r="J23" s="170">
+      <c r="J23" s="163">
         <f t="shared" si="1"/>
         <v>779.12891000000002</v>
       </c>
@@ -11616,37 +11616,37 @@
       </c>
     </row>
     <row r="25" spans="2:19">
-      <c r="B25" s="167" t="s">
+      <c r="B25" s="160" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="168" t="s">
+      <c r="C25" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="169">
+      <c r="D25" s="162">
         <f>H60</f>
         <v>5923.7602000000006</v>
       </c>
-      <c r="E25" s="170">
+      <c r="E25" s="163">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="F25" s="170">
+      <c r="F25" s="163">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="G25" s="170">
+      <c r="G25" s="163">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="H25" s="170">
+      <c r="H25" s="163">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="I25" s="170">
+      <c r="I25" s="163">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
-      <c r="J25" s="170">
+      <c r="J25" s="163">
         <f t="shared" si="1"/>
         <v>5923.7602000000006</v>
       </c>
@@ -11688,36 +11688,36 @@
       </c>
     </row>
     <row r="27" spans="2:19">
-      <c r="B27" s="167" t="s">
+      <c r="B27" s="160" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="168" t="s">
+      <c r="C27" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="169">
+      <c r="D27" s="162">
         <v>0</v>
       </c>
-      <c r="E27" s="170">
+      <c r="E27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F27" s="170">
+      <c r="F27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G27" s="170">
+      <c r="G27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H27" s="170">
+      <c r="H27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="170">
+      <c r="I27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="170">
+      <c r="J27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11817,32 +11817,32 @@
       <c r="J31" s="69"/>
     </row>
     <row r="32" spans="2:19" ht="16.149999999999999" customHeight="1">
-      <c r="B32" s="167" t="s">
+      <c r="B32" s="160" t="s">
         <v>187</v>
       </c>
-      <c r="C32" s="168" t="s">
+      <c r="C32" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="167">
-        <v>10</v>
-      </c>
-      <c r="E32" s="167">
-        <v>10</v>
-      </c>
-      <c r="F32" s="167">
-        <v>10</v>
-      </c>
-      <c r="G32" s="167">
-        <v>10</v>
-      </c>
-      <c r="H32" s="167">
-        <v>10</v>
-      </c>
-      <c r="I32" s="167">
-        <v>10</v>
-      </c>
-      <c r="J32" s="167">
-        <v>10</v>
+      <c r="D32" s="160">
+        <v>3</v>
+      </c>
+      <c r="E32" s="160">
+        <v>3</v>
+      </c>
+      <c r="F32" s="160">
+        <v>3</v>
+      </c>
+      <c r="G32" s="160">
+        <v>3</v>
+      </c>
+      <c r="H32" s="160">
+        <v>3</v>
+      </c>
+      <c r="I32" s="160">
+        <v>3</v>
+      </c>
+      <c r="J32" s="160">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="16.149999999999999" customHeight="1">
@@ -11853,25 +11853,25 @@
         <v>31</v>
       </c>
       <c r="D33" s="130">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" s="70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F33" s="130">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G33" s="70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H33" s="130">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I33" s="70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J33" s="130">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="16.149999999999999" customHeight="1"/>
@@ -11890,13 +11890,13 @@
       <c r="H36" s="107"/>
     </row>
     <row r="37" spans="2:10" ht="15.75">
-      <c r="B37" s="160" t="s">
+      <c r="B37" s="164" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="161"/>
-      <c r="D37" s="161"/>
-      <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
+      <c r="C37" s="165"/>
+      <c r="D37" s="165"/>
+      <c r="E37" s="165"/>
+      <c r="F37" s="165"/>
       <c r="G37" s="108"/>
       <c r="H37" s="109" t="s">
         <v>101</v>
@@ -11912,16 +11912,16 @@
       <c r="H38" s="111"/>
     </row>
     <row r="39" spans="2:10">
-      <c r="B39" s="162" t="s">
+      <c r="B39" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="163" t="s">
+      <c r="C39" s="167" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="163" t="s">
+      <c r="D39" s="167" t="s">
         <v>104</v>
       </c>
-      <c r="E39" s="163" t="s">
+      <c r="E39" s="167" t="s">
         <v>105</v>
       </c>
       <c r="F39" s="108"/>
@@ -11933,10 +11933,10 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="13.7" customHeight="1">
-      <c r="B40" s="162"/>
-      <c r="C40" s="163"/>
-      <c r="D40" s="163"/>
-      <c r="E40" s="163"/>
+      <c r="B40" s="166"/>
+      <c r="C40" s="167"/>
+      <c r="D40" s="167"/>
+      <c r="E40" s="167"/>
       <c r="F40" s="108"/>
       <c r="G40" s="108" t="s">
         <v>184</v>
@@ -12615,14 +12615,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12869,27 +12867,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12914,9 +12905,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/VT_Model_DMD.xlsx
+++ b/VT_Model_DMD.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr showObjects="placeholders" codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1072" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8302B44-54B7-4675-A980-0A9BCEC895F4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="151" r:id="rId1"/>
@@ -5964,7 +5964,7 @@
       <alignment horizontal="right"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6214,25 +6214,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="14" fillId="3" borderId="0" xfId="14" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="16" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="140" fillId="55" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6258,30 +6239,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="14" applyFont="1"/>
-    <xf numFmtId="0" fontId="143" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="14" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="59" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="60" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="61" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="14" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="14" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="14" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="143" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="59" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="60" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="61" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="16" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13387,9 +13386,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>331359</xdr:colOff>
+      <xdr:colOff>327549</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>97213</xdr:rowOff>
+      <xdr:rowOff>93403</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -13475,9 +13474,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>300830</xdr:colOff>
+      <xdr:colOff>298925</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>156324</xdr:rowOff>
+      <xdr:rowOff>158229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -13519,9 +13518,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>64</xdr:col>
-      <xdr:colOff>481788</xdr:colOff>
+      <xdr:colOff>477978</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>102011</xdr:rowOff>
+      <xdr:rowOff>98201</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -13601,7 +13600,7 @@
       <xdr:col>23</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>14907</xdr:rowOff>
+      <xdr:rowOff>18717</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -14056,10 +14055,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -14409,15 +14404,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77812A59-879F-495C-8D6A-A1B5ADCA0B5F}">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="3" width="4" style="51" customWidth="1"/>
-    <col min="4" max="9" width="14.28515625" style="51" customWidth="1"/>
+    <col min="4" max="9" width="14.33203125" style="51" customWidth="1"/>
     <col min="10" max="12" width="4" style="51" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="51"/>
+    <col min="13" max="16384" width="9.109375" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="22.7" customHeight="1">
+    <row r="1" spans="1:15" ht="22.65" customHeight="1">
       <c r="A1" s="52"/>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -14431,7 +14426,7 @@
       <c r="K1" s="52"/>
       <c r="L1" s="52"/>
     </row>
-    <row r="2" spans="1:15" ht="22.7" customHeight="1">
+    <row r="2" spans="1:15" ht="22.65" customHeight="1">
       <c r="A2" s="52"/>
       <c r="B2" s="50"/>
       <c r="C2" s="49"/>
@@ -14445,7 +14440,7 @@
       <c r="K2" s="48"/>
       <c r="L2" s="52"/>
     </row>
-    <row r="3" spans="1:15" ht="22.7" customHeight="1">
+    <row r="3" spans="1:15" ht="22.65" customHeight="1">
       <c r="A3" s="52"/>
       <c r="B3" s="47"/>
       <c r="C3" s="46"/>
@@ -14544,15 +14539,15 @@
       <c r="A14" s="52"/>
       <c r="B14" s="47"/>
       <c r="C14" s="42"/>
-      <c r="D14" s="168" t="s">
+      <c r="D14" s="192" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="168"/>
-      <c r="F14" s="169" t="s">
+      <c r="E14" s="192"/>
+      <c r="F14" s="193" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="169"/>
-      <c r="H14" s="169"/>
+      <c r="G14" s="193"/>
+      <c r="H14" s="193"/>
       <c r="J14" s="41"/>
       <c r="K14" s="43"/>
       <c r="L14" s="52"/>
@@ -14563,9 +14558,9 @@
       <c r="C15" s="42"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="169"/>
-      <c r="H15" s="169"/>
+      <c r="F15" s="193"/>
+      <c r="G15" s="193"/>
+      <c r="H15" s="193"/>
       <c r="J15" s="41"/>
       <c r="K15" s="43"/>
       <c r="L15" s="52"/>
@@ -14590,16 +14585,16 @@
       <c r="A18" s="52"/>
       <c r="B18" s="47"/>
       <c r="C18" s="42"/>
-      <c r="D18" s="168" t="s">
+      <c r="D18" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="168"/>
-      <c r="F18" s="169" t="s">
+      <c r="E18" s="192"/>
+      <c r="F18" s="193" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="169"/>
-      <c r="H18" s="169"/>
-      <c r="I18" s="169"/>
+      <c r="G18" s="193"/>
+      <c r="H18" s="193"/>
+      <c r="I18" s="193"/>
       <c r="J18" s="41"/>
       <c r="K18" s="43"/>
       <c r="L18" s="52"/>
@@ -14610,10 +14605,10 @@
       <c r="C19" s="42"/>
       <c r="D19" s="39"/>
       <c r="E19" s="39"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="169"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="169"/>
+      <c r="F19" s="193"/>
+      <c r="G19" s="193"/>
+      <c r="H19" s="193"/>
+      <c r="I19" s="193"/>
       <c r="J19" s="41"/>
       <c r="K19" s="43"/>
       <c r="L19" s="52"/>
@@ -14624,10 +14619,10 @@
       <c r="C20" s="42"/>
       <c r="D20" s="39"/>
       <c r="E20" s="39"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="169"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="193"/>
+      <c r="H20" s="193"/>
+      <c r="I20" s="193"/>
       <c r="J20" s="41"/>
       <c r="K20" s="43"/>
       <c r="L20" s="52"/>
@@ -14647,10 +14642,10 @@
       <c r="A22" s="52"/>
       <c r="B22" s="47"/>
       <c r="C22" s="42"/>
-      <c r="D22" s="168" t="s">
+      <c r="D22" s="192" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="168"/>
+      <c r="E22" s="192"/>
       <c r="F22" s="37">
         <v>45173</v>
       </c>
@@ -14728,10 +14723,10 @@
       <c r="A28" s="52"/>
       <c r="B28" s="47"/>
       <c r="C28" s="42"/>
-      <c r="D28" s="168" t="s">
+      <c r="D28" s="192" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="168"/>
+      <c r="E28" s="192"/>
       <c r="F28" s="51" t="s">
         <v>7</v>
       </c>
@@ -14770,10 +14765,10 @@
       <c r="A32" s="52"/>
       <c r="B32" s="47"/>
       <c r="C32" s="42"/>
-      <c r="D32" s="168" t="s">
+      <c r="D32" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="168"/>
+      <c r="E32" s="192"/>
       <c r="F32" s="51" t="s">
         <v>7</v>
       </c>
@@ -14838,7 +14833,7 @@
       <c r="K38" s="43"/>
       <c r="L38" s="52"/>
     </row>
-    <row r="39" spans="1:12" ht="22.7" customHeight="1">
+    <row r="39" spans="1:12" ht="22.65" customHeight="1">
       <c r="A39" s="52"/>
       <c r="B39" s="32"/>
       <c r="C39" s="31"/>
@@ -14852,7 +14847,7 @@
       <c r="K39" s="30"/>
       <c r="L39" s="52"/>
     </row>
-    <row r="40" spans="1:12" ht="22.7" customHeight="1">
+    <row r="40" spans="1:12" ht="22.65" customHeight="1">
       <c r="A40" s="52"/>
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
@@ -14866,8 +14861,8 @@
       <c r="K40" s="52"/>
       <c r="L40" s="52"/>
     </row>
-    <row r="48" spans="1:12" ht="59.45" customHeight="1"/>
-    <row r="49" ht="64.150000000000006" customHeight="1"/>
+    <row r="48" spans="1:12" ht="59.4" customHeight="1"/>
+    <row r="49" ht="64.2" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="D32:E32"/>
@@ -14890,17 +14885,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBF481A-D2DF-4904-8542-3490B02494C7}">
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="3" width="4" style="29" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="34.85546875" style="29" customWidth="1"/>
-    <col min="6" max="6" width="58.140625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="23.44140625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" style="29" customWidth="1"/>
+    <col min="6" max="6" width="58.109375" style="29" customWidth="1"/>
     <col min="7" max="9" width="4" style="29" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="29"/>
+    <col min="10" max="16384" width="9.109375" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.7" customHeight="1">
+    <row r="1" spans="1:9" ht="22.65" customHeight="1">
       <c r="A1" s="52"/>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -14911,7 +14906,7 @@
       <c r="H1" s="52"/>
       <c r="I1" s="52"/>
     </row>
-    <row r="2" spans="1:9" ht="22.7" customHeight="1">
+    <row r="2" spans="1:9" ht="22.65" customHeight="1">
       <c r="A2" s="52"/>
       <c r="B2" s="50"/>
       <c r="C2" s="49"/>
@@ -14922,7 +14917,7 @@
       <c r="H2" s="48"/>
       <c r="I2" s="52"/>
     </row>
-    <row r="3" spans="1:9" ht="18.75">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="52"/>
       <c r="B3" s="47"/>
       <c r="C3" s="46"/>
@@ -14933,20 +14928,20 @@
       <c r="H3" s="43"/>
       <c r="I3" s="52"/>
     </row>
-    <row r="4" spans="1:9" ht="18.75">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="52"/>
       <c r="B4" s="47"/>
       <c r="C4" s="42"/>
-      <c r="D4" s="170" t="s">
+      <c r="D4" s="194" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="170"/>
-      <c r="F4" s="170"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
       <c r="G4" s="41"/>
       <c r="H4" s="43"/>
       <c r="I4" s="52"/>
     </row>
-    <row r="5" spans="1:9" ht="18.75">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="52"/>
       <c r="B5" s="47"/>
       <c r="C5" s="42"/>
@@ -14957,7 +14952,7 @@
       <c r="H5" s="43"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="18.75">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="52"/>
       <c r="B6" s="47"/>
       <c r="C6" s="42"/>
@@ -14970,7 +14965,7 @@
       <c r="H6" s="43"/>
       <c r="I6" s="52"/>
     </row>
-    <row r="7" spans="1:9" ht="18.75">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="52"/>
       <c r="B7" s="47"/>
       <c r="C7" s="42"/>
@@ -14981,7 +14976,7 @@
       <c r="H7" s="43"/>
       <c r="I7" s="52"/>
     </row>
-    <row r="8" spans="1:9" ht="18.75">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="52"/>
       <c r="B8" s="47"/>
       <c r="C8" s="42"/>
@@ -14998,7 +14993,7 @@
       <c r="H8" s="43"/>
       <c r="I8" s="52"/>
     </row>
-    <row r="9" spans="1:9" ht="18.75">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="52"/>
       <c r="B9" s="47"/>
       <c r="C9" s="42"/>
@@ -15015,7 +15010,7 @@
       <c r="H9" s="43"/>
       <c r="I9" s="52"/>
     </row>
-    <row r="10" spans="1:9" ht="18.75">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="52"/>
       <c r="B10" s="47"/>
       <c r="C10" s="42"/>
@@ -15032,7 +15027,7 @@
       <c r="H10" s="43"/>
       <c r="I10" s="52"/>
     </row>
-    <row r="11" spans="1:9" ht="18.75">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="52"/>
       <c r="B11" s="47"/>
       <c r="C11" s="42"/>
@@ -15049,7 +15044,7 @@
       <c r="H11" s="43"/>
       <c r="I11" s="52"/>
     </row>
-    <row r="12" spans="1:9" ht="18.75">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="52"/>
       <c r="B12" s="47"/>
       <c r="C12" s="42"/>
@@ -15066,7 +15061,7 @@
       <c r="H12" s="43"/>
       <c r="I12" s="52"/>
     </row>
-    <row r="13" spans="1:9" ht="18.75">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="52"/>
       <c r="B13" s="47"/>
       <c r="C13" s="42"/>
@@ -15083,7 +15078,7 @@
       <c r="H13" s="43"/>
       <c r="I13" s="52"/>
     </row>
-    <row r="14" spans="1:9" ht="18.75">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="52"/>
       <c r="B14" s="47"/>
       <c r="C14" s="42"/>
@@ -15100,7 +15095,7 @@
       <c r="H14" s="43"/>
       <c r="I14" s="52"/>
     </row>
-    <row r="15" spans="1:9" ht="18.75">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="52"/>
       <c r="B15" s="47"/>
       <c r="C15" s="42"/>
@@ -15115,7 +15110,7 @@
       <c r="H15" s="43"/>
       <c r="I15" s="52"/>
     </row>
-    <row r="16" spans="1:9" ht="18.75">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="52"/>
       <c r="B16" s="47"/>
       <c r="C16" s="42"/>
@@ -15130,7 +15125,7 @@
       <c r="H16" s="43"/>
       <c r="I16" s="52"/>
     </row>
-    <row r="17" spans="1:9" ht="18.75">
+    <row r="17" spans="1:9" ht="18">
       <c r="A17" s="52"/>
       <c r="B17" s="47"/>
       <c r="C17" s="42"/>
@@ -15145,7 +15140,7 @@
       <c r="H17" s="43"/>
       <c r="I17" s="52"/>
     </row>
-    <row r="18" spans="1:9" ht="18.75">
+    <row r="18" spans="1:9" ht="18">
       <c r="A18" s="52"/>
       <c r="B18" s="47"/>
       <c r="C18" s="42"/>
@@ -15160,7 +15155,7 @@
       <c r="H18" s="43"/>
       <c r="I18" s="52"/>
     </row>
-    <row r="19" spans="1:9" ht="18.75">
+    <row r="19" spans="1:9" ht="18">
       <c r="A19" s="52"/>
       <c r="B19" s="47"/>
       <c r="C19" s="42"/>
@@ -15171,7 +15166,7 @@
       <c r="H19" s="43"/>
       <c r="I19" s="52"/>
     </row>
-    <row r="20" spans="1:9" ht="18.75">
+    <row r="20" spans="1:9" ht="18">
       <c r="A20" s="52"/>
       <c r="B20" s="47"/>
       <c r="C20" s="42"/>
@@ -15182,7 +15177,7 @@
       <c r="H20" s="43"/>
       <c r="I20" s="52"/>
     </row>
-    <row r="21" spans="1:9" ht="18.75">
+    <row r="21" spans="1:9" ht="18">
       <c r="A21" s="52"/>
       <c r="B21" s="47"/>
       <c r="C21" s="42"/>
@@ -15193,7 +15188,7 @@
       <c r="H21" s="43"/>
       <c r="I21" s="52"/>
     </row>
-    <row r="22" spans="1:9" ht="18.75">
+    <row r="22" spans="1:9" ht="18">
       <c r="A22" s="52"/>
       <c r="B22" s="47"/>
       <c r="C22" s="42"/>
@@ -15204,7 +15199,7 @@
       <c r="H22" s="43"/>
       <c r="I22" s="52"/>
     </row>
-    <row r="23" spans="1:9" ht="18.75">
+    <row r="23" spans="1:9" ht="18">
       <c r="A23" s="52"/>
       <c r="B23" s="47"/>
       <c r="C23" s="42"/>
@@ -15215,7 +15210,7 @@
       <c r="H23" s="43"/>
       <c r="I23" s="52"/>
     </row>
-    <row r="24" spans="1:9" ht="18.75">
+    <row r="24" spans="1:9" ht="18">
       <c r="A24" s="52"/>
       <c r="B24" s="47"/>
       <c r="C24" s="42"/>
@@ -15226,7 +15221,7 @@
       <c r="H24" s="43"/>
       <c r="I24" s="52"/>
     </row>
-    <row r="25" spans="1:9" ht="18.75">
+    <row r="25" spans="1:9" ht="18">
       <c r="A25" s="52"/>
       <c r="B25" s="47"/>
       <c r="C25" s="42"/>
@@ -15237,7 +15232,7 @@
       <c r="H25" s="43"/>
       <c r="I25" s="52"/>
     </row>
-    <row r="26" spans="1:9" ht="18.75">
+    <row r="26" spans="1:9" ht="18">
       <c r="A26" s="52"/>
       <c r="B26" s="47"/>
       <c r="C26" s="42"/>
@@ -15248,7 +15243,7 @@
       <c r="H26" s="43"/>
       <c r="I26" s="52"/>
     </row>
-    <row r="27" spans="1:9" ht="18.75">
+    <row r="27" spans="1:9" ht="18">
       <c r="A27" s="52"/>
       <c r="B27" s="47"/>
       <c r="C27" s="42"/>
@@ -15259,7 +15254,7 @@
       <c r="H27" s="43"/>
       <c r="I27" s="52"/>
     </row>
-    <row r="28" spans="1:9" ht="18.75">
+    <row r="28" spans="1:9" ht="18">
       <c r="A28" s="52"/>
       <c r="B28" s="47"/>
       <c r="C28" s="42"/>
@@ -15270,7 +15265,7 @@
       <c r="H28" s="43"/>
       <c r="I28" s="52"/>
     </row>
-    <row r="29" spans="1:9" ht="18.75">
+    <row r="29" spans="1:9" ht="18">
       <c r="A29" s="52"/>
       <c r="B29" s="47"/>
       <c r="C29" s="42"/>
@@ -15281,7 +15276,7 @@
       <c r="H29" s="43"/>
       <c r="I29" s="52"/>
     </row>
-    <row r="30" spans="1:9" ht="18.75">
+    <row r="30" spans="1:9" ht="18">
       <c r="A30" s="52"/>
       <c r="B30" s="47"/>
       <c r="C30" s="42"/>
@@ -15292,7 +15287,7 @@
       <c r="H30" s="43"/>
       <c r="I30" s="52"/>
     </row>
-    <row r="31" spans="1:9" ht="18.75">
+    <row r="31" spans="1:9" ht="18">
       <c r="A31" s="52"/>
       <c r="B31" s="47"/>
       <c r="C31" s="42"/>
@@ -15303,7 +15298,7 @@
       <c r="H31" s="43"/>
       <c r="I31" s="52"/>
     </row>
-    <row r="32" spans="1:9" ht="18.75">
+    <row r="32" spans="1:9" ht="18">
       <c r="A32" s="52"/>
       <c r="B32" s="47"/>
       <c r="C32" s="42"/>
@@ -15314,7 +15309,7 @@
       <c r="H32" s="43"/>
       <c r="I32" s="52"/>
     </row>
-    <row r="33" spans="1:9" ht="18.75">
+    <row r="33" spans="1:9" ht="18">
       <c r="A33" s="52"/>
       <c r="B33" s="47"/>
       <c r="C33" s="42"/>
@@ -15325,7 +15320,7 @@
       <c r="H33" s="43"/>
       <c r="I33" s="52"/>
     </row>
-    <row r="34" spans="1:9" ht="18.75">
+    <row r="34" spans="1:9" ht="18">
       <c r="A34" s="52"/>
       <c r="B34" s="47"/>
       <c r="C34" s="42"/>
@@ -15336,7 +15331,7 @@
       <c r="H34" s="43"/>
       <c r="I34" s="52"/>
     </row>
-    <row r="35" spans="1:9" ht="18.75">
+    <row r="35" spans="1:9" ht="18">
       <c r="A35" s="52"/>
       <c r="B35" s="47"/>
       <c r="C35" s="42"/>
@@ -15347,7 +15342,7 @@
       <c r="H35" s="43"/>
       <c r="I35" s="52"/>
     </row>
-    <row r="36" spans="1:9" ht="18.75">
+    <row r="36" spans="1:9" ht="18">
       <c r="A36" s="52"/>
       <c r="B36" s="47"/>
       <c r="C36" s="42"/>
@@ -15358,7 +15353,7 @@
       <c r="H36" s="43"/>
       <c r="I36" s="52"/>
     </row>
-    <row r="37" spans="1:9" ht="18.75">
+    <row r="37" spans="1:9" ht="18">
       <c r="A37" s="52"/>
       <c r="B37" s="47"/>
       <c r="C37" s="42"/>
@@ -15369,7 +15364,7 @@
       <c r="H37" s="43"/>
       <c r="I37" s="52"/>
     </row>
-    <row r="38" spans="1:9" ht="18.75">
+    <row r="38" spans="1:9" ht="18">
       <c r="A38" s="52"/>
       <c r="B38" s="47"/>
       <c r="C38" s="35"/>
@@ -15380,7 +15375,7 @@
       <c r="H38" s="43"/>
       <c r="I38" s="52"/>
     </row>
-    <row r="39" spans="1:9" ht="22.7" customHeight="1">
+    <row r="39" spans="1:9" ht="22.65" customHeight="1">
       <c r="A39" s="52"/>
       <c r="B39" s="32"/>
       <c r="C39" s="31"/>
@@ -15391,7 +15386,7 @@
       <c r="H39" s="30"/>
       <c r="I39" s="52"/>
     </row>
-    <row r="40" spans="1:9" ht="22.7" customHeight="1">
+    <row r="40" spans="1:9" ht="22.65" customHeight="1">
       <c r="A40" s="52"/>
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
@@ -15414,22 +15409,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
-    <col min="12" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" customWidth="1"/>
+    <col min="12" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="18">
+    <row r="2" spans="2:10" ht="17.399999999999999">
       <c r="B2" s="64" t="s">
         <v>164</v>
       </c>
@@ -15495,7 +15490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="39" thickBot="1">
+    <row r="6" spans="2:10" ht="40.200000000000003" thickBot="1">
       <c r="B6" s="13" t="s">
         <v>22</v>
       </c>
@@ -15633,7 +15628,7 @@
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
     </row>
-    <row r="24" ht="13.7" customHeight="1"/>
+    <row r="24" ht="13.65" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15647,15 +15642,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Arkusz1"/>
   <dimension ref="B2:J11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.44140625" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" customWidth="1"/>
     <col min="6" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15725,7 +15720,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="39" thickBot="1">
+    <row r="6" spans="2:10" ht="40.200000000000003" thickBot="1">
       <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
@@ -15821,18 +15816,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Arkusz2"/>
   <dimension ref="B2:L16"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="47.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="7" width="19.85546875" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" customWidth="1"/>
+    <col min="5" max="7" width="19.88671875" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="18">
+    <row r="2" spans="2:12" ht="17.399999999999999">
       <c r="B2" s="64" t="s">
         <v>56</v>
       </c>
@@ -15886,7 +15881,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="26.25" thickBot="1">
+    <row r="6" spans="2:12" ht="27" thickBot="1">
       <c r="B6" s="13" t="s">
         <v>64</v>
       </c>
@@ -16018,36 +16013,36 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41D2646-6146-4D14-B889-3C0C97BBED9D}">
   <dimension ref="A2:BV137"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9" style="72" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" style="72" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="72" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="72" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" style="72" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="72" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="72" customWidth="1"/>
     <col min="5" max="6" width="13" style="72" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="72" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" style="72" customWidth="1"/>
     <col min="8" max="8" width="13" style="72" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="72" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="72" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="72" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="72" customWidth="1"/>
     <col min="11" max="11" width="11" style="72" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="72" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" style="72" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="72" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="72" customWidth="1"/>
-    <col min="16" max="16" width="12.42578125" style="72" customWidth="1"/>
-    <col min="17" max="45" width="9.140625" style="72"/>
-    <col min="46" max="46" width="12.5703125" style="72" customWidth="1"/>
-    <col min="47" max="47" width="11.7109375" style="72" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="11.140625" style="72" customWidth="1"/>
-    <col min="49" max="49" width="23.42578125" style="72" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="72" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" style="72" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="72" customWidth="1"/>
+    <col min="15" max="15" width="11.88671875" style="72" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" style="72" customWidth="1"/>
+    <col min="17" max="45" width="9.109375" style="72"/>
+    <col min="46" max="46" width="12.5546875" style="72" customWidth="1"/>
+    <col min="47" max="47" width="11.6640625" style="72" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.109375" style="72" customWidth="1"/>
+    <col min="49" max="49" width="23.44140625" style="72" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="13" style="72" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" style="72" customWidth="1"/>
-    <col min="52" max="56" width="9.140625" style="72"/>
+    <col min="51" max="51" width="9.109375" style="72" customWidth="1"/>
+    <col min="52" max="56" width="9.109375" style="72"/>
     <col min="57" max="57" width="6" style="72" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.140625" style="72" bestFit="1" customWidth="1"/>
-    <col min="59" max="65" width="9.140625" style="72"/>
-    <col min="66" max="66" width="28.42578125" style="72" bestFit="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.140625" style="72"/>
+    <col min="58" max="58" width="11.109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="59" max="65" width="9.109375" style="72"/>
+    <col min="66" max="66" width="28.44140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.109375" style="72"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19">
@@ -16057,14 +16052,14 @@
       <c r="D2" s="63"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:19" ht="13.5" thickBot="1">
+    <row r="3" spans="1:19" ht="13.8" thickBot="1">
       <c r="B3" s="65" t="s">
         <v>76</v>
       </c>
       <c r="C3" s="65"/>
       <c r="D3" s="63"/>
     </row>
-    <row r="4" spans="1:19" ht="30" thickBot="1">
+    <row r="4" spans="1:19" ht="21" thickBot="1">
       <c r="B4" s="132" t="s">
         <v>15</v>
       </c>
@@ -16092,17 +16087,17 @@
       <c r="J4" s="132">
         <v>2050</v>
       </c>
-      <c r="O4" s="171" t="s">
+      <c r="O4" s="164" t="s">
         <v>187</v>
       </c>
-      <c r="P4" s="172" t="s">
+      <c r="P4" s="165" t="s">
         <v>188</v>
       </c>
-      <c r="Q4" s="172" t="s">
+      <c r="Q4" s="165" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="13.5" thickBot="1">
+    <row r="5" spans="1:19" ht="13.8" thickBot="1">
       <c r="B5" s="133" t="s">
         <v>75</v>
       </c>
@@ -16128,17 +16123,17 @@
       <c r="J5" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="O5" s="173">
+      <c r="O5" s="166">
         <v>2024</v>
       </c>
-      <c r="P5" s="174">
+      <c r="P5" s="167">
         <v>25.3</v>
       </c>
-      <c r="Q5" s="174">
+      <c r="Q5" s="167">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="6" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
       <c r="B6" s="67" t="s">
         <v>210</v>
       </c>
@@ -16152,17 +16147,17 @@
       <c r="H6" s="135"/>
       <c r="I6" s="135"/>
       <c r="J6" s="135"/>
-      <c r="O6" s="175">
+      <c r="O6" s="168">
         <v>2025</v>
       </c>
-      <c r="P6" s="176">
+      <c r="P6" s="169">
         <v>50</v>
       </c>
-      <c r="Q6" s="176">
+      <c r="Q6" s="169">
         <v>1.98</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="7" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
       <c r="B7" s="69" t="s">
         <v>75</v>
       </c>
@@ -16176,25 +16171,25 @@
       <c r="H7" s="69"/>
       <c r="I7" s="69"/>
       <c r="J7" s="69"/>
-      <c r="O7" s="173">
+      <c r="O7" s="166">
         <v>2030</v>
       </c>
-      <c r="P7" s="177">
+      <c r="P7" s="170">
         <v>1500</v>
       </c>
-      <c r="Q7" s="174">
+      <c r="Q7" s="167">
         <v>59.25</v>
       </c>
       <c r="R7" s="72">
-        <f>0.7*P7</f>
+        <f t="shared" ref="R7:S11" si="0">0.7*P7</f>
         <v>1050</v>
       </c>
       <c r="S7" s="72">
-        <f>0.7*Q7</f>
+        <f t="shared" si="0"/>
         <v>41.474999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="8" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
       <c r="B8" s="131" t="s">
         <v>79</v>
       </c>
@@ -16224,25 +16219,25 @@
       <c r="J8" s="129">
         <v>1080.14382844436</v>
       </c>
-      <c r="O8" s="175">
+      <c r="O8" s="168">
         <v>2035</v>
       </c>
-      <c r="P8" s="178">
+      <c r="P8" s="171">
         <v>2700</v>
       </c>
-      <c r="Q8" s="176">
+      <c r="Q8" s="169">
         <v>106.65</v>
       </c>
       <c r="R8" s="72">
-        <f>0.7*P8</f>
+        <f t="shared" si="0"/>
         <v>1889.9999999999998</v>
       </c>
       <c r="S8" s="72">
-        <f>0.7*Q8</f>
+        <f t="shared" si="0"/>
         <v>74.655000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="9" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
       <c r="B9" s="130" t="s">
         <v>80</v>
       </c>
@@ -16272,26 +16267,26 @@
       <c r="J9" s="158">
         <v>2093.2382440706288</v>
       </c>
-      <c r="N9" s="179"/>
-      <c r="O9" s="173">
+      <c r="N9" s="172"/>
+      <c r="O9" s="166">
         <v>2040</v>
       </c>
-      <c r="P9" s="177">
+      <c r="P9" s="170">
         <v>3900</v>
       </c>
-      <c r="Q9" s="174">
+      <c r="Q9" s="167">
         <v>154.05000000000001</v>
       </c>
       <c r="R9" s="72">
-        <f>0.7*P9</f>
+        <f t="shared" si="0"/>
         <v>2730</v>
       </c>
       <c r="S9" s="72">
-        <f>0.7*Q9</f>
+        <f t="shared" si="0"/>
         <v>107.83500000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="10" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
       <c r="B10" s="160" t="s">
         <v>81</v>
       </c>
@@ -16321,26 +16316,26 @@
       <c r="J10" s="163">
         <v>138.38316947218644</v>
       </c>
-      <c r="N10" s="179"/>
-      <c r="O10" s="175">
+      <c r="N10" s="172"/>
+      <c r="O10" s="168">
         <v>2045</v>
       </c>
-      <c r="P10" s="178">
+      <c r="P10" s="171">
         <v>4300</v>
       </c>
-      <c r="Q10" s="176">
+      <c r="Q10" s="169">
         <v>169.85</v>
       </c>
       <c r="R10" s="72">
-        <f>0.7*P10</f>
+        <f t="shared" si="0"/>
         <v>3010</v>
       </c>
       <c r="S10" s="72">
-        <f>0.7*Q10</f>
+        <f t="shared" si="0"/>
         <v>118.89499999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="11" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>82</v>
       </c>
@@ -16370,26 +16365,26 @@
       <c r="J11" s="158">
         <v>4765.3748163877262</v>
       </c>
-      <c r="N11" s="179"/>
-      <c r="O11" s="173">
+      <c r="N11" s="172"/>
+      <c r="O11" s="166">
         <v>2050</v>
       </c>
-      <c r="P11" s="177">
+      <c r="P11" s="170">
         <v>4700</v>
       </c>
-      <c r="Q11" s="174">
+      <c r="Q11" s="167">
         <v>185.65</v>
       </c>
       <c r="R11" s="72">
-        <f>0.7*P11</f>
+        <f t="shared" si="0"/>
         <v>3290</v>
       </c>
       <c r="S11" s="72">
-        <f>0.7*Q11</f>
+        <f t="shared" si="0"/>
         <v>129.95499999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="16.149999999999999" customHeight="1">
+    <row r="12" spans="1:19" ht="16.2" customHeight="1">
       <c r="B12" s="160" t="s">
         <v>83</v>
       </c>
@@ -16401,7 +16396,7 @@
         <v>64.180000000000007</v>
       </c>
       <c r="E12" s="163">
-        <f t="shared" ref="E9:J28" si="0">D12</f>
+        <f t="shared" ref="E12:J28" si="1">D12</f>
         <v>64.180000000000007</v>
       </c>
       <c r="F12" s="163">
@@ -16419,11 +16414,11 @@
       <c r="J12" s="163">
         <v>33.152783626079447</v>
       </c>
-      <c r="N12" s="179"/>
-      <c r="O12" s="179"/>
-      <c r="P12" s="179"/>
-    </row>
-    <row r="13" spans="1:19" ht="16.149999999999999" customHeight="1">
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172"/>
+    </row>
+    <row r="13" spans="1:19" ht="16.2" customHeight="1">
       <c r="B13" s="130" t="s">
         <v>84</v>
       </c>
@@ -16453,11 +16448,11 @@
       <c r="J13" s="158">
         <v>141017.61786916296</v>
       </c>
-      <c r="N13" s="179"/>
-      <c r="O13" s="179"/>
-      <c r="P13" s="179"/>
-    </row>
-    <row r="14" spans="1:19" ht="16.149999999999999" customHeight="1">
+      <c r="N13" s="172"/>
+      <c r="O13" s="172"/>
+      <c r="P13" s="172"/>
+    </row>
+    <row r="14" spans="1:19" ht="16.2" customHeight="1">
       <c r="B14" s="69" t="s">
         <v>75</v>
       </c>
@@ -16471,11 +16466,11 @@
       <c r="H14" s="69"/>
       <c r="I14" s="69"/>
       <c r="J14" s="69"/>
-      <c r="N14" s="179"/>
-      <c r="O14" s="179"/>
-      <c r="P14" s="179"/>
-    </row>
-    <row r="15" spans="1:19" ht="16.149999999999999" customHeight="1">
+      <c r="N14" s="172"/>
+      <c r="O14" s="172"/>
+      <c r="P14" s="172"/>
+    </row>
+    <row r="15" spans="1:19" ht="16.2" customHeight="1">
       <c r="B15" s="131" t="s">
         <v>85</v>
       </c>
@@ -16510,7 +16505,7 @@
         <f>AZ42</f>
         <v>8757.7688560000006</v>
       </c>
-      <c r="L15" s="185">
+      <c r="L15" s="174">
         <f>J15-F15</f>
         <v>-4938.4647130974536</v>
       </c>
@@ -16518,9 +16513,9 @@
         <f>L15/4</f>
         <v>-1234.6161782743634</v>
       </c>
-      <c r="N15" s="179"/>
-      <c r="O15" s="179"/>
-      <c r="P15" s="179"/>
+      <c r="N15" s="172"/>
+      <c r="O15" s="172"/>
+      <c r="P15" s="172"/>
     </row>
     <row r="16" spans="1:19">
       <c r="B16" s="130" t="s">
@@ -16546,28 +16541,28 @@
         <v>2977.7284014361885</v>
       </c>
       <c r="H16" s="158">
-        <f t="shared" ref="H16:I16" si="1">G16+$M$16</f>
+        <f t="shared" ref="H16:I16" si="2">G16+$M$16</f>
         <v>2676.4268726241257</v>
       </c>
       <c r="I16" s="158">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2375.125343812063</v>
       </c>
       <c r="J16" s="158">
         <f>AZ46</f>
         <v>2073.8238149999997</v>
       </c>
-      <c r="L16" s="185">
-        <f t="shared" ref="L16:L28" si="2">J16-F16</f>
+      <c r="L16" s="174">
+        <f t="shared" ref="L16:L28" si="3">J16-F16</f>
         <v>-1205.2061152482515</v>
       </c>
       <c r="M16" s="72">
-        <f t="shared" ref="M16:M28" si="3">L16/4</f>
+        <f t="shared" ref="M16:M28" si="4">L16/4</f>
         <v>-301.30152881206288</v>
       </c>
-      <c r="N16" s="179"/>
-      <c r="O16" s="179"/>
-      <c r="P16" s="179"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="172"/>
+      <c r="P16" s="172"/>
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="160" t="s">
@@ -16593,23 +16588,23 @@
         <v>8823.6360865801071</v>
       </c>
       <c r="H17" s="129">
-        <f t="shared" ref="H17:I17" si="4">G17+$M$17</f>
+        <f t="shared" ref="H17:I17" si="5">G17+$M$17</f>
         <v>6619.0782627200715</v>
       </c>
       <c r="I17" s="129">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4414.5204388600359</v>
       </c>
       <c r="J17" s="129">
         <f>AZ54</f>
         <v>2209.9626149999999</v>
       </c>
-      <c r="L17" s="185">
-        <f t="shared" si="2"/>
+      <c r="L17" s="174">
+        <f t="shared" si="3"/>
         <v>-8818.2312954401423</v>
       </c>
       <c r="M17" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2204.5578238600356</v>
       </c>
     </row>
@@ -16637,23 +16632,23 @@
         <v>961.90244853155855</v>
       </c>
       <c r="H18" s="158">
-        <f t="shared" ref="H18:I18" si="5">G18+$M$18</f>
+        <f t="shared" ref="H18:I18" si="6">G18+$M$18</f>
         <v>1324.0950590210391</v>
       </c>
       <c r="I18" s="158">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1686.2876695105197</v>
       </c>
       <c r="J18" s="158">
         <f>AZ52</f>
         <v>2048.4802799999998</v>
       </c>
-      <c r="L18" s="185">
-        <f t="shared" si="2"/>
+      <c r="L18" s="174">
+        <f t="shared" si="3"/>
         <v>1448.7704419579218</v>
       </c>
       <c r="M18" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>362.19261048948044</v>
       </c>
     </row>
@@ -16681,23 +16676,23 @@
         <v>4627.95882061251</v>
       </c>
       <c r="H19" s="129">
-        <f t="shared" ref="H19:I19" si="6">G19+$M$19</f>
+        <f t="shared" ref="H19:I19" si="7">G19+$M$19</f>
         <v>4330.5851977416733</v>
       </c>
       <c r="I19" s="129">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4033.2115748708366</v>
       </c>
       <c r="J19" s="129">
         <f>AZ50</f>
         <v>3735.8379519999999</v>
       </c>
-      <c r="L19" s="185">
-        <f t="shared" si="2"/>
+      <c r="L19" s="174">
+        <f t="shared" si="3"/>
         <v>-1189.4944914833468</v>
       </c>
       <c r="M19" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-297.3736228708367</v>
       </c>
       <c r="S19" s="63"/>
@@ -16726,23 +16721,23 @@
         <v>1508.0810034106876</v>
       </c>
       <c r="H20" s="158">
-        <f t="shared" ref="H20:I20" si="7">G20+$M$20</f>
+        <f t="shared" ref="H20:I20" si="8">G20+$M$20</f>
         <v>1290.2504106071251</v>
       </c>
       <c r="I20" s="158">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1072.4198178035626</v>
       </c>
       <c r="J20" s="158">
         <f>AZ48</f>
         <v>854.58922499999994</v>
       </c>
-      <c r="L20" s="185">
-        <f t="shared" si="2"/>
+      <c r="L20" s="174">
+        <f t="shared" si="3"/>
         <v>-871.3223712142501</v>
       </c>
       <c r="M20" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-217.83059280356252</v>
       </c>
       <c r="S20" s="63"/>
@@ -16771,23 +16766,23 @@
         <v>1971.3780670836961</v>
       </c>
       <c r="H21" s="129">
-        <f t="shared" ref="H21:I21" si="8">G21+$M$21</f>
+        <f t="shared" ref="H21:I21" si="9">G21+$M$21</f>
         <v>1784.7020853891308</v>
       </c>
       <c r="I21" s="129">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1598.0261036945656</v>
       </c>
       <c r="J21" s="129">
         <f>AZ44</f>
         <v>1411.3501220000001</v>
       </c>
-      <c r="L21" s="185">
-        <f t="shared" si="2"/>
+      <c r="L21" s="174">
+        <f t="shared" si="3"/>
         <v>-746.70392677826135</v>
       </c>
       <c r="M21" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-186.67598169456534</v>
       </c>
       <c r="S21" s="63"/>
@@ -16816,23 +16811,23 @@
         <v>116.88393575665523</v>
       </c>
       <c r="H22" s="158">
-        <f t="shared" ref="H22:I22" si="9">G22+$M$22</f>
+        <f t="shared" ref="H22:I22" si="10">G22+$M$22</f>
         <v>101.1738541711035</v>
       </c>
       <c r="I22" s="158">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>85.463772585551766</v>
       </c>
       <c r="J22" s="158">
         <f>AZ56+AZ58</f>
         <v>69.753691000000003</v>
       </c>
-      <c r="L22" s="185">
-        <f t="shared" si="2"/>
+      <c r="L22" s="174">
+        <f t="shared" si="3"/>
         <v>-62.840326342206964</v>
       </c>
       <c r="M22" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-15.710081585551741</v>
       </c>
       <c r="S22" s="63"/>
@@ -16861,23 +16856,23 @@
         <v>622.34230730807576</v>
       </c>
       <c r="H23" s="129">
-        <f t="shared" ref="H23:I23" si="10">G23+$M$23</f>
+        <f t="shared" ref="H23:I23" si="11">G23+$M$23</f>
         <v>471.94221820538382</v>
       </c>
       <c r="I23" s="129">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>321.54212910269189</v>
       </c>
       <c r="J23" s="129">
         <f>AX64</f>
         <v>171.14204000000001</v>
       </c>
-      <c r="L23" s="185">
-        <f t="shared" si="2"/>
+      <c r="L23" s="174">
+        <f t="shared" si="3"/>
         <v>-601.60035641076774</v>
       </c>
       <c r="M23" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-150.40008910269194</v>
       </c>
       <c r="S23" s="63"/>
@@ -16906,23 +16901,23 @@
         <v>623.69459029411769</v>
       </c>
       <c r="H24" s="158">
-        <f t="shared" ref="H24:I24" si="11">G24+$M$24</f>
+        <f t="shared" ref="H24:I24" si="12">G24+$M$24</f>
         <v>653.20439352941173</v>
       </c>
       <c r="I24" s="158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>682.71419676470578</v>
       </c>
       <c r="J24" s="158">
         <f>AZ66</f>
         <v>712.22399999999993</v>
       </c>
-      <c r="L24" s="185">
-        <f t="shared" si="2"/>
+      <c r="L24" s="174">
+        <f t="shared" si="3"/>
         <v>118.03921294117629</v>
       </c>
       <c r="M24" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.509803235294072</v>
       </c>
     </row>
@@ -16950,23 +16945,23 @@
         <v>6149.7571781358893</v>
       </c>
       <c r="H25" s="129">
-        <f t="shared" ref="H25:I25" si="12">G25+$M$25</f>
+        <f t="shared" ref="H25:I25" si="13">G25+$M$25</f>
         <v>6622.8201187572595</v>
       </c>
       <c r="I25" s="129">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7095.8830593786297</v>
       </c>
       <c r="J25" s="129">
         <f>AZ60</f>
         <v>7568.9459999999999</v>
       </c>
-      <c r="L25" s="185">
-        <f t="shared" si="2"/>
+      <c r="L25" s="174">
+        <f t="shared" si="3"/>
         <v>1892.2517624854809</v>
       </c>
       <c r="M25" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>473.06294062137022</v>
       </c>
     </row>
@@ -16994,23 +16989,23 @@
         <v>3803.7793606250007</v>
       </c>
       <c r="H26" s="158">
-        <f t="shared" ref="H26:I26" si="13">G26+$M$26</f>
+        <f t="shared" ref="H26:I26" si="14">G26+$M$26</f>
         <v>3457.172707083334</v>
       </c>
       <c r="I26" s="158">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3110.5660535416673</v>
       </c>
       <c r="J26" s="158">
         <f>AZ62</f>
         <v>2763.9594000000002</v>
       </c>
-      <c r="L26" s="185">
-        <f t="shared" si="2"/>
+      <c r="L26" s="174">
+        <f t="shared" si="3"/>
         <v>-1386.4266141666672</v>
       </c>
       <c r="M26" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-346.60665354166679</v>
       </c>
     </row>
@@ -17025,35 +17020,35 @@
         <v>0</v>
       </c>
       <c r="E27" s="163">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F27" s="129">
-        <f t="shared" ref="F27:F28" si="14">E27+(E27*W78)</f>
+        <f t="shared" ref="F27:F28" si="15">E27+(E27*W78)</f>
         <v>0</v>
       </c>
       <c r="G27" s="129">
-        <f t="shared" ref="G27:G28" si="15">F27+(F27*X78)</f>
+        <f t="shared" ref="G27:G28" si="16">F27+(F27*X78)</f>
         <v>0</v>
       </c>
       <c r="H27" s="129">
-        <f t="shared" ref="H27:H28" si="16">G27+(G27*Y78)</f>
+        <f t="shared" ref="H27:H28" si="17">G27+(G27*Y78)</f>
         <v>0</v>
       </c>
       <c r="I27" s="129">
-        <f t="shared" ref="I27:I28" si="17">H27+(H27*Z78)</f>
+        <f t="shared" ref="I27:I28" si="18">H27+(H27*Z78)</f>
         <v>0</v>
       </c>
       <c r="J27" s="163">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="185">
-        <f t="shared" si="2"/>
+      <c r="L27" s="174">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M27" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -17068,35 +17063,35 @@
         <v>0</v>
       </c>
       <c r="E28" s="159">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F28" s="158">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="158">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H28" s="158">
+      <c r="G28" s="158">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I28" s="158">
+      <c r="H28" s="158">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
+      <c r="I28" s="158">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="J28" s="158">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="185">
-        <f t="shared" si="2"/>
+      <c r="L28" s="174">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M28" s="72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -17115,7 +17110,7 @@
       <c r="I29" s="69"/>
       <c r="J29" s="69"/>
     </row>
-    <row r="30" spans="2:19" ht="16.149999999999999" customHeight="1">
+    <row r="30" spans="2:19" ht="16.2" customHeight="1">
       <c r="B30" s="150" t="s">
         <v>165</v>
       </c>
@@ -17144,7 +17139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="16.149999999999999" customHeight="1">
+    <row r="31" spans="2:19" ht="16.2" customHeight="1">
       <c r="B31" s="69" t="s">
         <v>75</v>
       </c>
@@ -17159,7 +17154,7 @@
       <c r="I31" s="69"/>
       <c r="J31" s="69"/>
     </row>
-    <row r="32" spans="2:19" ht="16.149999999999999" customHeight="1">
+    <row r="32" spans="2:19" ht="16.2" customHeight="1">
       <c r="B32" s="160" t="s">
         <v>185</v>
       </c>
@@ -17188,7 +17183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:74" ht="16.149999999999999" customHeight="1">
+    <row r="33" spans="2:74" ht="16.2" customHeight="1">
       <c r="B33" s="130" t="s">
         <v>186</v>
       </c>
@@ -17217,8 +17212,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:74" ht="16.149999999999999" customHeight="1"/>
-    <row r="35" spans="2:74" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="34" spans="2:74" ht="16.2" customHeight="1"/>
+    <row r="35" spans="2:74" ht="16.2" customHeight="1" thickBot="1">
       <c r="B35" s="72" t="s">
         <v>99</v>
       </c>
@@ -17256,36 +17251,36 @@
       </c>
     </row>
     <row r="37" spans="2:74" ht="15.75" customHeight="1">
-      <c r="B37" s="164" t="s">
+      <c r="B37" s="190" t="s">
         <v>190</v>
       </c>
-      <c r="C37" s="165"/>
-      <c r="D37" s="165"/>
-      <c r="E37" s="165"/>
-      <c r="F37" s="165"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="191"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="191"/>
       <c r="G37" s="108"/>
       <c r="H37" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="164" t="s">
+      <c r="J37" s="190" t="s">
         <v>191</v>
       </c>
-      <c r="K37" s="165"/>
-      <c r="L37" s="165"/>
-      <c r="M37" s="165"/>
-      <c r="N37" s="165"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="191"/>
+      <c r="N37" s="191"/>
       <c r="O37" s="108"/>
       <c r="P37" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="AR37" s="182" t="s">
+      <c r="AR37" s="187" t="s">
         <v>202</v>
       </c>
-      <c r="AS37" s="183"/>
-      <c r="AT37" s="183"/>
-      <c r="AU37" s="183"/>
-      <c r="AV37" s="183"/>
-      <c r="AW37" s="184"/>
+      <c r="AS37" s="188"/>
+      <c r="AT37" s="188"/>
+      <c r="AU37" s="188"/>
+      <c r="AV37" s="188"/>
+      <c r="AW37" s="189"/>
       <c r="AX37" s="109" t="s">
         <v>100</v>
       </c>
@@ -17312,27 +17307,27 @@
       <c r="AV38" s="108"/>
       <c r="AW38" s="108"/>
       <c r="AX38" s="111"/>
-      <c r="BP38" s="195" t="s">
+      <c r="BP38" s="183" t="s">
         <v>207</v>
       </c>
-      <c r="BQ38" s="195"/>
-      <c r="BR38" s="195"/>
-      <c r="BS38" s="195"/>
-      <c r="BT38" s="195"/>
-      <c r="BU38" s="195"/>
-      <c r="BV38" s="195"/>
-    </row>
-    <row r="39" spans="2:74" ht="13.5" thickBot="1">
-      <c r="B39" s="166" t="s">
+      <c r="BQ38" s="183"/>
+      <c r="BR38" s="183"/>
+      <c r="BS38" s="183"/>
+      <c r="BT38" s="183"/>
+      <c r="BU38" s="183"/>
+      <c r="BV38" s="183"/>
+    </row>
+    <row r="39" spans="2:74" ht="13.8" thickBot="1">
+      <c r="B39" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="167" t="s">
+      <c r="C39" s="186" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="167" t="s">
+      <c r="D39" s="186" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="167" t="s">
+      <c r="E39" s="186" t="s">
         <v>104</v>
       </c>
       <c r="F39" s="108"/>
@@ -17342,16 +17337,16 @@
       <c r="H39" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="J39" s="166" t="s">
+      <c r="J39" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="K39" s="180" t="s">
+      <c r="K39" s="185" t="s">
         <v>102</v>
       </c>
-      <c r="L39" s="167" t="s">
+      <c r="L39" s="186" t="s">
         <v>103</v>
       </c>
-      <c r="M39" s="167" t="s">
+      <c r="M39" s="186" t="s">
         <v>104</v>
       </c>
       <c r="N39" s="108"/>
@@ -17361,16 +17356,16 @@
       <c r="P39" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="AR39" s="166" t="s">
+      <c r="AR39" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="AS39" s="180" t="s">
+      <c r="AS39" s="185" t="s">
         <v>102</v>
       </c>
-      <c r="AT39" s="167" t="s">
+      <c r="AT39" s="186" t="s">
         <v>103</v>
       </c>
-      <c r="AU39" s="167" t="s">
+      <c r="AU39" s="186" t="s">
         <v>104</v>
       </c>
       <c r="AV39" s="108"/>
@@ -17402,11 +17397,11 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="2:74" ht="13.7" customHeight="1">
-      <c r="B40" s="166"/>
-      <c r="C40" s="167"/>
-      <c r="D40" s="167"/>
-      <c r="E40" s="167"/>
+    <row r="40" spans="2:74" ht="13.65" customHeight="1">
+      <c r="B40" s="184"/>
+      <c r="C40" s="186"/>
+      <c r="D40" s="186"/>
+      <c r="E40" s="186"/>
       <c r="F40" s="108"/>
       <c r="G40" s="108" t="s">
         <v>182</v>
@@ -17414,10 +17409,10 @@
       <c r="H40" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="J40" s="166"/>
-      <c r="K40" s="180"/>
-      <c r="L40" s="167"/>
-      <c r="M40" s="167"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="185"/>
+      <c r="L40" s="186"/>
+      <c r="M40" s="186"/>
       <c r="N40" s="108"/>
       <c r="O40" s="108" t="s">
         <v>182</v>
@@ -17425,10 +17420,10 @@
       <c r="P40" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="AR40" s="166"/>
-      <c r="AS40" s="180"/>
-      <c r="AT40" s="167"/>
-      <c r="AU40" s="167"/>
+      <c r="AR40" s="184"/>
+      <c r="AS40" s="185"/>
+      <c r="AT40" s="186"/>
+      <c r="AU40" s="186"/>
       <c r="AV40" s="108"/>
       <c r="AW40" s="108" t="s">
         <v>182</v>
@@ -17445,22 +17440,22 @@
       <c r="BF40" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="BG40" s="186">
+      <c r="BG40" s="175">
         <v>2025</v>
       </c>
-      <c r="BH40" s="187">
+      <c r="BH40" s="176">
         <v>2030</v>
       </c>
-      <c r="BI40" s="187">
+      <c r="BI40" s="176">
         <v>2035</v>
       </c>
-      <c r="BJ40" s="187">
+      <c r="BJ40" s="176">
         <v>2040</v>
       </c>
-      <c r="BK40" s="187">
+      <c r="BK40" s="176">
         <v>2045</v>
       </c>
-      <c r="BL40" s="188">
+      <c r="BL40" s="177">
         <v>2050</v>
       </c>
       <c r="BN40" s="72" t="s">
@@ -17516,12 +17511,8 @@
       <c r="AV41" s="108"/>
       <c r="AW41" s="108"/>
       <c r="AX41" s="111"/>
-      <c r="BG41" s="189"/>
-      <c r="BH41" s="190"/>
-      <c r="BI41" s="190"/>
-      <c r="BJ41" s="190"/>
-      <c r="BK41" s="190"/>
-      <c r="BL41" s="191"/>
+      <c r="BG41" s="178"/>
+      <c r="BL41" s="179"/>
       <c r="BN41" s="72" t="s">
         <v>86</v>
       </c>
@@ -17629,32 +17620,32 @@
         <f>BD42/3</f>
         <v>0.19333333333333336</v>
       </c>
-      <c r="BF42" s="181">
+      <c r="BF42" s="173">
         <f>BE42/BB42/5</f>
         <v>8.8280060882800614E-3</v>
       </c>
-      <c r="BG42" s="189">
+      <c r="BG42" s="178">
         <f>O42</f>
         <v>5.59</v>
       </c>
-      <c r="BH42" s="190">
+      <c r="BH42" s="72">
         <f>BG42+(BG42*BF42)</f>
         <v>5.6393485540334858</v>
       </c>
-      <c r="BI42" s="190">
-        <f t="shared" ref="BI42:BL42" si="18">BH42+(BH42*$BF$42)</f>
+      <c r="BI42" s="72">
+        <f t="shared" ref="BI42:BL42" si="19">BH42+(BH42*$BF$42)</f>
         <v>5.6891327574024269</v>
       </c>
-      <c r="BJ42" s="190">
-        <f t="shared" si="18"/>
+      <c r="BJ42" s="72">
+        <f t="shared" si="19"/>
         <v>5.7393564560218087</v>
       </c>
-      <c r="BK42" s="190">
-        <f t="shared" si="18"/>
+      <c r="BK42" s="72">
+        <f t="shared" si="19"/>
         <v>5.7900235297583791</v>
       </c>
-      <c r="BL42" s="191">
-        <f t="shared" si="18"/>
+      <c r="BL42" s="179">
+        <f t="shared" si="19"/>
         <v>5.8411378927303712</v>
       </c>
       <c r="BN42" s="72" t="s">
@@ -17710,13 +17701,9 @@
       <c r="AV43" s="108"/>
       <c r="AW43" s="108"/>
       <c r="AX43" s="155"/>
-      <c r="BF43" s="181"/>
-      <c r="BG43" s="189"/>
-      <c r="BH43" s="190"/>
-      <c r="BI43" s="190"/>
-      <c r="BJ43" s="190"/>
-      <c r="BK43" s="190"/>
-      <c r="BL43" s="191"/>
+      <c r="BF43" s="173"/>
+      <c r="BG43" s="178"/>
+      <c r="BL43" s="179"/>
       <c r="BN43" s="72" t="s">
         <v>88</v>
       </c>
@@ -17757,11 +17744,11 @@
       </c>
       <c r="F44" s="108"/>
       <c r="G44" s="108">
-        <f t="shared" ref="G44:G66" si="19">D44/10</f>
+        <f t="shared" ref="G44:G66" si="20">D44/10</f>
         <v>3.5700000000000003</v>
       </c>
       <c r="H44" s="155">
-        <f t="shared" ref="H44:H66" si="20">G44*C44</f>
+        <f t="shared" ref="H44:H66" si="21">G44*C44</f>
         <v>2435.3861700000002</v>
       </c>
       <c r="J44" s="110" t="s">
@@ -17778,11 +17765,11 @@
       </c>
       <c r="N44" s="108"/>
       <c r="O44" s="108">
-        <f t="shared" ref="O44:O66" si="21">L44/10</f>
+        <f t="shared" ref="O44" si="22">L44/10</f>
         <v>3.8200000000000003</v>
       </c>
       <c r="P44" s="155">
-        <f t="shared" ref="P44:P66" si="22">O44*K44</f>
+        <f t="shared" ref="P44" si="23">O44*K44</f>
         <v>2306.9591200000004</v>
       </c>
       <c r="AR44" s="110" t="s">
@@ -17799,11 +17786,11 @@
       </c>
       <c r="AV44" s="108"/>
       <c r="AW44" s="108">
-        <f t="shared" ref="AW44:AW66" si="23">AT44/10</f>
+        <f t="shared" ref="AW44" si="24">AT44/10</f>
         <v>2.7800000000000002</v>
       </c>
       <c r="AX44" s="155">
-        <f t="shared" ref="AX44:AX66" si="24">AW44*AS44</f>
+        <f t="shared" ref="AX44" si="25">AW44*AS44</f>
         <v>2016.2144600000001</v>
       </c>
       <c r="AZ44" s="72">
@@ -17817,38 +17804,38 @@
         <v>3.12</v>
       </c>
       <c r="BD44" s="72">
-        <f t="shared" ref="BD43:BD66" si="25">BC44-BB44</f>
+        <f t="shared" ref="BD44:BD66" si="26">BC44-BB44</f>
         <v>0.20999999999999996</v>
       </c>
       <c r="BE44" s="72">
-        <f t="shared" ref="BE43:BE66" si="26">BD44/2</f>
+        <f t="shared" ref="BE44:BE66" si="27">BD44/2</f>
         <v>0.10499999999999998</v>
       </c>
-      <c r="BF44" s="181">
-        <f t="shared" ref="BF43:BF66" si="27">BE44/BB44/5</f>
+      <c r="BF44" s="173">
+        <f t="shared" ref="BF44:BF66" si="28">BE44/BB44/5</f>
         <v>7.2164948453608225E-3</v>
       </c>
-      <c r="BG44" s="189">
+      <c r="BG44" s="178">
         <f>O44</f>
         <v>3.8200000000000003</v>
       </c>
-      <c r="BH44" s="190">
-        <f t="shared" ref="BH43:BH66" si="28">BG44+(BG44*BF44)</f>
+      <c r="BH44" s="72">
+        <f t="shared" ref="BH44:BH64" si="29">BG44+(BG44*BF44)</f>
         <v>3.8475670103092785</v>
       </c>
-      <c r="BI44" s="190">
+      <c r="BI44" s="72">
         <f>BH44+(BH44*BF44)</f>
         <v>3.8753329578063558</v>
       </c>
-      <c r="BJ44" s="190">
+      <c r="BJ44" s="72">
         <f>BI44+(BI44*BF44)</f>
         <v>3.9032992781204223</v>
       </c>
-      <c r="BK44" s="190">
+      <c r="BK44" s="72">
         <f>BJ44+(BJ44*BF44)</f>
         <v>3.9314674172408788</v>
       </c>
-      <c r="BL44" s="191">
+      <c r="BL44" s="179">
         <f>BK44+(BK44*BF44)</f>
         <v>3.9598388315921018</v>
       </c>
@@ -17905,13 +17892,9 @@
       <c r="AV45" s="108"/>
       <c r="AW45" s="108"/>
       <c r="AX45" s="155"/>
-      <c r="BF45" s="181"/>
-      <c r="BG45" s="189"/>
-      <c r="BH45" s="190"/>
-      <c r="BI45" s="190"/>
-      <c r="BJ45" s="190"/>
-      <c r="BK45" s="190"/>
-      <c r="BL45" s="191"/>
+      <c r="BF45" s="173"/>
+      <c r="BG45" s="178"/>
+      <c r="BL45" s="179"/>
       <c r="BN45" s="72" t="s">
         <v>90</v>
       </c>
@@ -17952,11 +17935,11 @@
       </c>
       <c r="F46" s="108"/>
       <c r="G46" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.34</v>
       </c>
       <c r="H46" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3017.6627599999997</v>
       </c>
       <c r="J46" s="110" t="s">
@@ -17973,11 +17956,11 @@
       </c>
       <c r="N46" s="108"/>
       <c r="O46" s="108">
-        <f t="shared" ref="O46:O66" si="29">L46/10</f>
+        <f t="shared" ref="O46" si="30">L46/10</f>
         <v>4.82</v>
       </c>
       <c r="P46" s="155">
-        <f t="shared" ref="P46:P66" si="30">O46*K46</f>
+        <f t="shared" ref="P46" si="31">O46*K46</f>
         <v>2991.41732</v>
       </c>
       <c r="AR46" s="110" t="s">
@@ -17994,11 +17977,11 @@
       </c>
       <c r="AV46" s="108"/>
       <c r="AW46" s="108">
-        <f t="shared" ref="AW46:AW66" si="31">AT46/10</f>
+        <f t="shared" ref="AW46" si="32">AT46/10</f>
         <v>3.53</v>
       </c>
       <c r="AX46" s="155">
-        <f t="shared" ref="AX46:AX66" si="32">AW46*AS46</f>
+        <f t="shared" ref="AX46" si="33">AW46*AS46</f>
         <v>2962.6054499999996</v>
       </c>
       <c r="AZ46" s="72">
@@ -18012,38 +17995,38 @@
         <v>4</v>
       </c>
       <c r="BD46" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.4700000000000002</v>
       </c>
       <c r="BE46" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.2350000000000001</v>
       </c>
-      <c r="BF46" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF46" s="173">
+        <f t="shared" si="28"/>
         <v>1.3314447592067995E-2</v>
       </c>
-      <c r="BG46" s="189">
+      <c r="BG46" s="178">
         <f>O46</f>
         <v>4.82</v>
       </c>
-      <c r="BH46" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH46" s="72">
+        <f t="shared" si="29"/>
         <v>4.8841756373937679</v>
       </c>
-      <c r="BI46" s="190">
+      <c r="BI46" s="72">
         <f>BH46+(BH46*BF46)</f>
         <v>4.9492057379483025</v>
       </c>
-      <c r="BJ46" s="190">
+      <c r="BJ46" s="72">
         <f>BI46+(BI46*BF46)</f>
         <v>5.0151016783685778</v>
       </c>
-      <c r="BK46" s="190">
+      <c r="BK46" s="72">
         <f>BJ46+(BJ46*BF46)</f>
         <v>5.0818749868341087</v>
       </c>
-      <c r="BL46" s="191">
+      <c r="BL46" s="179">
         <f>BK46+(BK46*BF46)</f>
         <v>5.1495373450157524</v>
       </c>
@@ -18100,13 +18083,9 @@
       <c r="AV47" s="108"/>
       <c r="AW47" s="108"/>
       <c r="AX47" s="155"/>
-      <c r="BF47" s="181"/>
-      <c r="BG47" s="189"/>
-      <c r="BH47" s="190"/>
-      <c r="BI47" s="190"/>
-      <c r="BJ47" s="190"/>
-      <c r="BK47" s="190"/>
-      <c r="BL47" s="191"/>
+      <c r="BF47" s="173"/>
+      <c r="BG47" s="178"/>
+      <c r="BL47" s="179"/>
       <c r="BN47" s="72" t="s">
         <v>92</v>
       </c>
@@ -18147,11 +18126,11 @@
       </c>
       <c r="F48" s="108"/>
       <c r="G48" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.17</v>
       </c>
       <c r="H48" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1645.2395100000001</v>
       </c>
       <c r="J48" s="110" t="s">
@@ -18168,11 +18147,11 @@
       </c>
       <c r="N48" s="108"/>
       <c r="O48" s="108">
-        <f t="shared" ref="O48:O66" si="33">L48/10</f>
+        <f t="shared" ref="O48" si="34">L48/10</f>
         <v>3.4899999999999998</v>
       </c>
       <c r="P48" s="155">
-        <f t="shared" ref="P48:P66" si="34">O48*K48</f>
+        <f t="shared" ref="P48" si="35">O48*K48</f>
         <v>1844.9989699999999</v>
       </c>
       <c r="AR48" s="110" t="s">
@@ -18189,11 +18168,11 @@
       </c>
       <c r="AV48" s="108"/>
       <c r="AW48" s="108">
-        <f t="shared" ref="AW48:AW66" si="35">AT48/10</f>
+        <f t="shared" ref="AW48" si="36">AT48/10</f>
         <v>2.65</v>
       </c>
       <c r="AX48" s="155">
-        <f t="shared" ref="AX48:AX66" si="36">AW48*AS48</f>
+        <f t="shared" ref="AX48" si="37">AW48*AS48</f>
         <v>1220.84175</v>
       </c>
       <c r="AZ48" s="72">
@@ -18207,38 +18186,38 @@
         <v>3.12</v>
       </c>
       <c r="BD48" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.20999999999999996</v>
       </c>
       <c r="BE48" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.10499999999999998</v>
       </c>
-      <c r="BF48" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF48" s="173">
+        <f t="shared" si="28"/>
         <v>7.2164948453608225E-3</v>
       </c>
-      <c r="BG48" s="189">
+      <c r="BG48" s="178">
         <f>O48</f>
         <v>3.4899999999999998</v>
       </c>
-      <c r="BH48" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH48" s="72">
+        <f t="shared" si="29"/>
         <v>3.5151855670103092</v>
       </c>
-      <c r="BI48" s="190">
+      <c r="BI48" s="72">
         <f>BH48+(BH48*BF48)</f>
         <v>3.5405528855351256</v>
       </c>
-      <c r="BJ48" s="190">
+      <c r="BJ48" s="72">
         <f>BI48+(BI48*BF48)</f>
         <v>3.5661032671833173</v>
       </c>
-      <c r="BK48" s="190">
+      <c r="BK48" s="72">
         <f>BJ48+(BJ48*BF48)</f>
         <v>3.5918380330289699</v>
       </c>
-      <c r="BL48" s="191">
+      <c r="BL48" s="179">
         <f>BK48+(BK48*BF48)</f>
         <v>3.6177585136796946</v>
       </c>
@@ -18295,13 +18274,9 @@
       <c r="AV49" s="108"/>
       <c r="AW49" s="108"/>
       <c r="AX49" s="155"/>
-      <c r="BF49" s="181"/>
-      <c r="BG49" s="189"/>
-      <c r="BH49" s="190"/>
-      <c r="BI49" s="190"/>
-      <c r="BJ49" s="190"/>
-      <c r="BK49" s="190"/>
-      <c r="BL49" s="191"/>
+      <c r="BF49" s="173"/>
+      <c r="BG49" s="178"/>
+      <c r="BL49" s="179"/>
       <c r="BN49" s="72" t="s">
         <v>94</v>
       </c>
@@ -18342,11 +18317,11 @@
       </c>
       <c r="F50" s="108"/>
       <c r="G50" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="H50" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5046.9496000000008</v>
       </c>
       <c r="J50" s="110" t="s">
@@ -18363,11 +18338,11 @@
       </c>
       <c r="N50" s="108"/>
       <c r="O50" s="108">
-        <f t="shared" ref="O50:O66" si="37">L50/10</f>
+        <f t="shared" ref="O50" si="38">L50/10</f>
         <v>4.7200000000000006</v>
       </c>
       <c r="P50" s="155">
-        <f t="shared" ref="P50:P66" si="38">O50*K50</f>
+        <f t="shared" ref="P50" si="39">O50*K50</f>
         <v>5265.1788800000004</v>
       </c>
       <c r="AR50" s="110" t="s">
@@ -18384,11 +18359,11 @@
       </c>
       <c r="AV50" s="108"/>
       <c r="AW50" s="108">
-        <f t="shared" ref="AW50:AW66" si="39">AT50/10</f>
+        <f t="shared" ref="AW50" si="40">AT50/10</f>
         <v>3.5200000000000005</v>
       </c>
       <c r="AX50" s="155">
-        <f t="shared" ref="AX50:AX66" si="40">AW50*AS50</f>
+        <f t="shared" ref="AX50" si="41">AW50*AS50</f>
         <v>5336.9113600000001</v>
       </c>
       <c r="AZ50" s="72">
@@ -18402,38 +18377,38 @@
         <v>3.12</v>
       </c>
       <c r="BD50" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.20999999999999996</v>
       </c>
       <c r="BE50" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.10499999999999998</v>
       </c>
-      <c r="BF50" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF50" s="173">
+        <f t="shared" si="28"/>
         <v>7.2164948453608225E-3</v>
       </c>
-      <c r="BG50" s="189">
+      <c r="BG50" s="178">
         <f>O50</f>
         <v>4.7200000000000006</v>
       </c>
-      <c r="BH50" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH50" s="72">
+        <f t="shared" si="29"/>
         <v>4.7540618556701038</v>
       </c>
-      <c r="BI50" s="190">
+      <c r="BI50" s="72">
         <f>BH50+(BH50*BF50)</f>
         <v>4.788369518546074</v>
       </c>
-      <c r="BJ50" s="190">
+      <c r="BJ50" s="72">
         <f>BI50+(BI50*BF50)</f>
         <v>4.8229247624943445</v>
       </c>
-      <c r="BK50" s="190">
+      <c r="BK50" s="72">
         <f>BJ50+(BJ50*BF50)</f>
         <v>4.8577293741824477</v>
       </c>
-      <c r="BL50" s="191">
+      <c r="BL50" s="179">
         <f>BK50+(BK50*BF50)</f>
         <v>4.8927851531713928</v>
       </c>
@@ -18490,13 +18465,9 @@
       <c r="AV51" s="108"/>
       <c r="AW51" s="108"/>
       <c r="AX51" s="155"/>
-      <c r="BF51" s="181"/>
-      <c r="BG51" s="189"/>
-      <c r="BH51" s="190"/>
-      <c r="BI51" s="190"/>
-      <c r="BJ51" s="190"/>
-      <c r="BK51" s="190"/>
-      <c r="BL51" s="191"/>
+      <c r="BF51" s="173"/>
+      <c r="BG51" s="178"/>
+      <c r="BL51" s="179"/>
       <c r="BN51" s="72" t="s">
         <v>96</v>
       </c>
@@ -18537,11 +18508,11 @@
       </c>
       <c r="F52" s="108"/>
       <c r="G52" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.3</v>
       </c>
       <c r="H52" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>832.92</v>
       </c>
       <c r="J52" s="110" t="s">
@@ -18558,11 +18529,11 @@
       </c>
       <c r="N52" s="108"/>
       <c r="O52" s="108">
-        <f t="shared" ref="O52:O66" si="41">L52/10</f>
+        <f t="shared" ref="O52" si="42">L52/10</f>
         <v>3.6</v>
       </c>
       <c r="P52" s="155">
-        <f t="shared" ref="P52:P66" si="42">O52*K52</f>
+        <f t="shared" ref="P52" si="43">O52*K52</f>
         <v>710.07839999999999</v>
       </c>
       <c r="AR52" s="110" t="s">
@@ -18579,11 +18550,11 @@
       </c>
       <c r="AV52" s="108"/>
       <c r="AW52" s="108">
-        <f t="shared" ref="AW52:AW66" si="43">AT52/10</f>
+        <f t="shared" ref="AW52" si="44">AT52/10</f>
         <v>3.6</v>
       </c>
       <c r="AX52" s="155">
-        <f t="shared" ref="AX52:AX66" si="44">AW52*AS52</f>
+        <f t="shared" ref="AX52" si="45">AW52*AS52</f>
         <v>2926.4004</v>
       </c>
       <c r="AZ52" s="72">
@@ -18597,38 +18568,38 @@
         <v>3.03</v>
       </c>
       <c r="BD52" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.19999999999999973</v>
       </c>
       <c r="BE52" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.9999999999999867E-2</v>
       </c>
-      <c r="BF52" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF52" s="173">
+        <f t="shared" si="28"/>
         <v>7.0671378091872695E-3</v>
       </c>
-      <c r="BG52" s="189">
+      <c r="BG52" s="178">
         <f>O52</f>
         <v>3.6</v>
       </c>
-      <c r="BH52" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH52" s="72">
+        <f t="shared" si="29"/>
         <v>3.6254416961130742</v>
       </c>
-      <c r="BI52" s="190">
+      <c r="BI52" s="72">
         <f>BH52+(BH52*BF52)</f>
         <v>3.6510631921986789</v>
       </c>
-      <c r="BJ52" s="190">
+      <c r="BJ52" s="72">
         <f>BI52+(BI52*BF52)</f>
         <v>3.6768657589279981</v>
       </c>
-      <c r="BK52" s="190">
+      <c r="BK52" s="72">
         <f>BJ52+(BJ52*BF52)</f>
         <v>3.7028506759522242</v>
       </c>
-      <c r="BL52" s="191">
+      <c r="BL52" s="179">
         <f>BK52+(BK52*BF52)</f>
         <v>3.7290192319660207</v>
       </c>
@@ -18661,24 +18632,20 @@
       <c r="AV53" s="108"/>
       <c r="AW53" s="108"/>
       <c r="AX53" s="155"/>
-      <c r="BF53" s="181"/>
-      <c r="BG53" s="189"/>
-      <c r="BH53" s="190"/>
-      <c r="BI53" s="190"/>
-      <c r="BJ53" s="190"/>
-      <c r="BK53" s="190"/>
-      <c r="BL53" s="191"/>
-      <c r="BP53" s="195" t="s">
+      <c r="BF53" s="173"/>
+      <c r="BG53" s="178"/>
+      <c r="BL53" s="179"/>
+      <c r="BP53" s="183" t="s">
         <v>208</v>
       </c>
-      <c r="BQ53" s="195"/>
-      <c r="BR53" s="195"/>
-      <c r="BS53" s="195"/>
-      <c r="BT53" s="195"/>
-      <c r="BU53" s="195"/>
-      <c r="BV53" s="195"/>
-    </row>
-    <row r="54" spans="2:74" ht="15">
+      <c r="BQ53" s="183"/>
+      <c r="BR53" s="183"/>
+      <c r="BS53" s="183"/>
+      <c r="BT53" s="183"/>
+      <c r="BU53" s="183"/>
+      <c r="BV53" s="183"/>
+    </row>
+    <row r="54" spans="2:74" ht="14.4">
       <c r="B54" s="110" t="s">
         <v>109</v>
       </c>
@@ -18693,11 +18660,11 @@
       </c>
       <c r="F54" s="115"/>
       <c r="G54" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.3599999999999994</v>
       </c>
       <c r="H54" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9396.7107199999991</v>
       </c>
       <c r="J54" s="110" t="s">
@@ -18714,11 +18681,11 @@
       </c>
       <c r="N54" s="115"/>
       <c r="O54" s="108">
-        <f t="shared" ref="O54:O66" si="45">L54/10</f>
+        <f t="shared" ref="O54" si="46">L54/10</f>
         <v>7.85</v>
       </c>
       <c r="P54" s="155">
-        <f t="shared" ref="P54:P66" si="46">O54*K54</f>
+        <f t="shared" ref="P54" si="47">O54*K54</f>
         <v>10533.224199999999</v>
       </c>
       <c r="AR54" s="110" t="s">
@@ -18735,11 +18702,11 @@
       </c>
       <c r="AV54" s="115"/>
       <c r="AW54" s="108">
-        <f t="shared" ref="AW54:AW66" si="47">AT54/10</f>
+        <f t="shared" ref="AW54" si="48">AT54/10</f>
         <v>4.71</v>
       </c>
       <c r="AX54" s="155">
-        <f t="shared" ref="AX54:AX66" si="48">AW54*AS54</f>
+        <f t="shared" ref="AX54" si="49">AW54*AS54</f>
         <v>3157.0894499999999</v>
       </c>
       <c r="AZ54" s="72">
@@ -18753,38 +18720,38 @@
         <v>8.2100000000000009</v>
       </c>
       <c r="BD54" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.2600000000000007</v>
       </c>
       <c r="BE54" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.63000000000000034</v>
       </c>
-      <c r="BF54" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF54" s="173">
+        <f t="shared" si="28"/>
         <v>1.8129496402877705E-2</v>
       </c>
-      <c r="BG54" s="189">
+      <c r="BG54" s="178">
         <f>O54</f>
         <v>7.85</v>
       </c>
-      <c r="BH54" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH54" s="72">
+        <f t="shared" si="29"/>
         <v>7.9923165467625896</v>
       </c>
-      <c r="BI54" s="190">
+      <c r="BI54" s="72">
         <f>BH54+(BH54*BF54)</f>
         <v>8.1372132208477819</v>
       </c>
-      <c r="BJ54" s="190">
+      <c r="BJ54" s="72">
         <f>BI54+(BI54*BF54)</f>
         <v>8.284736798664591</v>
       </c>
-      <c r="BK54" s="190">
+      <c r="BK54" s="72">
         <f>BJ54+(BJ54*BF54)</f>
         <v>8.434934904654769</v>
       </c>
-      <c r="BL54" s="191">
+      <c r="BL54" s="179">
         <f>BK54+(BK54*BF54)</f>
         <v>8.5878560266672146</v>
       </c>
@@ -18838,13 +18805,9 @@
       <c r="AV55" s="108"/>
       <c r="AW55" s="108"/>
       <c r="AX55" s="155"/>
-      <c r="BF55" s="181"/>
-      <c r="BG55" s="189"/>
-      <c r="BH55" s="190"/>
-      <c r="BI55" s="190"/>
-      <c r="BJ55" s="190"/>
-      <c r="BK55" s="190"/>
-      <c r="BL55" s="191"/>
+      <c r="BF55" s="173"/>
+      <c r="BG55" s="178"/>
+      <c r="BL55" s="179"/>
       <c r="BN55" s="72" t="s">
         <v>85</v>
       </c>
@@ -18853,23 +18816,23 @@
         <v>5.59</v>
       </c>
       <c r="BR55" s="72">
-        <f t="shared" ref="BR55:BV55" si="49">BH42</f>
+        <f t="shared" ref="BR55:BV55" si="50">BH42</f>
         <v>5.6393485540334858</v>
       </c>
       <c r="BS55" s="72">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5.6891327574024269</v>
       </c>
       <c r="BT55" s="72">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5.7393564560218087</v>
       </c>
       <c r="BU55" s="72">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5.7900235297583791</v>
       </c>
       <c r="BV55" s="72">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5.8411378927303712</v>
       </c>
     </row>
@@ -18888,11 +18851,11 @@
       </c>
       <c r="F56" s="108"/>
       <c r="G56" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.52</v>
       </c>
       <c r="H56" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>142.27351999999999</v>
       </c>
       <c r="J56" s="110" t="s">
@@ -18909,11 +18872,11 @@
       </c>
       <c r="N56" s="108"/>
       <c r="O56" s="108">
-        <f t="shared" ref="O56:O66" si="50">L56/10</f>
+        <f t="shared" ref="O56" si="51">L56/10</f>
         <v>1.55</v>
       </c>
       <c r="P56" s="155">
-        <f t="shared" ref="P56:P66" si="51">O56*K56</f>
+        <f t="shared" ref="P56" si="52">O56*K56</f>
         <v>119.37635</v>
       </c>
       <c r="AR56" s="110" t="s">
@@ -18930,11 +18893,11 @@
       </c>
       <c r="AV56" s="108"/>
       <c r="AW56" s="108">
-        <f t="shared" ref="AW56:AW66" si="52">AT56/10</f>
+        <f t="shared" ref="AW56" si="53">AT56/10</f>
         <v>1.0900000000000001</v>
       </c>
       <c r="AX56" s="155">
-        <f t="shared" ref="AX56:AX66" si="53">AW56*AS56</f>
+        <f t="shared" ref="AX56" si="54">AW56*AS56</f>
         <v>63.796610000000008</v>
       </c>
       <c r="AZ56" s="72">
@@ -18948,38 +18911,38 @@
         <v>3.03</v>
       </c>
       <c r="BD56" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.19999999999999973</v>
       </c>
       <c r="BE56" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.9999999999999867E-2</v>
       </c>
-      <c r="BF56" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF56" s="173">
+        <f t="shared" si="28"/>
         <v>7.0671378091872695E-3</v>
       </c>
-      <c r="BG56" s="189">
+      <c r="BG56" s="178">
         <f>O56</f>
         <v>1.55</v>
       </c>
-      <c r="BH56" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH56" s="72">
+        <f t="shared" si="29"/>
         <v>1.5609540636042403</v>
       </c>
-      <c r="BI56" s="190">
+      <c r="BI56" s="72">
         <f>BH56+(BH56*BF56)</f>
         <v>1.5719855410855423</v>
       </c>
-      <c r="BJ56" s="190">
+      <c r="BJ56" s="72">
         <f>BI56+(BI56*BF56)</f>
         <v>1.5830949795384437</v>
       </c>
-      <c r="BK56" s="190">
+      <c r="BK56" s="72">
         <f>BJ56+(BJ56*BF56)</f>
         <v>1.5942829299238743</v>
       </c>
-      <c r="BL56" s="191">
+      <c r="BL56" s="179">
         <f>BK56+(BK56*BF56)</f>
         <v>1.6055499470964811</v>
       </c>
@@ -18991,23 +18954,23 @@
         <v>4.82</v>
       </c>
       <c r="BR56" s="72">
-        <f t="shared" ref="BR56:BV56" si="54">BH46</f>
+        <f t="shared" ref="BR56:BV56" si="55">BH46</f>
         <v>4.8841756373937679</v>
       </c>
       <c r="BS56" s="72">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>4.9492057379483025</v>
       </c>
       <c r="BT56" s="72">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>5.0151016783685778</v>
       </c>
       <c r="BU56" s="72">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>5.0818749868341087</v>
       </c>
       <c r="BV56" s="72">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>5.1495373450157524</v>
       </c>
     </row>
@@ -19039,13 +19002,9 @@
       <c r="AV57" s="108"/>
       <c r="AW57" s="108"/>
       <c r="AX57" s="155"/>
-      <c r="BF57" s="181"/>
-      <c r="BG57" s="189"/>
-      <c r="BH57" s="190"/>
-      <c r="BI57" s="190"/>
-      <c r="BJ57" s="190"/>
-      <c r="BK57" s="190"/>
-      <c r="BL57" s="191"/>
+      <c r="BF57" s="173"/>
+      <c r="BG57" s="178"/>
+      <c r="BL57" s="179"/>
       <c r="BN57" s="72" t="s">
         <v>87</v>
       </c>
@@ -19054,23 +19013,23 @@
         <v>7.85</v>
       </c>
       <c r="BR57" s="72">
-        <f t="shared" ref="BR57:BV57" si="55">BH54</f>
+        <f t="shared" ref="BR57:BV57" si="56">BH54</f>
         <v>7.9923165467625896</v>
       </c>
       <c r="BS57" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>8.1372132208477819</v>
       </c>
       <c r="BT57" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>8.284736798664591</v>
       </c>
       <c r="BU57" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>8.434934904654769</v>
       </c>
       <c r="BV57" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>8.5878560266672146</v>
       </c>
     </row>
@@ -19089,11 +19048,11 @@
       </c>
       <c r="F58" s="108"/>
       <c r="G58" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.89</v>
       </c>
       <c r="H58" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43.052309999999999</v>
       </c>
       <c r="J58" s="110" t="s">
@@ -19110,11 +19069,11 @@
       </c>
       <c r="N58" s="108"/>
       <c r="O58" s="108">
-        <f t="shared" ref="O58:O66" si="56">L58/10</f>
+        <f t="shared" ref="O58" si="57">L58/10</f>
         <v>2.19</v>
       </c>
       <c r="P58" s="155">
-        <f t="shared" ref="P58:P66" si="57">O58*K58</f>
+        <f t="shared" ref="P58" si="58">O58*K58</f>
         <v>37.619820000000004</v>
       </c>
       <c r="AR58" s="110" t="s">
@@ -19131,11 +19090,11 @@
       </c>
       <c r="AV58" s="108"/>
       <c r="AW58" s="108">
-        <f t="shared" ref="AW58:AW66" si="58">AT58/10</f>
+        <f t="shared" ref="AW58" si="59">AT58/10</f>
         <v>1.28</v>
       </c>
       <c r="AX58" s="155">
-        <f t="shared" ref="AX58:AX66" si="59">AW58*AS58</f>
+        <f t="shared" ref="AX58" si="60">AW58*AS58</f>
         <v>35.851520000000001</v>
       </c>
       <c r="AZ58" s="72">
@@ -19149,38 +19108,38 @@
         <v>3.03</v>
       </c>
       <c r="BD58" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.19999999999999973</v>
       </c>
       <c r="BE58" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.9999999999999867E-2</v>
       </c>
-      <c r="BF58" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF58" s="173">
+        <f t="shared" si="28"/>
         <v>7.0671378091872695E-3</v>
       </c>
-      <c r="BG58" s="189">
+      <c r="BG58" s="178">
         <f>O58</f>
         <v>2.19</v>
       </c>
-      <c r="BH58" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH58" s="72">
+        <f t="shared" si="29"/>
         <v>2.2054770318021202</v>
       </c>
-      <c r="BI58" s="190">
+      <c r="BI58" s="72">
         <f>BH58+(BH58*BF58)</f>
         <v>2.221063441920863</v>
       </c>
-      <c r="BJ58" s="190">
+      <c r="BJ58" s="72">
         <f>BI58+(BI58*BF58)</f>
         <v>2.2367600033478654</v>
       </c>
-      <c r="BK58" s="190">
+      <c r="BK58" s="72">
         <f>BJ58+(BJ58*BF58)</f>
         <v>2.2525674945376029</v>
       </c>
-      <c r="BL58" s="191">
+      <c r="BL58" s="179">
         <f>BK58+(BK58*BF58)</f>
         <v>2.2684866994459956</v>
       </c>
@@ -19192,27 +19151,27 @@
         <v>3.6</v>
       </c>
       <c r="BR58" s="72">
-        <f t="shared" ref="BR58:BV58" si="60">BH52</f>
+        <f t="shared" ref="BR58:BV58" si="61">BH52</f>
         <v>3.6254416961130742</v>
       </c>
       <c r="BS58" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3.6510631921986789</v>
       </c>
       <c r="BT58" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3.6768657589279981</v>
       </c>
       <c r="BU58" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3.7028506759522242</v>
       </c>
       <c r="BV58" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3.7290192319660207</v>
       </c>
     </row>
-    <row r="59" spans="2:74" ht="14.25">
+    <row r="59" spans="2:74" ht="15.6">
       <c r="B59" s="112" t="s">
         <v>117</v>
       </c>
@@ -19240,13 +19199,9 @@
       <c r="AV59" s="108"/>
       <c r="AW59" s="108"/>
       <c r="AX59" s="155"/>
-      <c r="BF59" s="181"/>
-      <c r="BG59" s="189"/>
-      <c r="BH59" s="190"/>
-      <c r="BI59" s="190"/>
-      <c r="BJ59" s="190"/>
-      <c r="BK59" s="190"/>
-      <c r="BL59" s="191"/>
+      <c r="BF59" s="173"/>
+      <c r="BG59" s="178"/>
+      <c r="BL59" s="179"/>
       <c r="BN59" s="72" t="s">
         <v>89</v>
       </c>
@@ -19255,23 +19210,23 @@
         <v>4.7200000000000006</v>
       </c>
       <c r="BR59" s="72">
-        <f t="shared" ref="BR59:BV59" si="61">BH50</f>
+        <f t="shared" ref="BR59:BV59" si="62">BH50</f>
         <v>4.7540618556701038</v>
       </c>
       <c r="BS59" s="72">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.788369518546074</v>
       </c>
       <c r="BT59" s="72">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.8229247624943445</v>
       </c>
       <c r="BU59" s="72">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.8577293741824477</v>
       </c>
       <c r="BV59" s="72">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.8927851531713928</v>
       </c>
     </row>
@@ -19290,11 +19245,11 @@
       </c>
       <c r="F60" s="118"/>
       <c r="G60" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>30.2</v>
       </c>
       <c r="H60" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5923.7602000000006</v>
       </c>
       <c r="J60" s="116" t="s">
@@ -19311,11 +19266,11 @@
       </c>
       <c r="N60" s="118"/>
       <c r="O60" s="108">
-        <f t="shared" ref="O60:O66" si="62">L60/10</f>
+        <f t="shared" ref="O60" si="63">L60/10</f>
         <v>32.700000000000003</v>
       </c>
       <c r="P60" s="155">
-        <f t="shared" ref="P60:P66" si="63">O60*K60</f>
+        <f t="shared" ref="P60" si="64">O60*K60</f>
         <v>7004.0130000000008</v>
       </c>
       <c r="AR60" s="116" t="s">
@@ -19332,11 +19287,11 @@
       </c>
       <c r="AV60" s="118"/>
       <c r="AW60" s="108">
-        <f t="shared" ref="AW60:AW66" si="64">AT60/10</f>
+        <f t="shared" ref="AW60" si="65">AT60/10</f>
         <v>21</v>
       </c>
       <c r="AX60" s="155">
-        <f t="shared" ref="AX60:AX66" si="65">AW60*AS60</f>
+        <f t="shared" ref="AX60" si="66">AW60*AS60</f>
         <v>6307.4549999999999</v>
       </c>
       <c r="AZ60" s="72">
@@ -19350,38 +19305,38 @@
         <v>24.63</v>
       </c>
       <c r="BD60" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.59</v>
       </c>
       <c r="BE60" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.2949999999999999</v>
       </c>
-      <c r="BF60" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF60" s="173">
+        <f t="shared" si="28"/>
         <v>1.17513611615245E-2</v>
       </c>
-      <c r="BG60" s="189">
+      <c r="BG60" s="178">
         <f>O60</f>
         <v>32.700000000000003</v>
       </c>
-      <c r="BH60" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH60" s="72">
+        <f t="shared" si="29"/>
         <v>33.084269509981851</v>
       </c>
-      <c r="BI60" s="190">
+      <c r="BI60" s="72">
         <f>BH60+(BH60*BF60)</f>
         <v>33.473054709758863</v>
       </c>
-      <c r="BJ60" s="190">
+      <c r="BJ60" s="72">
         <f>BI60+(BI60*BF60)</f>
         <v>33.866408664832704</v>
       </c>
-      <c r="BK60" s="190">
+      <c r="BK60" s="72">
         <f>BJ60+(BJ60*BF60)</f>
         <v>34.264385064296938</v>
       </c>
-      <c r="BL60" s="191">
+      <c r="BL60" s="179">
         <f>BK60+(BK60*BF60)</f>
         <v>34.66703822816504</v>
       </c>
@@ -19393,23 +19348,23 @@
         <v>3.4899999999999998</v>
       </c>
       <c r="BR60" s="72">
-        <f t="shared" ref="BR60:BV60" si="66">BH48</f>
+        <f t="shared" ref="BR60:BV60" si="67">BH48</f>
         <v>3.5151855670103092</v>
       </c>
       <c r="BS60" s="72">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3.5405528855351256</v>
       </c>
       <c r="BT60" s="72">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3.5661032671833173</v>
       </c>
       <c r="BU60" s="72">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3.5918380330289699</v>
       </c>
       <c r="BV60" s="72">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3.6177585136796946</v>
       </c>
     </row>
@@ -19441,13 +19396,9 @@
       <c r="AV61" s="108"/>
       <c r="AW61" s="108"/>
       <c r="AX61" s="155"/>
-      <c r="BF61" s="181"/>
-      <c r="BG61" s="189"/>
-      <c r="BH61" s="190"/>
-      <c r="BI61" s="190"/>
-      <c r="BJ61" s="190"/>
-      <c r="BK61" s="190"/>
-      <c r="BL61" s="191"/>
+      <c r="BF61" s="173"/>
+      <c r="BG61" s="178"/>
+      <c r="BL61" s="179"/>
       <c r="BN61" s="72" t="s">
         <v>91</v>
       </c>
@@ -19456,23 +19407,23 @@
         <v>3.8200000000000003</v>
       </c>
       <c r="BR61" s="72">
-        <f t="shared" ref="BR61:BV61" si="67">BH44</f>
+        <f t="shared" ref="BR61:BV61" si="68">BH44</f>
         <v>3.8475670103092785</v>
       </c>
       <c r="BS61" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3.8753329578063558</v>
       </c>
       <c r="BT61" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3.9032992781204223</v>
       </c>
       <c r="BU61" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3.9314674172408788</v>
       </c>
       <c r="BV61" s="72">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3.9598388315921018</v>
       </c>
     </row>
@@ -19491,11 +19442,11 @@
       </c>
       <c r="F62" s="108"/>
       <c r="G62" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.1399999999999997</v>
       </c>
       <c r="H62" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3468.2807199999997</v>
       </c>
       <c r="J62" s="110" t="s">
@@ -19512,11 +19463,11 @@
       </c>
       <c r="N62" s="108"/>
       <c r="O62" s="108">
-        <f t="shared" ref="O62:O66" si="68">L62/10</f>
+        <f t="shared" ref="O62" si="69">L62/10</f>
         <v>3.22</v>
       </c>
       <c r="P62" s="155">
-        <f t="shared" ref="P62:P66" si="69">O62*K62</f>
+        <f t="shared" ref="P62" si="70">O62*K62</f>
         <v>3862.9631600000007</v>
       </c>
       <c r="AR62" s="110" t="s">
@@ -19533,11 +19484,11 @@
       </c>
       <c r="AV62" s="108"/>
       <c r="AW62" s="108">
-        <f t="shared" ref="AW62:AW66" si="70">AT62/10</f>
+        <f t="shared" ref="AW62" si="71">AT62/10</f>
         <v>2.7800000000000002</v>
       </c>
       <c r="AX62" s="155">
-        <f t="shared" ref="AX62:AX66" si="71">AW62*AS62</f>
+        <f t="shared" ref="AX62" si="72">AW62*AS62</f>
         <v>2763.9594000000002</v>
       </c>
       <c r="AZ62" s="72">
@@ -19551,38 +19502,38 @@
         <v>3.1</v>
       </c>
       <c r="BD62" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.33000000000000007</v>
       </c>
       <c r="BE62" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.16500000000000004</v>
       </c>
-      <c r="BF62" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF62" s="173">
+        <f t="shared" si="28"/>
         <v>1.1913357400722024E-2</v>
       </c>
-      <c r="BG62" s="189">
+      <c r="BG62" s="178">
         <f>O62</f>
         <v>3.22</v>
       </c>
-      <c r="BH62" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH62" s="72">
+        <f t="shared" si="29"/>
         <v>3.2583610108303249</v>
       </c>
-      <c r="BI62" s="190">
+      <c r="BI62" s="72">
         <f>BH62+(BH62*BF62)</f>
         <v>3.2971790300929245</v>
       </c>
-      <c r="BJ62" s="190">
+      <c r="BJ62" s="72">
         <f>BI62+(BI62*BF62)</f>
         <v>3.3364595022925876</v>
       </c>
-      <c r="BK62" s="190">
+      <c r="BK62" s="72">
         <f>BJ62+(BJ62*BF62)</f>
         <v>3.3762079367964342</v>
       </c>
-      <c r="BL62" s="191">
+      <c r="BL62" s="179">
         <f>BK62+(BK62*BF62)</f>
         <v>3.4164299086066445</v>
       </c>
@@ -19594,23 +19545,23 @@
         <v>1.87</v>
       </c>
       <c r="BR62" s="72">
-        <f t="shared" ref="BR62:BV62" si="72">(BH56+BH58)/2</f>
+        <f t="shared" ref="BR62:BV62" si="73">(BH56+BH58)/2</f>
         <v>1.8832155477031802</v>
       </c>
       <c r="BS62" s="72">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1.8965244915032027</v>
       </c>
       <c r="BT62" s="72">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1.9099274914431545</v>
       </c>
       <c r="BU62" s="72">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1.9234252122307387</v>
       </c>
       <c r="BV62" s="72">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>1.9370183232712384</v>
       </c>
     </row>
@@ -19642,13 +19593,9 @@
       <c r="AV63" s="121"/>
       <c r="AW63" s="108"/>
       <c r="AX63" s="155"/>
-      <c r="BF63" s="181"/>
-      <c r="BG63" s="189"/>
-      <c r="BH63" s="190"/>
-      <c r="BI63" s="190"/>
-      <c r="BJ63" s="190"/>
-      <c r="BK63" s="190"/>
-      <c r="BL63" s="191"/>
+      <c r="BF63" s="173"/>
+      <c r="BG63" s="178"/>
+      <c r="BL63" s="179"/>
       <c r="BN63" s="72" t="s">
         <v>93</v>
       </c>
@@ -19657,23 +19604,23 @@
         <v>18.600000000000001</v>
       </c>
       <c r="BR63" s="72">
-        <f t="shared" ref="BR63:BV63" si="73">BH66</f>
+        <f t="shared" ref="BR63:BV63" si="74">BH66</f>
         <v>18.962337662337664</v>
       </c>
       <c r="BS63" s="72">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>19.331733850565019</v>
       </c>
       <c r="BT63" s="72">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>19.70832606843317</v>
       </c>
       <c r="BU63" s="72">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>20.092254498337713</v>
       </c>
       <c r="BV63" s="72">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>20.483662053500137</v>
       </c>
     </row>
@@ -19692,11 +19639,11 @@
       </c>
       <c r="F64" s="121"/>
       <c r="G64" s="108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.4899999999999998</v>
       </c>
       <c r="H64" s="155">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>513.29357999999991</v>
       </c>
       <c r="J64" s="122" t="s">
@@ -19713,11 +19660,11 @@
       </c>
       <c r="N64" s="121"/>
       <c r="O64" s="108">
-        <f t="shared" ref="O64:O66" si="74">L64/10</f>
+        <f t="shared" ref="O64" si="75">L64/10</f>
         <v>2.5300000000000002</v>
       </c>
       <c r="P64" s="155">
-        <f t="shared" ref="P64:P66" si="75">O64*K64</f>
+        <f t="shared" ref="P64" si="76">O64*K64</f>
         <v>540.8052100000001</v>
       </c>
       <c r="AR64" s="122" t="s">
@@ -19734,11 +19681,11 @@
       </c>
       <c r="AV64" s="121"/>
       <c r="AW64" s="108">
-        <f t="shared" ref="AW64:AW66" si="76">AT64/10</f>
+        <f t="shared" ref="AW64" si="77">AT64/10</f>
         <v>1.8800000000000001</v>
       </c>
       <c r="AX64" s="155">
-        <f t="shared" ref="AX64:AX66" si="77">AW64*AS64</f>
+        <f t="shared" ref="AX64" si="78">AW64*AS64</f>
         <v>171.14204000000001</v>
       </c>
       <c r="AZ64" s="72">
@@ -19752,38 +19699,38 @@
         <v>2.76</v>
       </c>
       <c r="BD64" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.44999999999999973</v>
       </c>
       <c r="BE64" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.22499999999999987</v>
       </c>
-      <c r="BF64" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF64" s="173">
+        <f t="shared" si="28"/>
         <v>1.9480519480519466E-2</v>
       </c>
-      <c r="BG64" s="189">
+      <c r="BG64" s="178">
         <f>O64</f>
         <v>2.5300000000000002</v>
       </c>
-      <c r="BH64" s="190">
-        <f t="shared" si="28"/>
+      <c r="BH64" s="72">
+        <f t="shared" si="29"/>
         <v>2.5792857142857146</v>
       </c>
-      <c r="BI64" s="190">
+      <c r="BI64" s="72">
         <f>BH64+(BH64*BF64)</f>
         <v>2.6295315398886832</v>
       </c>
-      <c r="BJ64" s="190">
+      <c r="BJ64" s="72">
         <f>BI64+(BI64*BF64)</f>
         <v>2.6807561802761248</v>
       </c>
-      <c r="BK64" s="190">
+      <c r="BK64" s="72">
         <f>BJ64+(BJ64*BF64)</f>
         <v>2.7329787032685169</v>
       </c>
-      <c r="BL64" s="191">
+      <c r="BL64" s="179">
         <f>BK64+(BK64*BF64)</f>
         <v>2.7862185481373842</v>
       </c>
@@ -19795,23 +19742,23 @@
         <v>2.5300000000000002</v>
       </c>
       <c r="BR64" s="72">
-        <f t="shared" ref="BR64:BV64" si="78">BH64</f>
+        <f t="shared" ref="BR64:BV64" si="79">BH64</f>
         <v>2.5792857142857146</v>
       </c>
       <c r="BS64" s="72">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.6295315398886832</v>
       </c>
       <c r="BT64" s="72">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.6807561802761248</v>
       </c>
       <c r="BU64" s="72">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.7329787032685169</v>
       </c>
       <c r="BV64" s="72">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.7862185481373842</v>
       </c>
     </row>
@@ -19855,13 +19802,9 @@
       <c r="AV65" s="121"/>
       <c r="AW65" s="108"/>
       <c r="AX65" s="155"/>
-      <c r="BF65" s="181"/>
-      <c r="BG65" s="189"/>
-      <c r="BH65" s="190"/>
-      <c r="BI65" s="190"/>
-      <c r="BJ65" s="190"/>
-      <c r="BK65" s="190"/>
-      <c r="BL65" s="191"/>
+      <c r="BF65" s="173"/>
+      <c r="BG65" s="178"/>
+      <c r="BL65" s="179"/>
       <c r="BN65" s="72" t="s">
         <v>95</v>
       </c>
@@ -19870,27 +19813,27 @@
         <v>32.700000000000003</v>
       </c>
       <c r="BR65" s="72">
-        <f t="shared" ref="BR65:BV65" si="79">BH60</f>
+        <f t="shared" ref="BR65:BV65" si="80">BH60</f>
         <v>33.084269509981851</v>
       </c>
       <c r="BS65" s="72">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>33.473054709758863</v>
       </c>
       <c r="BT65" s="72">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>33.866408664832704</v>
       </c>
       <c r="BU65" s="72">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>34.264385064296938</v>
       </c>
       <c r="BV65" s="72">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>34.66703822816504</v>
       </c>
     </row>
-    <row r="66" spans="2:74" ht="13.5" thickBot="1">
+    <row r="66" spans="2:74" ht="13.8" thickBot="1">
       <c r="B66" s="124" t="s">
         <v>121</v>
       </c>
@@ -19905,11 +19848,11 @@
       </c>
       <c r="F66" s="127"/>
       <c r="G66" s="154">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.990000000000002</v>
       </c>
       <c r="H66" s="156">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>779.12891000000002</v>
       </c>
       <c r="J66" s="124" t="s">
@@ -19926,11 +19869,11 @@
       </c>
       <c r="N66" s="127"/>
       <c r="O66" s="154">
-        <f t="shared" ref="O66" si="80">L66/10</f>
+        <f t="shared" ref="O66" si="81">L66/10</f>
         <v>18.600000000000001</v>
       </c>
       <c r="P66" s="156">
-        <f t="shared" ref="P66" si="81">O66*K66</f>
+        <f t="shared" ref="P66" si="82">O66*K66</f>
         <v>703.32180000000005</v>
       </c>
       <c r="R66" s="72" t="s">
@@ -19950,7 +19893,7 @@
         <f>U66-T66</f>
         <v>143</v>
       </c>
-      <c r="W66" s="181">
+      <c r="W66" s="173">
         <f>V66/T66</f>
         <v>1.4920701168614357E-2</v>
       </c>
@@ -19968,11 +19911,11 @@
       </c>
       <c r="AV66" s="127"/>
       <c r="AW66" s="154">
-        <f t="shared" ref="AW66" si="82">AT66/10</f>
+        <f t="shared" ref="AW66" si="83">AT66/10</f>
         <v>16</v>
       </c>
       <c r="AX66" s="156">
-        <f t="shared" ref="AX66" si="83">AW66*AS66</f>
+        <f t="shared" ref="AX66" si="84">AW66*AS66</f>
         <v>593.52</v>
       </c>
       <c r="AZ66" s="72">
@@ -19988,38 +19931,38 @@
         <v>18.600000000000001</v>
       </c>
       <c r="BD66" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.6000000000000014</v>
       </c>
       <c r="BE66" s="72">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.3000000000000007</v>
       </c>
-      <c r="BF66" s="181">
-        <f t="shared" si="27"/>
+      <c r="BF66" s="173">
+        <f t="shared" si="28"/>
         <v>1.6250000000000007E-2</v>
       </c>
-      <c r="BG66" s="192">
+      <c r="BG66" s="180">
         <f>O66</f>
         <v>18.600000000000001</v>
       </c>
-      <c r="BH66" s="193">
+      <c r="BH66" s="181">
         <f>BG66+(BG66*BF64)</f>
         <v>18.962337662337664</v>
       </c>
-      <c r="BI66" s="193">
+      <c r="BI66" s="181">
         <f>BH66+(BH66*BF64)</f>
         <v>19.331733850565019</v>
       </c>
-      <c r="BJ66" s="193">
+      <c r="BJ66" s="181">
         <f>BI66+(BI66*BF64)</f>
         <v>19.70832606843317</v>
       </c>
-      <c r="BK66" s="193">
+      <c r="BK66" s="181">
         <f>BJ66+(BJ66*BF64)</f>
         <v>20.092254498337713</v>
       </c>
-      <c r="BL66" s="194">
+      <c r="BL66" s="182">
         <f>BK66+(BK66*BF64)</f>
         <v>20.483662053500137</v>
       </c>
@@ -20031,23 +19974,23 @@
         <v>3.22</v>
       </c>
       <c r="BR66" s="72">
-        <f t="shared" ref="BR66:BV66" si="84">BH62</f>
+        <f t="shared" ref="BR66:BV66" si="85">BH62</f>
         <v>3.2583610108303249</v>
       </c>
       <c r="BS66" s="72">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>3.2971790300929245</v>
       </c>
       <c r="BT66" s="72">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>3.3364595022925876</v>
       </c>
       <c r="BU66" s="72">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>3.3762079367964342</v>
       </c>
       <c r="BV66" s="72">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>3.4164299086066445</v>
       </c>
     </row>
@@ -20059,21 +20002,21 @@
         <v>3295</v>
       </c>
       <c r="T67" s="72">
-        <f t="shared" ref="T67:T73" si="85">(S67+U67)/2</f>
+        <f t="shared" ref="T67:T73" si="86">(S67+U67)/2</f>
         <v>3645.5</v>
       </c>
       <c r="U67" s="72">
         <v>3996</v>
       </c>
       <c r="V67" s="72">
-        <f t="shared" ref="V67:V73" si="86">U67-T67</f>
+        <f t="shared" ref="V67:V73" si="87">U67-T67</f>
         <v>350.5</v>
       </c>
-      <c r="W67" s="181">
-        <f t="shared" ref="W67:W73" si="87">V67/T67</f>
+      <c r="W67" s="173">
+        <f t="shared" ref="W67:W73" si="88">V67/T67</f>
         <v>9.6145933342477022E-2</v>
       </c>
-      <c r="BF67" s="181"/>
+      <c r="BF67" s="173"/>
     </row>
     <row r="68" spans="2:74">
       <c r="R68" s="72" t="s">
@@ -20083,29 +20026,29 @@
         <v>7463</v>
       </c>
       <c r="T68" s="72">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>7010.5</v>
       </c>
       <c r="U68" s="72">
         <v>6558</v>
       </c>
       <c r="V68" s="72">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-452.5</v>
       </c>
-      <c r="W68" s="181">
-        <f t="shared" si="87"/>
+      <c r="W68" s="173">
+        <f t="shared" si="88"/>
         <v>-6.4546038085728549E-2</v>
       </c>
-      <c r="BP68" s="195" t="s">
+      <c r="BP68" s="183" t="s">
         <v>204</v>
       </c>
-      <c r="BQ68" s="195"/>
-      <c r="BR68" s="195"/>
-      <c r="BS68" s="195"/>
-      <c r="BT68" s="195"/>
-      <c r="BU68" s="195"/>
-      <c r="BV68" s="195"/>
+      <c r="BQ68" s="183"/>
+      <c r="BR68" s="183"/>
+      <c r="BS68" s="183"/>
+      <c r="BT68" s="183"/>
+      <c r="BU68" s="183"/>
+      <c r="BV68" s="183"/>
     </row>
     <row r="69" spans="2:74">
       <c r="R69" s="72" t="s">
@@ -20115,18 +20058,18 @@
         <v>4482</v>
       </c>
       <c r="T69" s="72">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4703</v>
       </c>
       <c r="U69" s="72">
         <v>4924</v>
       </c>
       <c r="V69" s="72">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>221</v>
       </c>
-      <c r="W69" s="181">
-        <f t="shared" si="87"/>
+      <c r="W69" s="173">
+        <f t="shared" si="88"/>
         <v>4.6991282160323194E-2</v>
       </c>
       <c r="BP69" s="72">
@@ -20159,18 +20102,18 @@
         <v>2691</v>
       </c>
       <c r="T70" s="72">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2329</v>
       </c>
       <c r="U70" s="72">
         <v>1967</v>
       </c>
       <c r="V70" s="72">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-362</v>
       </c>
-      <c r="W70" s="181">
-        <f t="shared" si="87"/>
+      <c r="W70" s="173">
+        <f t="shared" si="88"/>
         <v>-0.15543151567196223</v>
       </c>
       <c r="BN70" s="72" t="s">
@@ -20181,23 +20124,23 @@
         <v>2414.1109999999999</v>
       </c>
       <c r="BR70" s="72">
-        <f t="shared" ref="BR70:BV70" si="88">BR40/BR55</f>
+        <f t="shared" ref="BR70:BV70" si="89">BR40/BR55</f>
         <v>2428.6907322480297</v>
       </c>
       <c r="BS70" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2190.4247839195932</v>
       </c>
       <c r="BT70" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1956.1428704727355</v>
       </c>
       <c r="BU70" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1725.7935106684015</v>
       </c>
       <c r="BV70" s="72">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1499.325819186625</v>
       </c>
     </row>
@@ -20209,45 +20152,45 @@
         <v>2799</v>
       </c>
       <c r="T71" s="72">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3024</v>
       </c>
       <c r="U71" s="72">
         <v>3249</v>
       </c>
       <c r="V71" s="72">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>225</v>
       </c>
-      <c r="W71" s="181">
-        <f t="shared" si="87"/>
+      <c r="W71" s="173">
+        <f t="shared" si="88"/>
         <v>7.4404761904761904E-2</v>
       </c>
       <c r="BN71" s="72" t="s">
         <v>86</v>
       </c>
       <c r="BQ71" s="72">
-        <f t="shared" ref="BQ71:BV71" si="89">BQ41/BQ56</f>
+        <f t="shared" ref="BQ71:BV71" si="90">BQ41/BQ56</f>
         <v>620.62599999999998</v>
       </c>
       <c r="BR71" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>671.35790636676734</v>
       </c>
       <c r="BS71" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>601.65783341846043</v>
       </c>
       <c r="BT71" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>533.67350141039867</v>
       </c>
       <c r="BU71" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>467.37185585348521</v>
       </c>
       <c r="BV71" s="72">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>402.72041468099223</v>
       </c>
     </row>
@@ -20259,45 +20202,45 @@
         <v>452</v>
       </c>
       <c r="T72" s="72">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>501.5</v>
       </c>
       <c r="U72" s="72">
         <v>551</v>
       </c>
       <c r="V72" s="72">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>49.5</v>
       </c>
-      <c r="W72" s="181">
-        <f t="shared" si="87"/>
+      <c r="W72" s="173">
+        <f t="shared" si="88"/>
         <v>9.8703888334995021E-2</v>
       </c>
       <c r="BN72" s="72" t="s">
         <v>87</v>
       </c>
       <c r="BQ72" s="72">
-        <f t="shared" ref="BQ72:BV72" si="90">BQ42/BQ57</f>
+        <f t="shared" ref="BQ72:BV72" si="91">BQ42/BQ57</f>
         <v>1341.8119999999999</v>
       </c>
       <c r="BR72" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>1379.8494899338393</v>
       </c>
       <c r="BS72" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>1084.3560131831975</v>
       </c>
       <c r="BT72" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>798.94852710191037</v>
       </c>
       <c r="BU72" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>523.36153020267045</v>
       </c>
       <c r="BV72" s="72">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>257.33577835231188</v>
       </c>
     </row>
@@ -20309,45 +20252,45 @@
         <v>6145</v>
       </c>
       <c r="T73" s="72">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>5166</v>
       </c>
       <c r="U73" s="72">
         <v>4187</v>
       </c>
       <c r="V73" s="72">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-979</v>
       </c>
-      <c r="W73" s="181">
-        <f t="shared" si="87"/>
+      <c r="W73" s="173">
+        <f t="shared" si="88"/>
         <v>-0.18950832365466511</v>
       </c>
       <c r="BN73" s="72" t="s">
         <v>88</v>
       </c>
       <c r="BQ73" s="72">
-        <f t="shared" ref="BQ73:BV73" si="91">BQ43/BQ58</f>
+        <f t="shared" ref="BQ73:BV73" si="92">BQ43/BQ58</f>
         <v>197.244</v>
       </c>
       <c r="BR73" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>165.41704109737631</v>
       </c>
       <c r="BS73" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>263.45817585049758</v>
       </c>
       <c r="BT73" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>360.11514856258532</v>
       </c>
       <c r="BU73" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>455.40255794324582</v>
       </c>
       <c r="BV73" s="72">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>549.3348659722509</v>
       </c>
     </row>
@@ -20356,27 +20299,27 @@
         <v>89</v>
       </c>
       <c r="BQ74" s="72">
-        <f t="shared" ref="BQ74:BV74" si="92">BQ44/BQ59</f>
+        <f t="shared" ref="BQ74:BV74" si="93">BQ44/BQ59</f>
         <v>1115.5039999999999</v>
       </c>
       <c r="BR74" s="72">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>1036.0261588958863</v>
       </c>
       <c r="BS74" s="72">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>966.49993336724128</v>
       </c>
       <c r="BT74" s="72">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>897.9168058806622</v>
       </c>
       <c r="BU74" s="72">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>830.26683131141351</v>
       </c>
       <c r="BV74" s="72">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>763.54015863102313</v>
       </c>
     </row>
@@ -20385,27 +20328,27 @@
         <v>90</v>
       </c>
       <c r="BQ75" s="72">
-        <f t="shared" ref="BQ75:BV75" si="93">BQ45/BQ60</f>
+        <f t="shared" ref="BQ75:BV75" si="94">BQ45/BQ60</f>
         <v>528.65300000000002</v>
       </c>
       <c r="BR75" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>490.98733575028598</v>
       </c>
       <c r="BS75" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>425.9450577823394</v>
       </c>
       <c r="BT75" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>361.80960391150643</v>
       </c>
       <c r="BU75" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>298.57131862351798</v>
       </c>
       <c r="BV75" s="72">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>236.22063821246601</v>
       </c>
     </row>
@@ -20414,27 +20357,27 @@
         <v>91</v>
       </c>
       <c r="BQ76" s="72">
-        <f t="shared" ref="BQ76:BV76" si="94">BQ46/BQ61</f>
+        <f t="shared" ref="BQ76:BV76" si="95">BQ46/BQ61</f>
         <v>603.91600000000005</v>
       </c>
       <c r="BR76" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>560.88796972110197</v>
       </c>
       <c r="BS76" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>508.69901723221244</v>
       </c>
       <c r="BT76" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>457.22911778584614</v>
       </c>
       <c r="BU76" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>406.47064673273252</v>
       </c>
       <c r="BV76" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>356.41605176959928</v>
       </c>
     </row>
@@ -20443,27 +20386,27 @@
         <v>92</v>
       </c>
       <c r="BQ77" s="72">
-        <f t="shared" ref="BQ77:BV77" si="95">BQ47/BQ62</f>
+        <f t="shared" ref="BQ77:BV77" si="96">BQ47/BQ62</f>
         <v>83.955171122994656</v>
       </c>
       <c r="BR77" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>70.408306422449712</v>
       </c>
       <c r="BS77" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>61.630596536094274</v>
       </c>
       <c r="BT77" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>52.972615256014684</v>
       </c>
       <c r="BU77" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>44.43311444713418</v>
       </c>
       <c r="BV77" s="72">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>36.010857595915716</v>
       </c>
     </row>
@@ -20472,27 +20415,27 @@
         <v>93</v>
       </c>
       <c r="BQ78" s="72">
-        <f t="shared" ref="BQ78:BV78" si="96">BQ48/BQ63</f>
+        <f t="shared" ref="BQ78:BV78" si="97">BQ48/BQ63</f>
         <v>37.813000000000002</v>
       </c>
       <c r="BR78" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>40.751431082548528</v>
       </c>
       <c r="BS78" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>32.192782712549409</v>
       </c>
       <c r="BT78" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>23.946337023583844</v>
       </c>
       <c r="BU78" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>16.003287691249081</v>
       </c>
       <c r="BV78" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>8.355050945138796</v>
       </c>
     </row>
@@ -20501,31 +20444,31 @@
         <v>94</v>
       </c>
       <c r="BQ79" s="72">
-        <f t="shared" ref="BQ79:BV79" si="97">BQ49/BQ64</f>
+        <f t="shared" ref="BQ79:BV79" si="98">BQ49/BQ64</f>
         <v>213.75700000000003</v>
       </c>
       <c r="BR79" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>230.36795953540653</v>
       </c>
       <c r="BS79" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>237.18848046999307</v>
       </c>
       <c r="BT79" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>243.66423113575738</v>
       </c>
       <c r="BU79" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>249.80589711446012</v>
       </c>
       <c r="BV79" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>255.62388150639833</v>
       </c>
     </row>
-    <row r="80" spans="2:74" ht="13.5" thickBot="1">
+    <row r="80" spans="2:74" ht="13.8" thickBot="1">
       <c r="B80" s="72" t="s">
         <v>122</v>
       </c>
@@ -20533,31 +20476,31 @@
         <v>95</v>
       </c>
       <c r="BQ80" s="72">
-        <f t="shared" ref="BQ80:BV80" si="98">BQ50/BQ65</f>
+        <f t="shared" ref="BQ80:BV80" si="99">BQ50/BQ65</f>
         <v>214.19</v>
       </c>
       <c r="BR80" s="72">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>171.58287976712933</v>
       </c>
       <c r="BS80" s="72">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>183.72261604026733</v>
       </c>
       <c r="BT80" s="72">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>195.55720195494121</v>
       </c>
       <c r="BU80" s="72">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>207.09208836123113</v>
       </c>
       <c r="BV80" s="72">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>218.33264065375658</v>
       </c>
     </row>
-    <row r="81" spans="2:74" ht="15.75">
+    <row r="81" spans="2:74" ht="15.6">
       <c r="B81" s="73" t="s">
         <v>181</v>
       </c>
@@ -20574,27 +20517,27 @@
         <v>96</v>
       </c>
       <c r="BQ81" s="72">
-        <f t="shared" ref="BQ81:BV81" si="99">BQ51/BQ66</f>
+        <f t="shared" ref="BQ81:BV81" si="100">BQ51/BQ66</f>
         <v>1199.6780000000001</v>
       </c>
       <c r="BR81" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1273.7649389896881</v>
       </c>
       <c r="BS81" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1153.646594834069</v>
       </c>
       <c r="BT81" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1036.1800299712315</v>
       </c>
       <c r="BU81" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>921.31945418420378</v>
       </c>
       <c r="BV81" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>809.01978788941472</v>
       </c>
     </row>
@@ -20624,23 +20567,23 @@
         <v>8571.2591711229943</v>
       </c>
       <c r="BR83" s="72">
-        <f t="shared" ref="BR83:BV83" si="100">SUM(BR70:BR81)</f>
+        <f t="shared" ref="BR83:BV83" si="101">SUM(BR70:BR81)</f>
         <v>8520.092149810509</v>
       </c>
       <c r="BS83" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>7709.4218853465136</v>
       </c>
       <c r="BT83" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>6918.1559904671713</v>
       </c>
       <c r="BU83" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>6145.8920931337461</v>
       </c>
       <c r="BV83" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>5392.2359453958925</v>
       </c>
     </row>
@@ -20675,28 +20618,28 @@
       <c r="I85" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="BQ85" s="181">
+      <c r="BQ85" s="173">
         <f>BQ83/$BQ$83</f>
         <v>1</v>
       </c>
-      <c r="BR85" s="181">
-        <f t="shared" ref="BR85:BV85" si="101">BR83/$BQ$83</f>
+      <c r="BR85" s="173">
+        <f t="shared" ref="BR85:BV85" si="102">BR83/$BQ$83</f>
         <v>0.99403039620072753</v>
       </c>
-      <c r="BS85" s="181">
-        <f t="shared" si="101"/>
+      <c r="BS85" s="173">
+        <f t="shared" si="102"/>
         <v>0.89945032945917047</v>
       </c>
-      <c r="BT85" s="181">
-        <f t="shared" si="101"/>
+      <c r="BT85" s="173">
+        <f t="shared" si="102"/>
         <v>0.80713415057787408</v>
       </c>
-      <c r="BU85" s="181">
-        <f t="shared" si="101"/>
+      <c r="BU85" s="173">
+        <f t="shared" si="102"/>
         <v>0.71703491522454099</v>
       </c>
-      <c r="BV85" s="181">
-        <f t="shared" si="101"/>
+      <c r="BV85" s="173">
+        <f t="shared" si="102"/>
         <v>0.62910662689591845</v>
       </c>
     </row>
@@ -20732,7 +20675,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="88" spans="2:74" ht="13.5" thickBot="1">
+    <row r="88" spans="2:74" ht="13.8" thickBot="1">
       <c r="B88" s="92" t="s">
         <v>135</v>
       </c>
@@ -20820,7 +20763,7 @@
       <c r="F93" s="88"/>
       <c r="I93" s="100"/>
     </row>
-    <row r="94" spans="2:74" ht="13.5" thickBot="1">
+    <row r="94" spans="2:74" ht="13.8" thickBot="1">
       <c r="B94" s="101" t="s">
         <v>143</v>
       </c>
@@ -20840,12 +20783,12 @@
       <c r="H94" s="103"/>
       <c r="I94" s="104"/>
     </row>
-    <row r="97" spans="2:9" ht="13.5" thickBot="1">
+    <row r="97" spans="2:9" ht="13.8" thickBot="1">
       <c r="B97" s="72" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="98" spans="2:9" ht="15.75">
+    <row r="98" spans="2:9" ht="15.6">
       <c r="B98" s="73" t="s">
         <v>203</v>
       </c>
@@ -20945,7 +20888,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="105" spans="2:9" ht="13.5" thickBot="1">
+    <row r="105" spans="2:9" ht="13.8" thickBot="1">
       <c r="B105" s="92" t="s">
         <v>135</v>
       </c>
@@ -21025,7 +20968,7 @@
       <c r="E110" s="88"/>
       <c r="I110" s="100"/>
     </row>
-    <row r="111" spans="2:9" ht="13.5" thickBot="1">
+    <row r="111" spans="2:9" ht="13.8" thickBot="1">
       <c r="B111" s="101" t="s">
         <v>143</v>
       </c>
@@ -21108,23 +21051,23 @@
         <v>4052.27</v>
       </c>
       <c r="N119" s="72">
-        <f t="shared" ref="N119:N123" si="102">$N$116*N133</f>
+        <f t="shared" ref="N119:N123" si="103">$N$116*N133</f>
         <v>3819.5152641105351</v>
       </c>
       <c r="O119" s="72">
-        <f t="shared" ref="O119:O123" si="103">$O$116*O133</f>
+        <f t="shared" ref="O119:O123" si="104">$O$116*O133</f>
         <v>3205.3777836527279</v>
       </c>
       <c r="P119" s="72">
-        <f t="shared" ref="P119:P123" si="104">$P$116*P133</f>
+        <f t="shared" ref="P119:P123" si="105">$P$116*P133</f>
         <v>2764.815719387308</v>
       </c>
       <c r="Q119" s="72">
-        <f t="shared" ref="Q119:Q123" si="105">$Q$116*Q133</f>
+        <f t="shared" ref="Q119:Q123" si="106">$Q$116*Q133</f>
         <v>2407.9262734357599</v>
       </c>
       <c r="R119" s="72">
-        <f t="shared" ref="R119:R124" si="106">$R$116*R133</f>
+        <f t="shared" ref="R119:R123" si="107">$R$116*R133</f>
         <v>2093.2382440706288</v>
       </c>
     </row>
@@ -21139,23 +21082,23 @@
         <v>267.89400000000001</v>
       </c>
       <c r="N120" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>252.50667457095099</v>
       </c>
       <c r="O120" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>211.90628363210342</v>
       </c>
       <c r="P120" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>182.78089622101771</v>
       </c>
       <c r="Q120" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>159.18707319497449</v>
       </c>
       <c r="R120" s="72">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>138.38316947218644</v>
       </c>
     </row>
@@ -21170,23 +21113,23 @@
         <v>9225.2209999999995</v>
       </c>
       <c r="N121" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>8695.3417280420745</v>
       </c>
       <c r="O121" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>7297.2231471956711</v>
       </c>
       <c r="P121" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>6294.2587822681853</v>
       </c>
       <c r="Q121" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>5481.7798478757122</v>
       </c>
       <c r="R121" s="72">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>4765.3748163877262</v>
       </c>
     </row>
@@ -21201,23 +21144,23 @@
         <v>64.180000000000007</v>
       </c>
       <c r="N122" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>60.49362200707607</v>
       </c>
       <c r="O122" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>50.766890201006369</v>
       </c>
       <c r="P122" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>43.789252164904468</v>
       </c>
       <c r="Q122" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>38.136824108242308</v>
       </c>
       <c r="R122" s="72">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>33.152783626079447</v>
       </c>
     </row>
@@ -21232,23 +21175,23 @@
         <v>272993.99099999998</v>
       </c>
       <c r="N123" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>257313.73171949401</v>
       </c>
       <c r="O123" s="72">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>215940.41705564849</v>
       </c>
       <c r="P123" s="72">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>186260.55954195483</v>
       </c>
       <c r="Q123" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>162217.57272318608</v>
       </c>
       <c r="R123" s="72">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>141017.61786916296</v>
       </c>
     </row>
@@ -21265,31 +21208,31 @@
     </row>
     <row r="126" spans="11:18">
       <c r="M126" s="72">
-        <f t="shared" ref="M126:M130" si="107">M119/$M$116</f>
+        <f t="shared" ref="M126:M130" si="108">M119/$M$116</f>
         <v>0.47277417694383839</v>
       </c>
     </row>
     <row r="127" spans="11:18">
       <c r="M127" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>3.1254917702471116E-2</v>
       </c>
     </row>
     <row r="128" spans="11:18">
       <c r="M128" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>1.0762970545891595</v>
       </c>
     </row>
     <row r="129" spans="13:18">
       <c r="M129" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>7.4878146511105012E-3</v>
       </c>
     </row>
     <row r="130" spans="13:18">
       <c r="M130" s="72">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>31.849928411887316</v>
       </c>
     </row>
@@ -21321,136 +21264,147 @@
     </row>
     <row r="133" spans="13:18">
       <c r="M133" s="72">
-        <f t="shared" ref="M133:M137" si="108">M126/58</f>
+        <f t="shared" ref="M133:M137" si="109">M126/58</f>
         <v>8.1512789128247998E-3</v>
       </c>
       <c r="N133" s="72">
-        <f t="shared" ref="N133:N137" si="109">M133*55</f>
+        <f t="shared" ref="N133:N137" si="110">M133*55</f>
         <v>0.44832034020536399</v>
       </c>
       <c r="O133" s="72">
-        <f t="shared" ref="O133:O137" si="110">M133*51</f>
+        <f t="shared" ref="O133:O137" si="111">M133*51</f>
         <v>0.41571522455406479</v>
       </c>
       <c r="P133" s="72">
-        <f t="shared" ref="P133:P137" si="111">M133*49</f>
+        <f t="shared" ref="P133:P137" si="112">M133*49</f>
         <v>0.39941266672841519</v>
       </c>
       <c r="Q133" s="72">
-        <f t="shared" ref="Q133:Q137" si="112">M133*48</f>
+        <f t="shared" ref="Q133:Q137" si="113">M133*48</f>
         <v>0.39126138781559039</v>
       </c>
       <c r="R133" s="72">
-        <f t="shared" ref="R133:R137" si="113">M133*47.5</f>
+        <f t="shared" ref="R133:R137" si="114">M133*47.5</f>
         <v>0.38718574835917796</v>
       </c>
     </row>
     <row r="134" spans="13:18">
       <c r="M134" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>5.3887789142191577E-4</v>
       </c>
       <c r="N134" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>2.9638284028205366E-2</v>
       </c>
       <c r="O134" s="72">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>2.7482772462517704E-2</v>
       </c>
       <c r="P134" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.6405016679673873E-2</v>
       </c>
       <c r="Q134" s="72">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.5866138788251957E-2</v>
       </c>
       <c r="R134" s="72">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>2.5596699842540999E-2</v>
       </c>
     </row>
     <row r="135" spans="13:18">
       <c r="M135" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>1.8556845768778613E-2</v>
       </c>
       <c r="N135" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>1.0206265172828237</v>
       </c>
       <c r="O135" s="72">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.94639913420770927</v>
       </c>
       <c r="P135" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.90928544267015199</v>
       </c>
       <c r="Q135" s="72">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.8907285969013734</v>
       </c>
       <c r="R135" s="72">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.88145017401698411</v>
       </c>
     </row>
     <row r="136" spans="13:18">
       <c r="M136" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>1.2910025260535346E-4</v>
       </c>
       <c r="N136" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>7.1005138932944403E-3</v>
       </c>
       <c r="O136" s="72">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>6.584112882873026E-3</v>
       </c>
       <c r="P136" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>6.3259123776623193E-3</v>
       </c>
       <c r="Q136" s="72">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>6.196812125056966E-3</v>
       </c>
       <c r="R136" s="72">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>6.1322619987542893E-3</v>
       </c>
     </row>
     <row r="137" spans="13:18">
       <c r="M137" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.54913669675667787</v>
       </c>
       <c r="N137" s="72">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>30.202518321617283</v>
       </c>
       <c r="O137" s="72">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>28.005971534590572</v>
       </c>
       <c r="P137" s="72">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>26.907698141077216</v>
       </c>
       <c r="Q137" s="72">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>26.358561444320536</v>
       </c>
       <c r="R137" s="72">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>26.083993095942198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="AR37:AW37"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="M39:M40"/>
     <mergeCell ref="BP38:BV38"/>
     <mergeCell ref="BP53:BV53"/>
     <mergeCell ref="BP68:BV68"/>
@@ -21458,17 +21412,6 @@
     <mergeCell ref="AS39:AS40"/>
     <mergeCell ref="AT39:AT40"/>
     <mergeCell ref="AU39:AU40"/>
-    <mergeCell ref="AR37:AW37"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21481,6 +21424,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -21489,15 +21441,6 @@
     <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21744,26 +21687,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/VT_Model_DMD.xlsx
+++ b/VT_Model_DMD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1072" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8302B44-54B7-4675-A980-0A9BCEC895F4}"/>
+  <xr:revisionPtr revIDLastSave="1079" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CDBBA23-34F2-40F6-A98A-F3F51960EB4C}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="151" r:id="rId1"/>
@@ -6249,30 +6249,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="14" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="59" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="60" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="61" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="14" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="143" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="59" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="60" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="61" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -9456,16 +9456,16 @@
                   <c:v>710.07839999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>599.7098380420781</c:v>
+                  <c:v>596.70453781512606</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>961.90244853155855</c:v>
+                  <c:v>959.64847336134449</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1324.0950590210391</c:v>
+                  <c:v>1322.5924089075629</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1686.2876695105197</c:v>
+                  <c:v>1685.5363444537813</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2048.4802799999998</c:v>
@@ -9832,16 +9832,16 @@
                   <c:v>156.99617000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132.59401734220697</c:v>
+                  <c:v>131.92955462184875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>116.88393575665523</c:v>
+                  <c:v>116.38558871638656</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>101.1738541711035</c:v>
+                  <c:v>100.84162281092438</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>85.463772585551766</c:v>
+                  <c:v>85.29765690546219</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>69.753691000000003</c:v>
@@ -14404,15 +14404,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77812A59-879F-495C-8D6A-A1B5ADCA0B5F}">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="3" width="4" style="51" customWidth="1"/>
-    <col min="4" max="9" width="14.33203125" style="51" customWidth="1"/>
+    <col min="4" max="9" width="14.28515625" style="51" customWidth="1"/>
     <col min="10" max="12" width="4" style="51" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="51"/>
+    <col min="13" max="16384" width="9.140625" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="22.65" customHeight="1">
+    <row r="1" spans="1:15" ht="22.7" customHeight="1">
       <c r="A1" s="52"/>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -14426,7 +14426,7 @@
       <c r="K1" s="52"/>
       <c r="L1" s="52"/>
     </row>
-    <row r="2" spans="1:15" ht="22.65" customHeight="1">
+    <row r="2" spans="1:15" ht="22.7" customHeight="1">
       <c r="A2" s="52"/>
       <c r="B2" s="50"/>
       <c r="C2" s="49"/>
@@ -14440,7 +14440,7 @@
       <c r="K2" s="48"/>
       <c r="L2" s="52"/>
     </row>
-    <row r="3" spans="1:15" ht="22.65" customHeight="1">
+    <row r="3" spans="1:15" ht="22.7" customHeight="1">
       <c r="A3" s="52"/>
       <c r="B3" s="47"/>
       <c r="C3" s="46"/>
@@ -14833,7 +14833,7 @@
       <c r="K38" s="43"/>
       <c r="L38" s="52"/>
     </row>
-    <row r="39" spans="1:12" ht="22.65" customHeight="1">
+    <row r="39" spans="1:12" ht="22.7" customHeight="1">
       <c r="A39" s="52"/>
       <c r="B39" s="32"/>
       <c r="C39" s="31"/>
@@ -14847,7 +14847,7 @@
       <c r="K39" s="30"/>
       <c r="L39" s="52"/>
     </row>
-    <row r="40" spans="1:12" ht="22.65" customHeight="1">
+    <row r="40" spans="1:12" ht="22.7" customHeight="1">
       <c r="A40" s="52"/>
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
@@ -14861,8 +14861,8 @@
       <c r="K40" s="52"/>
       <c r="L40" s="52"/>
     </row>
-    <row r="48" spans="1:12" ht="59.4" customHeight="1"/>
-    <row r="49" ht="64.2" customHeight="1"/>
+    <row r="48" spans="1:12" ht="59.45" customHeight="1"/>
+    <row r="49" ht="64.150000000000006" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="D32:E32"/>
@@ -14885,17 +14885,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBF481A-D2DF-4904-8542-3490B02494C7}">
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="4" style="29" customWidth="1"/>
-    <col min="4" max="4" width="23.44140625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" style="29" customWidth="1"/>
-    <col min="6" max="6" width="58.109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="34.85546875" style="29" customWidth="1"/>
+    <col min="6" max="6" width="58.140625" style="29" customWidth="1"/>
     <col min="7" max="9" width="4" style="29" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="29"/>
+    <col min="10" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.65" customHeight="1">
+    <row r="1" spans="1:9" ht="22.7" customHeight="1">
       <c r="A1" s="52"/>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -14906,7 +14906,7 @@
       <c r="H1" s="52"/>
       <c r="I1" s="52"/>
     </row>
-    <row r="2" spans="1:9" ht="22.65" customHeight="1">
+    <row r="2" spans="1:9" ht="22.7" customHeight="1">
       <c r="A2" s="52"/>
       <c r="B2" s="50"/>
       <c r="C2" s="49"/>
@@ -14917,7 +14917,7 @@
       <c r="H2" s="48"/>
       <c r="I2" s="52"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="52"/>
       <c r="B3" s="47"/>
       <c r="C3" s="46"/>
@@ -14928,7 +14928,7 @@
       <c r="H3" s="43"/>
       <c r="I3" s="52"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9" ht="18.75">
       <c r="A4" s="52"/>
       <c r="B4" s="47"/>
       <c r="C4" s="42"/>
@@ -14941,7 +14941,7 @@
       <c r="H4" s="43"/>
       <c r="I4" s="52"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9" ht="18.75">
       <c r="A5" s="52"/>
       <c r="B5" s="47"/>
       <c r="C5" s="42"/>
@@ -14952,7 +14952,7 @@
       <c r="H5" s="43"/>
       <c r="I5" s="52"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9" ht="18.75">
       <c r="A6" s="52"/>
       <c r="B6" s="47"/>
       <c r="C6" s="42"/>
@@ -14965,7 +14965,7 @@
       <c r="H6" s="43"/>
       <c r="I6" s="52"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9" ht="18.75">
       <c r="A7" s="52"/>
       <c r="B7" s="47"/>
       <c r="C7" s="42"/>
@@ -14976,7 +14976,7 @@
       <c r="H7" s="43"/>
       <c r="I7" s="52"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9" ht="18.75">
       <c r="A8" s="52"/>
       <c r="B8" s="47"/>
       <c r="C8" s="42"/>
@@ -14993,7 +14993,7 @@
       <c r="H8" s="43"/>
       <c r="I8" s="52"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" ht="18.75">
       <c r="A9" s="52"/>
       <c r="B9" s="47"/>
       <c r="C9" s="42"/>
@@ -15010,7 +15010,7 @@
       <c r="H9" s="43"/>
       <c r="I9" s="52"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9" ht="18.75">
       <c r="A10" s="52"/>
       <c r="B10" s="47"/>
       <c r="C10" s="42"/>
@@ -15027,7 +15027,7 @@
       <c r="H10" s="43"/>
       <c r="I10" s="52"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9" ht="18.75">
       <c r="A11" s="52"/>
       <c r="B11" s="47"/>
       <c r="C11" s="42"/>
@@ -15044,7 +15044,7 @@
       <c r="H11" s="43"/>
       <c r="I11" s="52"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9" ht="18.75">
       <c r="A12" s="52"/>
       <c r="B12" s="47"/>
       <c r="C12" s="42"/>
@@ -15061,7 +15061,7 @@
       <c r="H12" s="43"/>
       <c r="I12" s="52"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9" ht="18.75">
       <c r="A13" s="52"/>
       <c r="B13" s="47"/>
       <c r="C13" s="42"/>
@@ -15078,7 +15078,7 @@
       <c r="H13" s="43"/>
       <c r="I13" s="52"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9" ht="18.75">
       <c r="A14" s="52"/>
       <c r="B14" s="47"/>
       <c r="C14" s="42"/>
@@ -15095,7 +15095,7 @@
       <c r="H14" s="43"/>
       <c r="I14" s="52"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9" ht="18.75">
       <c r="A15" s="52"/>
       <c r="B15" s="47"/>
       <c r="C15" s="42"/>
@@ -15110,7 +15110,7 @@
       <c r="H15" s="43"/>
       <c r="I15" s="52"/>
     </row>
-    <row r="16" spans="1:9" ht="18">
+    <row r="16" spans="1:9" ht="18.75">
       <c r="A16" s="52"/>
       <c r="B16" s="47"/>
       <c r="C16" s="42"/>
@@ -15125,7 +15125,7 @@
       <c r="H16" s="43"/>
       <c r="I16" s="52"/>
     </row>
-    <row r="17" spans="1:9" ht="18">
+    <row r="17" spans="1:9" ht="18.75">
       <c r="A17" s="52"/>
       <c r="B17" s="47"/>
       <c r="C17" s="42"/>
@@ -15140,7 +15140,7 @@
       <c r="H17" s="43"/>
       <c r="I17" s="52"/>
     </row>
-    <row r="18" spans="1:9" ht="18">
+    <row r="18" spans="1:9" ht="18.75">
       <c r="A18" s="52"/>
       <c r="B18" s="47"/>
       <c r="C18" s="42"/>
@@ -15155,7 +15155,7 @@
       <c r="H18" s="43"/>
       <c r="I18" s="52"/>
     </row>
-    <row r="19" spans="1:9" ht="18">
+    <row r="19" spans="1:9" ht="18.75">
       <c r="A19" s="52"/>
       <c r="B19" s="47"/>
       <c r="C19" s="42"/>
@@ -15166,7 +15166,7 @@
       <c r="H19" s="43"/>
       <c r="I19" s="52"/>
     </row>
-    <row r="20" spans="1:9" ht="18">
+    <row r="20" spans="1:9" ht="18.75">
       <c r="A20" s="52"/>
       <c r="B20" s="47"/>
       <c r="C20" s="42"/>
@@ -15177,7 +15177,7 @@
       <c r="H20" s="43"/>
       <c r="I20" s="52"/>
     </row>
-    <row r="21" spans="1:9" ht="18">
+    <row r="21" spans="1:9" ht="18.75">
       <c r="A21" s="52"/>
       <c r="B21" s="47"/>
       <c r="C21" s="42"/>
@@ -15188,7 +15188,7 @@
       <c r="H21" s="43"/>
       <c r="I21" s="52"/>
     </row>
-    <row r="22" spans="1:9" ht="18">
+    <row r="22" spans="1:9" ht="18.75">
       <c r="A22" s="52"/>
       <c r="B22" s="47"/>
       <c r="C22" s="42"/>
@@ -15199,7 +15199,7 @@
       <c r="H22" s="43"/>
       <c r="I22" s="52"/>
     </row>
-    <row r="23" spans="1:9" ht="18">
+    <row r="23" spans="1:9" ht="18.75">
       <c r="A23" s="52"/>
       <c r="B23" s="47"/>
       <c r="C23" s="42"/>
@@ -15210,7 +15210,7 @@
       <c r="H23" s="43"/>
       <c r="I23" s="52"/>
     </row>
-    <row r="24" spans="1:9" ht="18">
+    <row r="24" spans="1:9" ht="18.75">
       <c r="A24" s="52"/>
       <c r="B24" s="47"/>
       <c r="C24" s="42"/>
@@ -15221,7 +15221,7 @@
       <c r="H24" s="43"/>
       <c r="I24" s="52"/>
     </row>
-    <row r="25" spans="1:9" ht="18">
+    <row r="25" spans="1:9" ht="18.75">
       <c r="A25" s="52"/>
       <c r="B25" s="47"/>
       <c r="C25" s="42"/>
@@ -15232,7 +15232,7 @@
       <c r="H25" s="43"/>
       <c r="I25" s="52"/>
     </row>
-    <row r="26" spans="1:9" ht="18">
+    <row r="26" spans="1:9" ht="18.75">
       <c r="A26" s="52"/>
       <c r="B26" s="47"/>
       <c r="C26" s="42"/>
@@ -15243,7 +15243,7 @@
       <c r="H26" s="43"/>
       <c r="I26" s="52"/>
     </row>
-    <row r="27" spans="1:9" ht="18">
+    <row r="27" spans="1:9" ht="18.75">
       <c r="A27" s="52"/>
       <c r="B27" s="47"/>
       <c r="C27" s="42"/>
@@ -15254,7 +15254,7 @@
       <c r="H27" s="43"/>
       <c r="I27" s="52"/>
     </row>
-    <row r="28" spans="1:9" ht="18">
+    <row r="28" spans="1:9" ht="18.75">
       <c r="A28" s="52"/>
       <c r="B28" s="47"/>
       <c r="C28" s="42"/>
@@ -15265,7 +15265,7 @@
       <c r="H28" s="43"/>
       <c r="I28" s="52"/>
     </row>
-    <row r="29" spans="1:9" ht="18">
+    <row r="29" spans="1:9" ht="18.75">
       <c r="A29" s="52"/>
       <c r="B29" s="47"/>
       <c r="C29" s="42"/>
@@ -15276,7 +15276,7 @@
       <c r="H29" s="43"/>
       <c r="I29" s="52"/>
     </row>
-    <row r="30" spans="1:9" ht="18">
+    <row r="30" spans="1:9" ht="18.75">
       <c r="A30" s="52"/>
       <c r="B30" s="47"/>
       <c r="C30" s="42"/>
@@ -15287,7 +15287,7 @@
       <c r="H30" s="43"/>
       <c r="I30" s="52"/>
     </row>
-    <row r="31" spans="1:9" ht="18">
+    <row r="31" spans="1:9" ht="18.75">
       <c r="A31" s="52"/>
       <c r="B31" s="47"/>
       <c r="C31" s="42"/>
@@ -15298,7 +15298,7 @@
       <c r="H31" s="43"/>
       <c r="I31" s="52"/>
     </row>
-    <row r="32" spans="1:9" ht="18">
+    <row r="32" spans="1:9" ht="18.75">
       <c r="A32" s="52"/>
       <c r="B32" s="47"/>
       <c r="C32" s="42"/>
@@ -15309,7 +15309,7 @@
       <c r="H32" s="43"/>
       <c r="I32" s="52"/>
     </row>
-    <row r="33" spans="1:9" ht="18">
+    <row r="33" spans="1:9" ht="18.75">
       <c r="A33" s="52"/>
       <c r="B33" s="47"/>
       <c r="C33" s="42"/>
@@ -15320,7 +15320,7 @@
       <c r="H33" s="43"/>
       <c r="I33" s="52"/>
     </row>
-    <row r="34" spans="1:9" ht="18">
+    <row r="34" spans="1:9" ht="18.75">
       <c r="A34" s="52"/>
       <c r="B34" s="47"/>
       <c r="C34" s="42"/>
@@ -15331,7 +15331,7 @@
       <c r="H34" s="43"/>
       <c r="I34" s="52"/>
     </row>
-    <row r="35" spans="1:9" ht="18">
+    <row r="35" spans="1:9" ht="18.75">
       <c r="A35" s="52"/>
       <c r="B35" s="47"/>
       <c r="C35" s="42"/>
@@ -15342,7 +15342,7 @@
       <c r="H35" s="43"/>
       <c r="I35" s="52"/>
     </row>
-    <row r="36" spans="1:9" ht="18">
+    <row r="36" spans="1:9" ht="18.75">
       <c r="A36" s="52"/>
       <c r="B36" s="47"/>
       <c r="C36" s="42"/>
@@ -15353,7 +15353,7 @@
       <c r="H36" s="43"/>
       <c r="I36" s="52"/>
     </row>
-    <row r="37" spans="1:9" ht="18">
+    <row r="37" spans="1:9" ht="18.75">
       <c r="A37" s="52"/>
       <c r="B37" s="47"/>
       <c r="C37" s="42"/>
@@ -15364,7 +15364,7 @@
       <c r="H37" s="43"/>
       <c r="I37" s="52"/>
     </row>
-    <row r="38" spans="1:9" ht="18">
+    <row r="38" spans="1:9" ht="18.75">
       <c r="A38" s="52"/>
       <c r="B38" s="47"/>
       <c r="C38" s="35"/>
@@ -15375,7 +15375,7 @@
       <c r="H38" s="43"/>
       <c r="I38" s="52"/>
     </row>
-    <row r="39" spans="1:9" ht="22.65" customHeight="1">
+    <row r="39" spans="1:9" ht="22.7" customHeight="1">
       <c r="A39" s="52"/>
       <c r="B39" s="32"/>
       <c r="C39" s="31"/>
@@ -15386,7 +15386,7 @@
       <c r="H39" s="30"/>
       <c r="I39" s="52"/>
     </row>
-    <row r="40" spans="1:9" ht="22.65" customHeight="1">
+    <row r="40" spans="1:9" ht="22.7" customHeight="1">
       <c r="A40" s="52"/>
       <c r="B40" s="52"/>
       <c r="C40" s="52"/>
@@ -15409,22 +15409,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:J24"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" customWidth="1"/>
-    <col min="12" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="17.399999999999999">
+    <row r="2" spans="2:10" ht="18">
       <c r="B2" s="64" t="s">
         <v>164</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="40.200000000000003" thickBot="1">
+    <row r="6" spans="2:10" ht="39" thickBot="1">
       <c r="B6" s="13" t="s">
         <v>22</v>
       </c>
@@ -15628,7 +15628,7 @@
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
     </row>
-    <row r="24" ht="13.65" customHeight="1"/>
+    <row r="24" ht="13.7" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15642,15 +15642,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Arkusz1"/>
   <dimension ref="B2:J11"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" customWidth="1"/>
-    <col min="5" max="5" width="45.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="45.7109375" customWidth="1"/>
     <col min="6" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15720,7 +15720,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="40.200000000000003" thickBot="1">
+    <row r="6" spans="2:10" ht="39" thickBot="1">
       <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
@@ -15816,18 +15816,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Arkusz2"/>
   <dimension ref="B2:L16"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.33203125" customWidth="1"/>
-    <col min="3" max="3" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="7" width="19.88671875" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" customWidth="1"/>
+    <col min="5" max="7" width="19.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="17.399999999999999">
+    <row r="2" spans="2:12" ht="18">
       <c r="B2" s="64" t="s">
         <v>56</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="27" thickBot="1">
+    <row r="6" spans="2:12" ht="26.25" thickBot="1">
       <c r="B6" s="13" t="s">
         <v>64</v>
       </c>
@@ -16013,36 +16013,36 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41D2646-6146-4D14-B889-3C0C97BBED9D}">
   <dimension ref="A2:BV137"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="72" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.109375" style="72" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="72" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="72" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="72" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="72" customWidth="1"/>
     <col min="5" max="6" width="13" style="72" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" style="72" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="72" customWidth="1"/>
     <col min="8" max="8" width="13" style="72" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="72" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="72" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="72" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="72" customWidth="1"/>
     <col min="11" max="11" width="11" style="72" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="72" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" style="72" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="72" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" style="72" customWidth="1"/>
-    <col min="16" max="16" width="12.44140625" style="72" customWidth="1"/>
-    <col min="17" max="45" width="9.109375" style="72"/>
-    <col min="46" max="46" width="12.5546875" style="72" customWidth="1"/>
-    <col min="47" max="47" width="11.6640625" style="72" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="11.109375" style="72" customWidth="1"/>
-    <col min="49" max="49" width="23.44140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="72" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="72" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="72" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" style="72" customWidth="1"/>
+    <col min="17" max="45" width="9.140625" style="72"/>
+    <col min="46" max="46" width="12.5703125" style="72" customWidth="1"/>
+    <col min="47" max="47" width="11.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.140625" style="72" customWidth="1"/>
+    <col min="49" max="49" width="23.42578125" style="72" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="13" style="72" customWidth="1"/>
-    <col min="51" max="51" width="9.109375" style="72" customWidth="1"/>
-    <col min="52" max="56" width="9.109375" style="72"/>
+    <col min="51" max="51" width="9.140625" style="72" customWidth="1"/>
+    <col min="52" max="56" width="9.140625" style="72"/>
     <col min="57" max="57" width="6" style="72" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.109375" style="72" bestFit="1" customWidth="1"/>
-    <col min="59" max="65" width="9.109375" style="72"/>
-    <col min="66" max="66" width="28.44140625" style="72" bestFit="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.109375" style="72"/>
+    <col min="58" max="58" width="11.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="59" max="65" width="9.140625" style="72"/>
+    <col min="66" max="66" width="28.42578125" style="72" bestFit="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.140625" style="72"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19">
@@ -16052,14 +16052,14 @@
       <c r="D2" s="63"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:19" ht="13.8" thickBot="1">
+    <row r="3" spans="1:19" ht="13.5" thickBot="1">
       <c r="B3" s="65" t="s">
         <v>76</v>
       </c>
       <c r="C3" s="65"/>
       <c r="D3" s="63"/>
     </row>
-    <row r="4" spans="1:19" ht="21" thickBot="1">
+    <row r="4" spans="1:19" ht="20.25" thickBot="1">
       <c r="B4" s="132" t="s">
         <v>15</v>
       </c>
@@ -16097,7 +16097,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="13.8" thickBot="1">
+    <row r="5" spans="1:19" ht="13.5" thickBot="1">
       <c r="B5" s="133" t="s">
         <v>75</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
+    <row r="6" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B6" s="67" t="s">
         <v>210</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
+    <row r="7" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B7" s="69" t="s">
         <v>75</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>41.474999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
+    <row r="8" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B8" s="131" t="s">
         <v>79</v>
       </c>
@@ -16237,7 +16237,7 @@
         <v>74.655000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
+    <row r="9" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B9" s="130" t="s">
         <v>80</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>107.83500000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
+    <row r="10" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B10" s="160" t="s">
         <v>81</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>118.89499999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="16.2" customHeight="1" thickBot="1">
+    <row r="11" spans="1:19" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B11" s="130" t="s">
         <v>82</v>
       </c>
@@ -16384,7 +16384,7 @@
         <v>129.95499999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="16.2" customHeight="1">
+    <row r="12" spans="1:19" ht="16.149999999999999" customHeight="1">
       <c r="B12" s="160" t="s">
         <v>83</v>
       </c>
@@ -16418,7 +16418,7 @@
       <c r="O12" s="172"/>
       <c r="P12" s="172"/>
     </row>
-    <row r="13" spans="1:19" ht="16.2" customHeight="1">
+    <row r="13" spans="1:19" ht="16.149999999999999" customHeight="1">
       <c r="B13" s="130" t="s">
         <v>84</v>
       </c>
@@ -16452,7 +16452,7 @@
       <c r="O13" s="172"/>
       <c r="P13" s="172"/>
     </row>
-    <row r="14" spans="1:19" ht="16.2" customHeight="1">
+    <row r="14" spans="1:19" ht="16.149999999999999" customHeight="1">
       <c r="B14" s="69" t="s">
         <v>75</v>
       </c>
@@ -16470,7 +16470,7 @@
       <c r="O14" s="172"/>
       <c r="P14" s="172"/>
     </row>
-    <row r="15" spans="1:19" ht="16.2" customHeight="1">
+    <row r="15" spans="1:19" ht="16.149999999999999" customHeight="1">
       <c r="B15" s="131" t="s">
         <v>85</v>
       </c>
@@ -16625,19 +16625,19 @@
       </c>
       <c r="F18" s="158">
         <f>E18+(E18*$W$70)</f>
-        <v>599.7098380420781</v>
+        <v>596.70453781512606</v>
       </c>
       <c r="G18" s="158">
         <f>F18+$M$18</f>
-        <v>961.90244853155855</v>
+        <v>959.64847336134449</v>
       </c>
       <c r="H18" s="158">
         <f t="shared" ref="H18:I18" si="6">G18+$M$18</f>
-        <v>1324.0950590210391</v>
+        <v>1322.5924089075629</v>
       </c>
       <c r="I18" s="158">
         <f t="shared" si="6"/>
-        <v>1686.2876695105197</v>
+        <v>1685.5363444537813</v>
       </c>
       <c r="J18" s="158">
         <f>AZ52</f>
@@ -16645,11 +16645,11 @@
       </c>
       <c r="L18" s="174">
         <f t="shared" si="3"/>
-        <v>1448.7704419579218</v>
+        <v>1451.7757421848737</v>
       </c>
       <c r="M18" s="72">
         <f t="shared" si="4"/>
-        <v>362.19261048948044</v>
+        <v>362.94393554621843</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -16804,19 +16804,19 @@
       </c>
       <c r="F22" s="158">
         <f>E22+(E22*$W$70)</f>
-        <v>132.59401734220697</v>
+        <v>131.92955462184875</v>
       </c>
       <c r="G22" s="158">
         <f>F22+$M$22</f>
-        <v>116.88393575665523</v>
+        <v>116.38558871638656</v>
       </c>
       <c r="H22" s="158">
         <f t="shared" ref="H22:I22" si="10">G22+$M$22</f>
-        <v>101.1738541711035</v>
+        <v>100.84162281092438</v>
       </c>
       <c r="I22" s="158">
         <f t="shared" si="10"/>
-        <v>85.463772585551766</v>
+        <v>85.29765690546219</v>
       </c>
       <c r="J22" s="158">
         <f>AZ56+AZ58</f>
@@ -16824,11 +16824,11 @@
       </c>
       <c r="L22" s="174">
         <f t="shared" si="3"/>
-        <v>-62.840326342206964</v>
+        <v>-62.175863621848748</v>
       </c>
       <c r="M22" s="72">
         <f t="shared" si="4"/>
-        <v>-15.710081585551741</v>
+        <v>-15.543965905462187</v>
       </c>
       <c r="S22" s="63"/>
     </row>
@@ -17110,7 +17110,7 @@
       <c r="I29" s="69"/>
       <c r="J29" s="69"/>
     </row>
-    <row r="30" spans="2:19" ht="16.2" customHeight="1">
+    <row r="30" spans="2:19" ht="16.149999999999999" customHeight="1">
       <c r="B30" s="150" t="s">
         <v>165</v>
       </c>
@@ -17139,7 +17139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="16.2" customHeight="1">
+    <row r="31" spans="2:19" ht="16.149999999999999" customHeight="1">
       <c r="B31" s="69" t="s">
         <v>75</v>
       </c>
@@ -17154,7 +17154,7 @@
       <c r="I31" s="69"/>
       <c r="J31" s="69"/>
     </row>
-    <row r="32" spans="2:19" ht="16.2" customHeight="1">
+    <row r="32" spans="2:19" ht="16.149999999999999" customHeight="1">
       <c r="B32" s="160" t="s">
         <v>185</v>
       </c>
@@ -17183,7 +17183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:74" ht="16.2" customHeight="1">
+    <row r="33" spans="2:74" ht="16.149999999999999" customHeight="1">
       <c r="B33" s="130" t="s">
         <v>186</v>
       </c>
@@ -17212,8 +17212,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:74" ht="16.2" customHeight="1"/>
-    <row r="35" spans="2:74" ht="16.2" customHeight="1" thickBot="1">
+    <row r="34" spans="2:74" ht="16.149999999999999" customHeight="1"/>
+    <row r="35" spans="2:74" ht="16.149999999999999" customHeight="1" thickBot="1">
       <c r="B35" s="72" t="s">
         <v>99</v>
       </c>
@@ -17251,24 +17251,24 @@
       </c>
     </row>
     <row r="37" spans="2:74" ht="15.75" customHeight="1">
-      <c r="B37" s="190" t="s">
+      <c r="B37" s="183" t="s">
         <v>190</v>
       </c>
-      <c r="C37" s="191"/>
-      <c r="D37" s="191"/>
-      <c r="E37" s="191"/>
-      <c r="F37" s="191"/>
+      <c r="C37" s="184"/>
+      <c r="D37" s="184"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
       <c r="G37" s="108"/>
       <c r="H37" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="190" t="s">
+      <c r="J37" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="K37" s="191"/>
-      <c r="L37" s="191"/>
-      <c r="M37" s="191"/>
-      <c r="N37" s="191"/>
+      <c r="K37" s="184"/>
+      <c r="L37" s="184"/>
+      <c r="M37" s="184"/>
+      <c r="N37" s="184"/>
       <c r="O37" s="108"/>
       <c r="P37" s="109" t="s">
         <v>100</v>
@@ -17307,18 +17307,18 @@
       <c r="AV38" s="108"/>
       <c r="AW38" s="108"/>
       <c r="AX38" s="111"/>
-      <c r="BP38" s="183" t="s">
+      <c r="BP38" s="191" t="s">
         <v>207</v>
       </c>
-      <c r="BQ38" s="183"/>
-      <c r="BR38" s="183"/>
-      <c r="BS38" s="183"/>
-      <c r="BT38" s="183"/>
-      <c r="BU38" s="183"/>
-      <c r="BV38" s="183"/>
-    </row>
-    <row r="39" spans="2:74" ht="13.8" thickBot="1">
-      <c r="B39" s="184" t="s">
+      <c r="BQ38" s="191"/>
+      <c r="BR38" s="191"/>
+      <c r="BS38" s="191"/>
+      <c r="BT38" s="191"/>
+      <c r="BU38" s="191"/>
+      <c r="BV38" s="191"/>
+    </row>
+    <row r="39" spans="2:74" ht="13.5" thickBot="1">
+      <c r="B39" s="185" t="s">
         <v>101</v>
       </c>
       <c r="C39" s="186" t="s">
@@ -17337,10 +17337,10 @@
       <c r="H39" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="J39" s="184" t="s">
+      <c r="J39" s="185" t="s">
         <v>101</v>
       </c>
-      <c r="K39" s="185" t="s">
+      <c r="K39" s="190" t="s">
         <v>102</v>
       </c>
       <c r="L39" s="186" t="s">
@@ -17356,10 +17356,10 @@
       <c r="P39" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="AR39" s="184" t="s">
+      <c r="AR39" s="185" t="s">
         <v>101</v>
       </c>
-      <c r="AS39" s="185" t="s">
+      <c r="AS39" s="190" t="s">
         <v>102</v>
       </c>
       <c r="AT39" s="186" t="s">
@@ -17397,8 +17397,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="2:74" ht="13.65" customHeight="1">
-      <c r="B40" s="184"/>
+    <row r="40" spans="2:74" ht="13.7" customHeight="1">
+      <c r="B40" s="185"/>
       <c r="C40" s="186"/>
       <c r="D40" s="186"/>
       <c r="E40" s="186"/>
@@ -17409,8 +17409,8 @@
       <c r="H40" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="J40" s="184"/>
-      <c r="K40" s="185"/>
+      <c r="J40" s="185"/>
+      <c r="K40" s="190"/>
       <c r="L40" s="186"/>
       <c r="M40" s="186"/>
       <c r="N40" s="108"/>
@@ -17420,8 +17420,8 @@
       <c r="P40" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="AR40" s="184"/>
-      <c r="AS40" s="185"/>
+      <c r="AR40" s="185"/>
+      <c r="AS40" s="190"/>
       <c r="AT40" s="186"/>
       <c r="AU40" s="186"/>
       <c r="AV40" s="108"/>
@@ -18635,17 +18635,17 @@
       <c r="BF53" s="173"/>
       <c r="BG53" s="178"/>
       <c r="BL53" s="179"/>
-      <c r="BP53" s="183" t="s">
+      <c r="BP53" s="191" t="s">
         <v>208</v>
       </c>
-      <c r="BQ53" s="183"/>
-      <c r="BR53" s="183"/>
-      <c r="BS53" s="183"/>
-      <c r="BT53" s="183"/>
-      <c r="BU53" s="183"/>
-      <c r="BV53" s="183"/>
-    </row>
-    <row r="54" spans="2:74" ht="14.4">
+      <c r="BQ53" s="191"/>
+      <c r="BR53" s="191"/>
+      <c r="BS53" s="191"/>
+      <c r="BT53" s="191"/>
+      <c r="BU53" s="191"/>
+      <c r="BV53" s="191"/>
+    </row>
+    <row r="54" spans="2:74" ht="15">
       <c r="B54" s="110" t="s">
         <v>109</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>3.7290192319660207</v>
       </c>
     </row>
-    <row r="59" spans="2:74" ht="15.6">
+    <row r="59" spans="2:74" ht="14.25">
       <c r="B59" s="112" t="s">
         <v>117</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>34.66703822816504</v>
       </c>
     </row>
-    <row r="66" spans="2:74" ht="13.8" thickBot="1">
+    <row r="66" spans="2:74" ht="13.5" thickBot="1">
       <c r="B66" s="124" t="s">
         <v>121</v>
       </c>
@@ -20040,15 +20040,15 @@
         <f t="shared" si="88"/>
         <v>-6.4546038085728549E-2</v>
       </c>
-      <c r="BP68" s="183" t="s">
+      <c r="BP68" s="191" t="s">
         <v>204</v>
       </c>
-      <c r="BQ68" s="183"/>
-      <c r="BR68" s="183"/>
-      <c r="BS68" s="183"/>
-      <c r="BT68" s="183"/>
-      <c r="BU68" s="183"/>
-      <c r="BV68" s="183"/>
+      <c r="BQ68" s="191"/>
+      <c r="BR68" s="191"/>
+      <c r="BS68" s="191"/>
+      <c r="BT68" s="191"/>
+      <c r="BU68" s="191"/>
+      <c r="BV68" s="191"/>
     </row>
     <row r="69" spans="2:74">
       <c r="R69" s="72" t="s">
@@ -20103,18 +20103,18 @@
       </c>
       <c r="T70" s="72">
         <f t="shared" si="86"/>
-        <v>2329</v>
+        <v>2320.5</v>
       </c>
       <c r="U70" s="72">
-        <v>1967</v>
+        <v>1950</v>
       </c>
       <c r="V70" s="72">
         <f t="shared" si="87"/>
-        <v>-362</v>
+        <v>-370.5</v>
       </c>
       <c r="W70" s="173">
         <f t="shared" si="88"/>
-        <v>-0.15543151567196223</v>
+        <v>-0.15966386554621848</v>
       </c>
       <c r="BN70" s="72" t="s">
         <v>85</v>
@@ -20468,7 +20468,7 @@
         <v>255.62388150639833</v>
       </c>
     </row>
-    <row r="80" spans="2:74" ht="13.8" thickBot="1">
+    <row r="80" spans="2:74" ht="13.5" thickBot="1">
       <c r="B80" s="72" t="s">
         <v>122</v>
       </c>
@@ -20500,7 +20500,7 @@
         <v>218.33264065375658</v>
       </c>
     </row>
-    <row r="81" spans="2:74" ht="15.6">
+    <row r="81" spans="2:74" ht="15.75">
       <c r="B81" s="73" t="s">
         <v>181</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="88" spans="2:74" ht="13.8" thickBot="1">
+    <row r="88" spans="2:74" ht="13.5" thickBot="1">
       <c r="B88" s="92" t="s">
         <v>135</v>
       </c>
@@ -20763,7 +20763,7 @@
       <c r="F93" s="88"/>
       <c r="I93" s="100"/>
     </row>
-    <row r="94" spans="2:74" ht="13.8" thickBot="1">
+    <row r="94" spans="2:74" ht="13.5" thickBot="1">
       <c r="B94" s="101" t="s">
         <v>143</v>
       </c>
@@ -20783,12 +20783,12 @@
       <c r="H94" s="103"/>
       <c r="I94" s="104"/>
     </row>
-    <row r="97" spans="2:9" ht="13.8" thickBot="1">
+    <row r="97" spans="2:9" ht="13.5" thickBot="1">
       <c r="B97" s="72" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="98" spans="2:9" ht="15.6">
+    <row r="98" spans="2:9" ht="15.75">
       <c r="B98" s="73" t="s">
         <v>203</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="105" spans="2:9" ht="13.8" thickBot="1">
+    <row r="105" spans="2:9" ht="13.5" thickBot="1">
       <c r="B105" s="92" t="s">
         <v>135</v>
       </c>
@@ -20968,7 +20968,7 @@
       <c r="E110" s="88"/>
       <c r="I110" s="100"/>
     </row>
-    <row r="111" spans="2:9" ht="13.8" thickBot="1">
+    <row r="111" spans="2:9" ht="13.5" thickBot="1">
       <c r="B111" s="101" t="s">
         <v>143</v>
       </c>
@@ -21394,17 +21394,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="AR37:AW37"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="M39:M40"/>
     <mergeCell ref="BP38:BV38"/>
     <mergeCell ref="BP53:BV53"/>
     <mergeCell ref="BP68:BV68"/>
@@ -21412,6 +21401,17 @@
     <mergeCell ref="AS39:AS40"/>
     <mergeCell ref="AT39:AT40"/>
     <mergeCell ref="AU39:AU40"/>
+    <mergeCell ref="AR37:AW37"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21424,26 +21424,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -21686,32 +21666,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B5E23FA-4CBB-4638-8409-464A8CA39611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21728,4 +21703,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/VT_Model_DMD.xlsx
+++ b/VT_Model_DMD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1079" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CDBBA23-34F2-40F6-A98A-F3F51960EB4C}"/>
+  <xr:revisionPtr revIDLastSave="1087" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C259C1AA-2D7D-468C-BC35-738B7FFFBED3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="151" r:id="rId1"/>
@@ -6249,30 +6249,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="14" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="14" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="143" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="59" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="60" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="61" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="23" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="14" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="59" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="60" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="61" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="3" borderId="24" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="14" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="16" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -9456,16 +9456,16 @@
                   <c:v>710.07839999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>596.70453781512606</c:v>
+                  <c:v>599.7098380420781</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>959.64847336134449</c:v>
+                  <c:v>961.90244853155855</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1322.5924089075629</c:v>
+                  <c:v>1324.0950590210391</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1685.5363444537813</c:v>
+                  <c:v>1686.2876695105197</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2048.4802799999998</c:v>
@@ -9832,16 +9832,16 @@
                   <c:v>156.99617000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>131.92955462184875</c:v>
+                  <c:v>132.59401734220697</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>116.38558871638656</c:v>
+                  <c:v>116.88393575665523</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100.84162281092438</c:v>
+                  <c:v>101.1738541711035</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>85.29765690546219</c:v>
+                  <c:v>85.463772585551766</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>69.753691000000003</c:v>
@@ -16625,19 +16625,19 @@
       </c>
       <c r="F18" s="158">
         <f>E18+(E18*$W$70)</f>
-        <v>596.70453781512606</v>
+        <v>599.7098380420781</v>
       </c>
       <c r="G18" s="158">
         <f>F18+$M$18</f>
-        <v>959.64847336134449</v>
+        <v>961.90244853155855</v>
       </c>
       <c r="H18" s="158">
         <f t="shared" ref="H18:I18" si="6">G18+$M$18</f>
-        <v>1322.5924089075629</v>
+        <v>1324.0950590210391</v>
       </c>
       <c r="I18" s="158">
         <f t="shared" si="6"/>
-        <v>1685.5363444537813</v>
+        <v>1686.2876695105197</v>
       </c>
       <c r="J18" s="158">
         <f>AZ52</f>
@@ -16645,11 +16645,11 @@
       </c>
       <c r="L18" s="174">
         <f t="shared" si="3"/>
-        <v>1451.7757421848737</v>
+        <v>1448.7704419579218</v>
       </c>
       <c r="M18" s="72">
         <f t="shared" si="4"/>
-        <v>362.94393554621843</v>
+        <v>362.19261048948044</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -16804,19 +16804,19 @@
       </c>
       <c r="F22" s="158">
         <f>E22+(E22*$W$70)</f>
-        <v>131.92955462184875</v>
+        <v>132.59401734220697</v>
       </c>
       <c r="G22" s="158">
         <f>F22+$M$22</f>
-        <v>116.38558871638656</v>
+        <v>116.88393575665523</v>
       </c>
       <c r="H22" s="158">
         <f t="shared" ref="H22:I22" si="10">G22+$M$22</f>
-        <v>100.84162281092438</v>
+        <v>101.1738541711035</v>
       </c>
       <c r="I22" s="158">
         <f t="shared" si="10"/>
-        <v>85.29765690546219</v>
+        <v>85.463772585551766</v>
       </c>
       <c r="J22" s="158">
         <f>AZ56+AZ58</f>
@@ -16824,11 +16824,11 @@
       </c>
       <c r="L22" s="174">
         <f t="shared" si="3"/>
-        <v>-62.175863621848748</v>
+        <v>-62.840326342206964</v>
       </c>
       <c r="M22" s="72">
         <f t="shared" si="4"/>
-        <v>-15.543965905462187</v>
+        <v>-15.710081585551741</v>
       </c>
       <c r="S22" s="63"/>
     </row>
@@ -17251,24 +17251,24 @@
       </c>
     </row>
     <row r="37" spans="2:74" ht="15.75" customHeight="1">
-      <c r="B37" s="183" t="s">
+      <c r="B37" s="190" t="s">
         <v>190</v>
       </c>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="184"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="191"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="191"/>
       <c r="G37" s="108"/>
       <c r="H37" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="183" t="s">
+      <c r="J37" s="190" t="s">
         <v>191</v>
       </c>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-      <c r="M37" s="184"/>
-      <c r="N37" s="184"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="191"/>
+      <c r="N37" s="191"/>
       <c r="O37" s="108"/>
       <c r="P37" s="109" t="s">
         <v>100</v>
@@ -17307,18 +17307,18 @@
       <c r="AV38" s="108"/>
       <c r="AW38" s="108"/>
       <c r="AX38" s="111"/>
-      <c r="BP38" s="191" t="s">
+      <c r="BP38" s="183" t="s">
         <v>207</v>
       </c>
-      <c r="BQ38" s="191"/>
-      <c r="BR38" s="191"/>
-      <c r="BS38" s="191"/>
-      <c r="BT38" s="191"/>
-      <c r="BU38" s="191"/>
-      <c r="BV38" s="191"/>
+      <c r="BQ38" s="183"/>
+      <c r="BR38" s="183"/>
+      <c r="BS38" s="183"/>
+      <c r="BT38" s="183"/>
+      <c r="BU38" s="183"/>
+      <c r="BV38" s="183"/>
     </row>
     <row r="39" spans="2:74" ht="13.5" thickBot="1">
-      <c r="B39" s="185" t="s">
+      <c r="B39" s="184" t="s">
         <v>101</v>
       </c>
       <c r="C39" s="186" t="s">
@@ -17337,10 +17337,10 @@
       <c r="H39" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="J39" s="185" t="s">
+      <c r="J39" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="K39" s="190" t="s">
+      <c r="K39" s="185" t="s">
         <v>102</v>
       </c>
       <c r="L39" s="186" t="s">
@@ -17356,10 +17356,10 @@
       <c r="P39" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="AR39" s="185" t="s">
+      <c r="AR39" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="AS39" s="190" t="s">
+      <c r="AS39" s="185" t="s">
         <v>102</v>
       </c>
       <c r="AT39" s="186" t="s">
@@ -17398,7 +17398,7 @@
       </c>
     </row>
     <row r="40" spans="2:74" ht="13.7" customHeight="1">
-      <c r="B40" s="185"/>
+      <c r="B40" s="184"/>
       <c r="C40" s="186"/>
       <c r="D40" s="186"/>
       <c r="E40" s="186"/>
@@ -17409,8 +17409,8 @@
       <c r="H40" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="J40" s="185"/>
-      <c r="K40" s="190"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="185"/>
       <c r="L40" s="186"/>
       <c r="M40" s="186"/>
       <c r="N40" s="108"/>
@@ -17420,8 +17420,8 @@
       <c r="P40" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="AR40" s="185"/>
-      <c r="AS40" s="190"/>
+      <c r="AR40" s="184"/>
+      <c r="AS40" s="185"/>
       <c r="AT40" s="186"/>
       <c r="AU40" s="186"/>
       <c r="AV40" s="108"/>
@@ -18635,15 +18635,15 @@
       <c r="BF53" s="173"/>
       <c r="BG53" s="178"/>
       <c r="BL53" s="179"/>
-      <c r="BP53" s="191" t="s">
+      <c r="BP53" s="183" t="s">
         <v>208</v>
       </c>
-      <c r="BQ53" s="191"/>
-      <c r="BR53" s="191"/>
-      <c r="BS53" s="191"/>
-      <c r="BT53" s="191"/>
-      <c r="BU53" s="191"/>
-      <c r="BV53" s="191"/>
+      <c r="BQ53" s="183"/>
+      <c r="BR53" s="183"/>
+      <c r="BS53" s="183"/>
+      <c r="BT53" s="183"/>
+      <c r="BU53" s="183"/>
+      <c r="BV53" s="183"/>
     </row>
     <row r="54" spans="2:74" ht="15">
       <c r="B54" s="110" t="s">
@@ -20040,15 +20040,15 @@
         <f t="shared" si="88"/>
         <v>-6.4546038085728549E-2</v>
       </c>
-      <c r="BP68" s="191" t="s">
+      <c r="BP68" s="183" t="s">
         <v>204</v>
       </c>
-      <c r="BQ68" s="191"/>
-      <c r="BR68" s="191"/>
-      <c r="BS68" s="191"/>
-      <c r="BT68" s="191"/>
-      <c r="BU68" s="191"/>
-      <c r="BV68" s="191"/>
+      <c r="BQ68" s="183"/>
+      <c r="BR68" s="183"/>
+      <c r="BS68" s="183"/>
+      <c r="BT68" s="183"/>
+      <c r="BU68" s="183"/>
+      <c r="BV68" s="183"/>
     </row>
     <row r="69" spans="2:74">
       <c r="R69" s="72" t="s">
@@ -20103,18 +20103,18 @@
       </c>
       <c r="T70" s="72">
         <f t="shared" si="86"/>
-        <v>2320.5</v>
+        <v>2329</v>
       </c>
       <c r="U70" s="72">
-        <v>1950</v>
+        <v>1967</v>
       </c>
       <c r="V70" s="72">
         <f t="shared" si="87"/>
-        <v>-370.5</v>
+        <v>-362</v>
       </c>
       <c r="W70" s="173">
         <f t="shared" si="88"/>
-        <v>-0.15966386554621848</v>
+        <v>-0.15543151567196223</v>
       </c>
       <c r="BN70" s="72" t="s">
         <v>85</v>
@@ -20274,7 +20274,7 @@
         <v>197.244</v>
       </c>
       <c r="BR73" s="72">
-        <f t="shared" si="92"/>
+        <f>BR43/BR58</f>
         <v>165.41704109737631</v>
       </c>
       <c r="BS73" s="72">
@@ -21394,6 +21394,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="AR37:AW37"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="M39:M40"/>
     <mergeCell ref="BP38:BV38"/>
     <mergeCell ref="BP53:BV53"/>
     <mergeCell ref="BP68:BV68"/>
@@ -21401,17 +21412,6 @@
     <mergeCell ref="AS39:AS40"/>
     <mergeCell ref="AT39:AT40"/>
     <mergeCell ref="AU39:AU40"/>
-    <mergeCell ref="AR37:AW37"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21424,6 +21424,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -21666,27 +21686,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B5E23FA-4CBB-4638-8409-464A8CA39611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21703,29 +21728,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/VT_Model_DMD.xlsx
+++ b/VT_Model_DMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr showObjects="placeholders" codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1087" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C259C1AA-2D7D-468C-BC35-738B7FFFBED3}"/>
+  <xr:revisionPtr revIDLastSave="1104" documentId="13_ncr:1_{7DAD6907-FF2C-4C04-8170-EB4B769AE67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DDB2CB5-88BE-458A-BB60-17B88D4B61E3}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="151" r:id="rId1"/>
@@ -14017,15 +14017,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>29048</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>171920</xdr:rowOff>
+      <xdr:colOff>137905</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>63062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
-      <xdr:colOff>418443</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>58615</xdr:rowOff>
+      <xdr:colOff>527300</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>72222</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17165,22 +17165,22 @@
         <v>1</v>
       </c>
       <c r="E32" s="160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="160">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32" s="160">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I32" s="160">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J32" s="160">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="2:74" ht="16.149999999999999" customHeight="1">
@@ -17194,22 +17194,22 @@
         <v>1</v>
       </c>
       <c r="E33" s="130">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F33" s="130">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33" s="130">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H33" s="130">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I33" s="130">
+        <v>56</v>
+      </c>
+      <c r="J33" s="130">
         <v>70</v>
-      </c>
-      <c r="J33" s="130">
-        <v>100</v>
       </c>
     </row>
     <row r="34" spans="2:74" ht="16.149999999999999" customHeight="1"/>
@@ -21424,26 +21424,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -21686,32 +21666,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B5E23FA-4CBB-4638-8409-464A8CA39611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21728,4 +21703,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>